--- a/source/INVOICE.xlsx
+++ b/source/INVOICE.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\ADMISSION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1DAB8730-03F8-42E0-9B4C-B209E0172DCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CF95A7-79BB-4346-9015-0ECA4F51626E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="FEE BREAKDOWN" sheetId="1" r:id="rId1"/>
@@ -477,30 +477,50 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{0C8E206A-8D4D-4E99-BFCB-89273F9D19CB}">
+  <we:reference id="wa200009404" version="1.0.0.8" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="WA200009404" version="1.0.0.8" store="" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA1000"/>
-  <sheetFormatPr defaultColWidth="14.453125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.7265625" customWidth="1"/>
-    <col min="2" max="2" width="11.7265625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="2" max="2" width="11.7109375" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="12" customWidth="1"/>
-    <col min="5" max="5" width="13.1796875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.140625" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="16" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.453125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.81640625" style="13" customWidth="1"/>
+    <col min="7" max="8" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.85546875" style="13" customWidth="1"/>
     <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="11" customWidth="1"/>
-    <col min="12" max="12" width="15.453125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.26953125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.81640625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="27.1796875" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="32.1796875" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="15.81640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="27.140625" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="32.140625" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="15.85546875" bestFit="1" customWidth="1"/>
     <col min="18" max="21" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" ht="15.5" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:27" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
@@ -563,7 +583,7 @@
       <c r="Z1" s="1"/>
       <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A2" s="15" t="s">
         <v>15</v>
       </c>
@@ -589,7 +609,7 @@
         <v>0</v>
       </c>
       <c r="I2" s="10">
-        <v>3200</v>
+        <v>3050</v>
       </c>
       <c r="J2" s="8">
         <v>16000</v>
@@ -614,10 +634,10 @@
       </c>
       <c r="Q2" s="17">
         <f t="shared" ref="Q2:Q17" si="0">SUM(B2:P2)</f>
-        <v>73200</v>
-      </c>
-    </row>
-    <row r="3" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+        <v>73050</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A3" s="15" t="s">
         <v>16</v>
       </c>
@@ -671,7 +691,7 @@
         <v>83340</v>
       </c>
     </row>
-    <row r="4" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A4" s="15" t="s">
         <v>17</v>
       </c>
@@ -697,7 +717,7 @@
         <v>12360</v>
       </c>
       <c r="I4" s="10">
-        <v>7400</v>
+        <v>7550</v>
       </c>
       <c r="J4" s="8">
         <v>16000</v>
@@ -722,10 +742,10 @@
       </c>
       <c r="Q4" s="17">
         <f t="shared" si="0"/>
-        <v>89760</v>
-      </c>
-    </row>
-    <row r="5" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+        <v>89910</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A5" s="15" t="s">
         <v>18</v>
       </c>
@@ -751,7 +771,7 @@
         <v>12840</v>
       </c>
       <c r="I5" s="10">
-        <v>7400</v>
+        <v>7550</v>
       </c>
       <c r="J5" s="8">
         <v>16000</v>
@@ -776,10 +796,10 @@
       </c>
       <c r="Q5" s="17">
         <f t="shared" si="0"/>
-        <v>90240</v>
-      </c>
-    </row>
-    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>90390</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="15" t="s">
         <v>19</v>
       </c>
@@ -805,7 +825,7 @@
         <v>28080</v>
       </c>
       <c r="I6" s="10">
-        <v>10330</v>
+        <v>10730</v>
       </c>
       <c r="J6" s="8">
         <v>16000</v>
@@ -830,10 +850,10 @@
       </c>
       <c r="Q6" s="17">
         <f t="shared" si="0"/>
-        <v>108410</v>
-      </c>
-    </row>
-    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>108810</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="15" t="s">
         <v>20</v>
       </c>
@@ -859,7 +879,7 @@
         <v>24900</v>
       </c>
       <c r="I7" s="10">
-        <v>10780</v>
+        <v>11330</v>
       </c>
       <c r="J7" s="8">
         <v>16000</v>
@@ -884,10 +904,10 @@
       </c>
       <c r="Q7" s="17">
         <f t="shared" si="0"/>
-        <v>114180</v>
-      </c>
-    </row>
-    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>114730</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="15" t="s">
         <v>21</v>
       </c>
@@ -913,7 +933,7 @@
         <v>24900</v>
       </c>
       <c r="I8" s="10">
-        <v>10780</v>
+        <v>11330</v>
       </c>
       <c r="J8" s="8">
         <v>16000</v>
@@ -938,10 +958,10 @@
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="0"/>
-        <v>114180</v>
-      </c>
-    </row>
-    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>114730</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="15" t="s">
         <v>22</v>
       </c>
@@ -967,7 +987,7 @@
         <v>26040</v>
       </c>
       <c r="I9" s="10">
-        <v>12020</v>
+        <v>13230</v>
       </c>
       <c r="J9" s="8">
         <v>16000</v>
@@ -992,10 +1012,10 @@
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="0"/>
-        <v>116560</v>
-      </c>
-    </row>
-    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>117770</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="15" t="s">
         <v>23</v>
       </c>
@@ -1021,7 +1041,7 @@
         <v>26040</v>
       </c>
       <c r="I10" s="10">
-        <v>12020</v>
+        <v>13230</v>
       </c>
       <c r="J10" s="8">
         <v>16000</v>
@@ -1046,10 +1066,10 @@
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="0"/>
-        <v>116560</v>
-      </c>
-    </row>
-    <row r="11" spans="1:27" ht="14.5" x14ac:dyDescent="0.35">
+        <v>117770</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.25">
       <c r="A11" s="15" t="s">
         <v>24</v>
       </c>
@@ -1075,7 +1095,7 @@
         <v>27660</v>
       </c>
       <c r="I11" s="10">
-        <v>12020</v>
+        <v>13230</v>
       </c>
       <c r="J11" s="8">
         <v>16000</v>
@@ -1100,10 +1120,10 @@
       </c>
       <c r="Q11" s="17">
         <f t="shared" si="0"/>
-        <v>118180</v>
-      </c>
-    </row>
-    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119390</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="15" t="s">
         <v>25</v>
       </c>
@@ -1129,7 +1149,7 @@
         <v>17940</v>
       </c>
       <c r="I12" s="10">
-        <v>29790</v>
+        <v>16190</v>
       </c>
       <c r="J12" s="8">
         <v>12000</v>
@@ -1154,10 +1174,10 @@
       </c>
       <c r="Q12" s="17">
         <f t="shared" si="0"/>
-        <v>132730</v>
-      </c>
-    </row>
-    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>119130</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="15" t="s">
         <v>26</v>
       </c>
@@ -1183,7 +1203,7 @@
         <v>17940</v>
       </c>
       <c r="I13" s="10">
-        <v>14990</v>
+        <v>14330</v>
       </c>
       <c r="J13" s="8">
         <v>12000</v>
@@ -1208,10 +1228,10 @@
       </c>
       <c r="Q13" s="17">
         <f t="shared" si="0"/>
-        <v>117930</v>
-      </c>
-    </row>
-    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>117270</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="15" t="s">
         <v>27</v>
       </c>
@@ -1237,7 +1257,7 @@
         <v>24180</v>
       </c>
       <c r="I14" s="10">
-        <v>14990</v>
+        <v>14330</v>
       </c>
       <c r="J14" s="8">
         <v>12000</v>
@@ -1262,10 +1282,10 @@
       </c>
       <c r="Q14" s="17">
         <f t="shared" si="0"/>
-        <v>124170</v>
-      </c>
-    </row>
-    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>123510</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="15" t="s">
         <v>28</v>
       </c>
@@ -1291,7 +1311,7 @@
         <v>12480</v>
       </c>
       <c r="I15" s="10">
-        <v>27390</v>
+        <v>14330</v>
       </c>
       <c r="J15" s="8">
         <v>20000</v>
@@ -1316,10 +1336,10 @@
       </c>
       <c r="Q15" s="17">
         <f t="shared" si="0"/>
-        <v>141870</v>
-      </c>
-    </row>
-    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>128810</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="15" t="s">
         <v>29</v>
       </c>
@@ -1345,7 +1365,7 @@
         <v>12480</v>
       </c>
       <c r="I16" s="10">
-        <v>14990</v>
+        <v>14330</v>
       </c>
       <c r="J16" s="8">
         <v>20000</v>
@@ -1370,10 +1390,10 @@
       </c>
       <c r="Q16" s="17">
         <f t="shared" si="0"/>
-        <v>129470</v>
-      </c>
-    </row>
-    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>128810</v>
+      </c>
+    </row>
+    <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="15" t="s">
         <v>30</v>
       </c>
@@ -1399,7 +1419,7 @@
         <v>12480</v>
       </c>
       <c r="I17" s="10">
-        <v>14990</v>
+        <v>14330</v>
       </c>
       <c r="J17" s="8">
         <v>20000</v>
@@ -1424,10 +1444,10 @@
       </c>
       <c r="Q17" s="17">
         <f t="shared" si="0"/>
-        <v>129470</v>
-      </c>
-    </row>
-    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+        <v>128810</v>
+      </c>
+    </row>
+    <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="2"/>
       <c r="B18" s="3"/>
       <c r="C18" s="3"/>
@@ -1446,7 +1466,7 @@
       <c r="P18" s="5"/>
       <c r="Q18" s="4"/>
     </row>
-    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A19" s="6"/>
       <c r="B19" s="4"/>
       <c r="C19" s="4"/>
@@ -1465,7 +1485,7 @@
       <c r="P19" s="4"/>
       <c r="Q19" s="4"/>
     </row>
-    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A20" s="6"/>
       <c r="B20" s="4"/>
       <c r="C20" s="4"/>
@@ -1484,7 +1504,7 @@
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
     </row>
-    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="6"/>
       <c r="B21" s="4"/>
       <c r="C21" s="4"/>
@@ -1503,7 +1523,7 @@
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
     </row>
-    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A22" s="6"/>
       <c r="B22" s="4"/>
       <c r="C22" s="4"/>
@@ -1522,7 +1542,7 @@
       <c r="P22" s="4"/>
       <c r="Q22" s="4"/>
     </row>
-    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A23" s="6"/>
       <c r="B23" s="4"/>
       <c r="C23" s="4"/>
@@ -1541,7 +1561,7 @@
       <c r="P23" s="4"/>
       <c r="Q23" s="4"/>
     </row>
-    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="6"/>
       <c r="B24" s="4"/>
       <c r="C24" s="4"/>
@@ -1560,7 +1580,7 @@
       <c r="P24" s="4"/>
       <c r="Q24" s="4"/>
     </row>
-    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="6"/>
       <c r="B25" s="4"/>
       <c r="C25" s="4"/>
@@ -1579,7 +1599,7 @@
       <c r="P25" s="4"/>
       <c r="Q25" s="4"/>
     </row>
-    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="6"/>
       <c r="B26" s="4"/>
       <c r="C26" s="4"/>
@@ -1598,7 +1618,7 @@
       <c r="P26" s="4"/>
       <c r="Q26" s="4"/>
     </row>
-    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="6"/>
       <c r="B27" s="4"/>
       <c r="C27" s="4"/>
@@ -1617,7 +1637,7 @@
       <c r="P27" s="4"/>
       <c r="Q27" s="4"/>
     </row>
-    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="6"/>
       <c r="B28" s="4"/>
       <c r="C28" s="4"/>
@@ -1636,7 +1656,7 @@
       <c r="P28" s="4"/>
       <c r="Q28" s="4"/>
     </row>
-    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="6"/>
       <c r="B29" s="4"/>
       <c r="C29" s="4"/>
@@ -1655,7 +1675,7 @@
       <c r="P29" s="4"/>
       <c r="Q29" s="4"/>
     </row>
-    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="6"/>
       <c r="B30" s="4"/>
       <c r="C30" s="4"/>
@@ -1674,7 +1694,7 @@
       <c r="P30" s="4"/>
       <c r="Q30" s="4"/>
     </row>
-    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="6"/>
       <c r="B31" s="4"/>
       <c r="C31" s="4"/>
@@ -1693,7 +1713,7 @@
       <c r="P31" s="4"/>
       <c r="Q31" s="4"/>
     </row>
-    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="6"/>
       <c r="B32" s="4"/>
       <c r="C32" s="4"/>
@@ -1712,7 +1732,7 @@
       <c r="P32" s="4"/>
       <c r="Q32" s="4"/>
     </row>
-    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="6"/>
       <c r="B33" s="4"/>
       <c r="C33" s="4"/>
@@ -1731,7 +1751,7 @@
       <c r="P33" s="4"/>
       <c r="Q33" s="4"/>
     </row>
-    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="6"/>
       <c r="B34" s="4"/>
       <c r="C34" s="4"/>
@@ -1750,7 +1770,7 @@
       <c r="P34" s="4"/>
       <c r="Q34" s="4"/>
     </row>
-    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A35" s="2"/>
       <c r="B35" s="3"/>
       <c r="C35" s="3"/>
@@ -1769,7 +1789,7 @@
       <c r="P35" s="5"/>
       <c r="Q35" s="4"/>
     </row>
-    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A36" s="2"/>
       <c r="B36" s="3"/>
       <c r="C36" s="3"/>
@@ -1788,7 +1808,7 @@
       <c r="P36" s="5"/>
       <c r="Q36" s="4"/>
     </row>
-    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A37" s="2"/>
       <c r="B37" s="3"/>
       <c r="C37" s="3"/>
@@ -1807,7 +1827,7 @@
       <c r="P37" s="5"/>
       <c r="Q37" s="4"/>
     </row>
-    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A38" s="2"/>
       <c r="B38" s="3"/>
       <c r="C38" s="3"/>
@@ -1826,7 +1846,7 @@
       <c r="P38" s="5"/>
       <c r="Q38" s="4"/>
     </row>
-    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A39" s="2"/>
       <c r="B39" s="3"/>
       <c r="C39" s="3"/>
@@ -1845,7 +1865,7 @@
       <c r="P39" s="5"/>
       <c r="Q39" s="4"/>
     </row>
-    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A40" s="2"/>
       <c r="B40" s="3"/>
       <c r="C40" s="3"/>
@@ -1864,7 +1884,7 @@
       <c r="P40" s="5"/>
       <c r="Q40" s="4"/>
     </row>
-    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A41" s="2"/>
       <c r="B41" s="3"/>
       <c r="C41" s="3"/>
@@ -1883,7 +1903,7 @@
       <c r="P41" s="5"/>
       <c r="Q41" s="4"/>
     </row>
-    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A42" s="2"/>
       <c r="B42" s="3"/>
       <c r="C42" s="3"/>
@@ -1902,7 +1922,7 @@
       <c r="P42" s="5"/>
       <c r="Q42" s="4"/>
     </row>
-    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A43" s="2"/>
       <c r="B43" s="3"/>
       <c r="C43" s="3"/>
@@ -1921,7 +1941,7 @@
       <c r="P43" s="5"/>
       <c r="Q43" s="4"/>
     </row>
-    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A44" s="2"/>
       <c r="B44" s="3"/>
       <c r="C44" s="3"/>
@@ -1940,7 +1960,7 @@
       <c r="P44" s="5"/>
       <c r="Q44" s="4"/>
     </row>
-    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A45" s="2"/>
       <c r="B45" s="3"/>
       <c r="C45" s="3"/>
@@ -1959,7 +1979,7 @@
       <c r="P45" s="5"/>
       <c r="Q45" s="4"/>
     </row>
-    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A46" s="2"/>
       <c r="B46" s="3"/>
       <c r="C46" s="3"/>
@@ -1978,7 +1998,7 @@
       <c r="P46" s="5"/>
       <c r="Q46" s="4"/>
     </row>
-    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="2"/>
       <c r="B47" s="3"/>
       <c r="C47" s="3"/>
@@ -1997,7 +2017,7 @@
       <c r="P47" s="5"/>
       <c r="Q47" s="4"/>
     </row>
-    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="2"/>
       <c r="B48" s="3"/>
       <c r="C48" s="3"/>
@@ -2016,7 +2036,7 @@
       <c r="P48" s="5"/>
       <c r="Q48" s="4"/>
     </row>
-    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A49" s="2"/>
       <c r="B49" s="3"/>
       <c r="C49" s="3"/>
@@ -2035,7 +2055,7 @@
       <c r="P49" s="5"/>
       <c r="Q49" s="4"/>
     </row>
-    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="2"/>
       <c r="B50" s="3"/>
       <c r="C50" s="3"/>
@@ -2054,7 +2074,7 @@
       <c r="P50" s="5"/>
       <c r="Q50" s="4"/>
     </row>
-    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="2"/>
       <c r="B51" s="3"/>
       <c r="C51" s="3"/>
@@ -2073,7 +2093,7 @@
       <c r="P51" s="5"/>
       <c r="Q51" s="4"/>
     </row>
-    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A52" s="2"/>
       <c r="B52" s="3"/>
       <c r="C52" s="3"/>
@@ -2092,7 +2112,7 @@
       <c r="P52" s="5"/>
       <c r="Q52" s="4"/>
     </row>
-    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A53" s="2"/>
       <c r="B53" s="3"/>
       <c r="C53" s="3"/>
@@ -2111,7 +2131,7 @@
       <c r="P53" s="5"/>
       <c r="Q53" s="4"/>
     </row>
-    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2130,7 +2150,7 @@
       <c r="P54" s="5"/>
       <c r="Q54" s="4"/>
     </row>
-    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A55" s="2"/>
       <c r="B55" s="3"/>
       <c r="C55" s="3"/>
@@ -2149,7 +2169,7 @@
       <c r="P55" s="5"/>
       <c r="Q55" s="4"/>
     </row>
-    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A56" s="2"/>
       <c r="B56" s="3"/>
       <c r="C56" s="3"/>
@@ -2168,7 +2188,7 @@
       <c r="P56" s="5"/>
       <c r="Q56" s="4"/>
     </row>
-    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A57" s="2"/>
       <c r="B57" s="3"/>
       <c r="C57" s="3"/>
@@ -2187,7 +2207,7 @@
       <c r="P57" s="5"/>
       <c r="Q57" s="4"/>
     </row>
-    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="2"/>
       <c r="B58" s="3"/>
       <c r="C58" s="3"/>
@@ -2206,7 +2226,7 @@
       <c r="P58" s="5"/>
       <c r="Q58" s="4"/>
     </row>
-    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="2"/>
       <c r="B59" s="3"/>
       <c r="C59" s="3"/>
@@ -2225,7 +2245,7 @@
       <c r="P59" s="5"/>
       <c r="Q59" s="4"/>
     </row>
-    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A60" s="2"/>
       <c r="B60" s="3"/>
       <c r="C60" s="3"/>
@@ -2244,7 +2264,7 @@
       <c r="P60" s="5"/>
       <c r="Q60" s="4"/>
     </row>
-    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="2"/>
       <c r="B61" s="3"/>
       <c r="C61" s="3"/>
@@ -2263,7 +2283,7 @@
       <c r="P61" s="5"/>
       <c r="Q61" s="4"/>
     </row>
-    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A62" s="2"/>
       <c r="B62" s="3"/>
       <c r="C62" s="3"/>
@@ -2282,7 +2302,7 @@
       <c r="P62" s="5"/>
       <c r="Q62" s="4"/>
     </row>
-    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A63" s="2"/>
       <c r="B63" s="3"/>
       <c r="C63" s="3"/>
@@ -2301,7 +2321,7 @@
       <c r="P63" s="5"/>
       <c r="Q63" s="4"/>
     </row>
-    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A64" s="2"/>
       <c r="B64" s="3"/>
       <c r="C64" s="3"/>
@@ -2320,7 +2340,7 @@
       <c r="P64" s="5"/>
       <c r="Q64" s="4"/>
     </row>
-    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A65" s="2"/>
       <c r="B65" s="3"/>
       <c r="C65" s="3"/>
@@ -2339,7 +2359,7 @@
       <c r="P65" s="5"/>
       <c r="Q65" s="4"/>
     </row>
-    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A66" s="2"/>
       <c r="B66" s="3"/>
       <c r="C66" s="3"/>
@@ -2358,7 +2378,7 @@
       <c r="P66" s="5"/>
       <c r="Q66" s="4"/>
     </row>
-    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A67" s="2"/>
       <c r="B67" s="3"/>
       <c r="C67" s="3"/>
@@ -2377,7 +2397,7 @@
       <c r="P67" s="5"/>
       <c r="Q67" s="4"/>
     </row>
-    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A68" s="2"/>
       <c r="B68" s="3"/>
       <c r="C68" s="3"/>
@@ -2396,7 +2416,7 @@
       <c r="P68" s="5"/>
       <c r="Q68" s="4"/>
     </row>
-    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A69" s="2"/>
       <c r="B69" s="3"/>
       <c r="C69" s="3"/>
@@ -2415,7 +2435,7 @@
       <c r="P69" s="5"/>
       <c r="Q69" s="4"/>
     </row>
-    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A70" s="2"/>
       <c r="B70" s="3"/>
       <c r="C70" s="3"/>
@@ -2434,7 +2454,7 @@
       <c r="P70" s="5"/>
       <c r="Q70" s="4"/>
     </row>
-    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A71" s="2"/>
       <c r="B71" s="3"/>
       <c r="C71" s="3"/>
@@ -2453,7 +2473,7 @@
       <c r="P71" s="5"/>
       <c r="Q71" s="4"/>
     </row>
-    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A72" s="2"/>
       <c r="B72" s="3"/>
       <c r="C72" s="3"/>
@@ -2472,7 +2492,7 @@
       <c r="P72" s="5"/>
       <c r="Q72" s="4"/>
     </row>
-    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A73" s="2"/>
       <c r="B73" s="3"/>
       <c r="C73" s="3"/>
@@ -2491,7 +2511,7 @@
       <c r="P73" s="5"/>
       <c r="Q73" s="4"/>
     </row>
-    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A74" s="2"/>
       <c r="B74" s="3"/>
       <c r="C74" s="3"/>
@@ -2510,7 +2530,7 @@
       <c r="P74" s="5"/>
       <c r="Q74" s="4"/>
     </row>
-    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A75" s="2"/>
       <c r="B75" s="3"/>
       <c r="C75" s="3"/>
@@ -2529,7 +2549,7 @@
       <c r="P75" s="5"/>
       <c r="Q75" s="4"/>
     </row>
-    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A76" s="2"/>
       <c r="B76" s="3"/>
       <c r="C76" s="3"/>
@@ -2548,7 +2568,7 @@
       <c r="P76" s="5"/>
       <c r="Q76" s="4"/>
     </row>
-    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A77" s="2"/>
       <c r="B77" s="3"/>
       <c r="C77" s="3"/>
@@ -2567,7 +2587,7 @@
       <c r="P77" s="5"/>
       <c r="Q77" s="4"/>
     </row>
-    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A78" s="2"/>
       <c r="B78" s="3"/>
       <c r="C78" s="3"/>
@@ -2586,7 +2606,7 @@
       <c r="P78" s="5"/>
       <c r="Q78" s="4"/>
     </row>
-    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A79" s="2"/>
       <c r="B79" s="3"/>
       <c r="C79" s="3"/>
@@ -2605,7 +2625,7 @@
       <c r="P79" s="5"/>
       <c r="Q79" s="4"/>
     </row>
-    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A80" s="2"/>
       <c r="B80" s="3"/>
       <c r="C80" s="3"/>
@@ -2624,7 +2644,7 @@
       <c r="P80" s="5"/>
       <c r="Q80" s="4"/>
     </row>
-    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A81" s="2"/>
       <c r="B81" s="3"/>
       <c r="C81" s="3"/>
@@ -2643,7 +2663,7 @@
       <c r="P81" s="5"/>
       <c r="Q81" s="4"/>
     </row>
-    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A82" s="2"/>
       <c r="B82" s="3"/>
       <c r="C82" s="3"/>
@@ -2662,7 +2682,7 @@
       <c r="P82" s="5"/>
       <c r="Q82" s="4"/>
     </row>
-    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A83" s="2"/>
       <c r="B83" s="3"/>
       <c r="C83" s="3"/>
@@ -2681,7 +2701,7 @@
       <c r="P83" s="5"/>
       <c r="Q83" s="4"/>
     </row>
-    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A84" s="2"/>
       <c r="B84" s="3"/>
       <c r="C84" s="3"/>
@@ -2700,7 +2720,7 @@
       <c r="P84" s="5"/>
       <c r="Q84" s="4"/>
     </row>
-    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A85" s="2"/>
       <c r="B85" s="3"/>
       <c r="C85" s="3"/>
@@ -2719,7 +2739,7 @@
       <c r="P85" s="5"/>
       <c r="Q85" s="4"/>
     </row>
-    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A86" s="2"/>
       <c r="B86" s="3"/>
       <c r="C86" s="3"/>
@@ -2738,7 +2758,7 @@
       <c r="P86" s="5"/>
       <c r="Q86" s="4"/>
     </row>
-    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A87" s="2"/>
       <c r="B87" s="3"/>
       <c r="C87" s="3"/>
@@ -2757,7 +2777,7 @@
       <c r="P87" s="5"/>
       <c r="Q87" s="4"/>
     </row>
-    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A88" s="2"/>
       <c r="B88" s="3"/>
       <c r="C88" s="3"/>
@@ -2776,7 +2796,7 @@
       <c r="P88" s="5"/>
       <c r="Q88" s="4"/>
     </row>
-    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A89" s="2"/>
       <c r="B89" s="3"/>
       <c r="C89" s="3"/>
@@ -2795,7 +2815,7 @@
       <c r="P89" s="5"/>
       <c r="Q89" s="4"/>
     </row>
-    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A90" s="2"/>
       <c r="B90" s="3"/>
       <c r="C90" s="3"/>
@@ -2814,7 +2834,7 @@
       <c r="P90" s="5"/>
       <c r="Q90" s="4"/>
     </row>
-    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A91" s="2"/>
       <c r="B91" s="3"/>
       <c r="C91" s="3"/>
@@ -2833,7 +2853,7 @@
       <c r="P91" s="5"/>
       <c r="Q91" s="4"/>
     </row>
-    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A92" s="2"/>
       <c r="B92" s="3"/>
       <c r="C92" s="3"/>
@@ -2852,7 +2872,7 @@
       <c r="P92" s="5"/>
       <c r="Q92" s="4"/>
     </row>
-    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A93" s="2"/>
       <c r="B93" s="3"/>
       <c r="C93" s="3"/>
@@ -2871,7 +2891,7 @@
       <c r="P93" s="5"/>
       <c r="Q93" s="4"/>
     </row>
-    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A94" s="2"/>
       <c r="B94" s="3"/>
       <c r="C94" s="3"/>
@@ -2890,7 +2910,7 @@
       <c r="P94" s="5"/>
       <c r="Q94" s="4"/>
     </row>
-    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A95" s="2"/>
       <c r="B95" s="3"/>
       <c r="C95" s="3"/>
@@ -2909,7 +2929,7 @@
       <c r="P95" s="5"/>
       <c r="Q95" s="4"/>
     </row>
-    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A96" s="2"/>
       <c r="B96" s="3"/>
       <c r="C96" s="3"/>
@@ -2928,7 +2948,7 @@
       <c r="P96" s="5"/>
       <c r="Q96" s="4"/>
     </row>
-    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A97" s="2"/>
       <c r="B97" s="3"/>
       <c r="C97" s="3"/>
@@ -2947,7 +2967,7 @@
       <c r="P97" s="5"/>
       <c r="Q97" s="4"/>
     </row>
-    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A98" s="2"/>
       <c r="B98" s="3"/>
       <c r="C98" s="3"/>
@@ -2966,7 +2986,7 @@
       <c r="P98" s="5"/>
       <c r="Q98" s="4"/>
     </row>
-    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="2"/>
       <c r="B99" s="3"/>
       <c r="C99" s="3"/>
@@ -2985,7 +3005,7 @@
       <c r="P99" s="5"/>
       <c r="Q99" s="4"/>
     </row>
-    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A100" s="2"/>
       <c r="B100" s="3"/>
       <c r="C100" s="3"/>
@@ -3004,7 +3024,7 @@
       <c r="P100" s="5"/>
       <c r="Q100" s="4"/>
     </row>
-    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A101" s="2"/>
       <c r="B101" s="3"/>
       <c r="C101" s="3"/>
@@ -3023,7 +3043,7 @@
       <c r="P101" s="5"/>
       <c r="Q101" s="4"/>
     </row>
-    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A102" s="2"/>
       <c r="B102" s="3"/>
       <c r="C102" s="3"/>
@@ -3042,7 +3062,7 @@
       <c r="P102" s="5"/>
       <c r="Q102" s="4"/>
     </row>
-    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A103" s="2"/>
       <c r="B103" s="3"/>
       <c r="C103" s="3"/>
@@ -3061,7 +3081,7 @@
       <c r="P103" s="5"/>
       <c r="Q103" s="4"/>
     </row>
-    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A104" s="2"/>
       <c r="B104" s="3"/>
       <c r="C104" s="3"/>
@@ -3080,7 +3100,7 @@
       <c r="P104" s="5"/>
       <c r="Q104" s="4"/>
     </row>
-    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A105" s="2"/>
       <c r="B105" s="3"/>
       <c r="C105" s="3"/>
@@ -3099,7 +3119,7 @@
       <c r="P105" s="5"/>
       <c r="Q105" s="4"/>
     </row>
-    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A106" s="2"/>
       <c r="B106" s="3"/>
       <c r="C106" s="3"/>
@@ -3118,7 +3138,7 @@
       <c r="P106" s="5"/>
       <c r="Q106" s="4"/>
     </row>
-    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="2"/>
       <c r="B107" s="3"/>
       <c r="C107" s="3"/>
@@ -3137,7 +3157,7 @@
       <c r="P107" s="5"/>
       <c r="Q107" s="4"/>
     </row>
-    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="2"/>
       <c r="B108" s="3"/>
       <c r="C108" s="3"/>
@@ -3156,7 +3176,7 @@
       <c r="P108" s="5"/>
       <c r="Q108" s="4"/>
     </row>
-    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A109" s="2"/>
       <c r="B109" s="3"/>
       <c r="C109" s="3"/>
@@ -3175,7 +3195,7 @@
       <c r="P109" s="5"/>
       <c r="Q109" s="4"/>
     </row>
-    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A110" s="2"/>
       <c r="B110" s="3"/>
       <c r="C110" s="3"/>
@@ -3194,7 +3214,7 @@
       <c r="P110" s="5"/>
       <c r="Q110" s="4"/>
     </row>
-    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A111" s="2"/>
       <c r="B111" s="3"/>
       <c r="C111" s="3"/>
@@ -3213,7 +3233,7 @@
       <c r="P111" s="5"/>
       <c r="Q111" s="4"/>
     </row>
-    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A112" s="2"/>
       <c r="B112" s="3"/>
       <c r="C112" s="3"/>
@@ -3232,7 +3252,7 @@
       <c r="P112" s="5"/>
       <c r="Q112" s="4"/>
     </row>
-    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A113" s="2"/>
       <c r="B113" s="3"/>
       <c r="C113" s="3"/>
@@ -3251,7 +3271,7 @@
       <c r="P113" s="5"/>
       <c r="Q113" s="4"/>
     </row>
-    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A114" s="2"/>
       <c r="B114" s="3"/>
       <c r="C114" s="3"/>
@@ -3270,7 +3290,7 @@
       <c r="P114" s="5"/>
       <c r="Q114" s="4"/>
     </row>
-    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A115" s="2"/>
       <c r="B115" s="3"/>
       <c r="C115" s="3"/>
@@ -3289,7 +3309,7 @@
       <c r="P115" s="5"/>
       <c r="Q115" s="4"/>
     </row>
-    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A116" s="2"/>
       <c r="B116" s="3"/>
       <c r="C116" s="3"/>
@@ -3308,7 +3328,7 @@
       <c r="P116" s="5"/>
       <c r="Q116" s="4"/>
     </row>
-    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A117" s="2"/>
       <c r="B117" s="3"/>
       <c r="C117" s="3"/>
@@ -3327,7 +3347,7 @@
       <c r="P117" s="5"/>
       <c r="Q117" s="4"/>
     </row>
-    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A118" s="2"/>
       <c r="B118" s="3"/>
       <c r="C118" s="3"/>
@@ -3346,7 +3366,7 @@
       <c r="P118" s="5"/>
       <c r="Q118" s="4"/>
     </row>
-    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A119" s="2"/>
       <c r="B119" s="3"/>
       <c r="C119" s="3"/>
@@ -3365,7 +3385,7 @@
       <c r="P119" s="5"/>
       <c r="Q119" s="4"/>
     </row>
-    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A120" s="2"/>
       <c r="B120" s="3"/>
       <c r="C120" s="3"/>
@@ -3384,7 +3404,7 @@
       <c r="P120" s="5"/>
       <c r="Q120" s="4"/>
     </row>
-    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A121" s="2"/>
       <c r="B121" s="3"/>
       <c r="C121" s="3"/>
@@ -3403,7 +3423,7 @@
       <c r="P121" s="5"/>
       <c r="Q121" s="4"/>
     </row>
-    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A122" s="2"/>
       <c r="B122" s="3"/>
       <c r="C122" s="3"/>
@@ -3422,7 +3442,7 @@
       <c r="P122" s="5"/>
       <c r="Q122" s="4"/>
     </row>
-    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="2"/>
       <c r="B123" s="3"/>
       <c r="C123" s="3"/>
@@ -3441,7 +3461,7 @@
       <c r="P123" s="5"/>
       <c r="Q123" s="4"/>
     </row>
-    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="2"/>
       <c r="B124" s="3"/>
       <c r="C124" s="3"/>
@@ -3460,7 +3480,7 @@
       <c r="P124" s="5"/>
       <c r="Q124" s="4"/>
     </row>
-    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A125" s="2"/>
       <c r="B125" s="3"/>
       <c r="C125" s="3"/>
@@ -3479,7 +3499,7 @@
       <c r="P125" s="5"/>
       <c r="Q125" s="4"/>
     </row>
-    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A126" s="2"/>
       <c r="B126" s="3"/>
       <c r="C126" s="3"/>
@@ -3498,7 +3518,7 @@
       <c r="P126" s="5"/>
       <c r="Q126" s="4"/>
     </row>
-    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A127" s="2"/>
       <c r="B127" s="3"/>
       <c r="C127" s="3"/>
@@ -3517,7 +3537,7 @@
       <c r="P127" s="5"/>
       <c r="Q127" s="4"/>
     </row>
-    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A128" s="2"/>
       <c r="B128" s="3"/>
       <c r="C128" s="3"/>
@@ -3536,7 +3556,7 @@
       <c r="P128" s="5"/>
       <c r="Q128" s="4"/>
     </row>
-    <row r="129" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A129" s="2"/>
       <c r="B129" s="3"/>
       <c r="C129" s="3"/>
@@ -3555,7 +3575,7 @@
       <c r="P129" s="5"/>
       <c r="Q129" s="4"/>
     </row>
-    <row r="130" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A130" s="2"/>
       <c r="B130" s="3"/>
       <c r="C130" s="3"/>
@@ -3574,7 +3594,7 @@
       <c r="P130" s="5"/>
       <c r="Q130" s="4"/>
     </row>
-    <row r="131" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A131" s="2"/>
       <c r="B131" s="3"/>
       <c r="C131" s="3"/>
@@ -3593,7 +3613,7 @@
       <c r="P131" s="5"/>
       <c r="Q131" s="4"/>
     </row>
-    <row r="132" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A132" s="2"/>
       <c r="B132" s="3"/>
       <c r="C132" s="3"/>
@@ -3612,7 +3632,7 @@
       <c r="P132" s="5"/>
       <c r="Q132" s="4"/>
     </row>
-    <row r="133" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A133" s="2"/>
       <c r="B133" s="3"/>
       <c r="C133" s="3"/>
@@ -3631,7 +3651,7 @@
       <c r="P133" s="5"/>
       <c r="Q133" s="4"/>
     </row>
-    <row r="134" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A134" s="2"/>
       <c r="B134" s="3"/>
       <c r="C134" s="3"/>
@@ -3650,7 +3670,7 @@
       <c r="P134" s="5"/>
       <c r="Q134" s="4"/>
     </row>
-    <row r="135" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A135" s="2"/>
       <c r="B135" s="3"/>
       <c r="C135" s="3"/>
@@ -3669,7 +3689,7 @@
       <c r="P135" s="5"/>
       <c r="Q135" s="4"/>
     </row>
-    <row r="136" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A136" s="2"/>
       <c r="B136" s="3"/>
       <c r="C136" s="3"/>
@@ -3688,7 +3708,7 @@
       <c r="P136" s="5"/>
       <c r="Q136" s="4"/>
     </row>
-    <row r="137" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A137" s="2"/>
       <c r="B137" s="3"/>
       <c r="C137" s="3"/>
@@ -3707,7 +3727,7 @@
       <c r="P137" s="5"/>
       <c r="Q137" s="4"/>
     </row>
-    <row r="138" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A138" s="2"/>
       <c r="B138" s="3"/>
       <c r="C138" s="3"/>
@@ -3726,7 +3746,7 @@
       <c r="P138" s="5"/>
       <c r="Q138" s="4"/>
     </row>
-    <row r="139" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A139" s="2"/>
       <c r="B139" s="3"/>
       <c r="C139" s="3"/>
@@ -3745,7 +3765,7 @@
       <c r="P139" s="5"/>
       <c r="Q139" s="4"/>
     </row>
-    <row r="140" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A140" s="2"/>
       <c r="B140" s="3"/>
       <c r="C140" s="3"/>
@@ -3764,7 +3784,7 @@
       <c r="P140" s="5"/>
       <c r="Q140" s="4"/>
     </row>
-    <row r="141" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A141" s="2"/>
       <c r="B141" s="3"/>
       <c r="C141" s="3"/>
@@ -3783,7 +3803,7 @@
       <c r="P141" s="5"/>
       <c r="Q141" s="4"/>
     </row>
-    <row r="142" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A142" s="2"/>
       <c r="B142" s="3"/>
       <c r="C142" s="3"/>
@@ -3802,7 +3822,7 @@
       <c r="P142" s="5"/>
       <c r="Q142" s="4"/>
     </row>
-    <row r="143" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A143" s="2"/>
       <c r="B143" s="3"/>
       <c r="C143" s="3"/>
@@ -3821,7 +3841,7 @@
       <c r="P143" s="5"/>
       <c r="Q143" s="4"/>
     </row>
-    <row r="144" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A144" s="2"/>
       <c r="B144" s="3"/>
       <c r="C144" s="3"/>
@@ -3840,7 +3860,7 @@
       <c r="P144" s="5"/>
       <c r="Q144" s="4"/>
     </row>
-    <row r="145" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A145" s="2"/>
       <c r="B145" s="3"/>
       <c r="C145" s="3"/>
@@ -3859,7 +3879,7 @@
       <c r="P145" s="5"/>
       <c r="Q145" s="4"/>
     </row>
-    <row r="146" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A146" s="2"/>
       <c r="B146" s="3"/>
       <c r="C146" s="3"/>
@@ -3878,7 +3898,7 @@
       <c r="P146" s="5"/>
       <c r="Q146" s="4"/>
     </row>
-    <row r="147" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A147" s="2"/>
       <c r="B147" s="3"/>
       <c r="C147" s="3"/>
@@ -3897,7 +3917,7 @@
       <c r="P147" s="5"/>
       <c r="Q147" s="4"/>
     </row>
-    <row r="148" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A148" s="2"/>
       <c r="B148" s="3"/>
       <c r="C148" s="3"/>
@@ -3916,7 +3936,7 @@
       <c r="P148" s="5"/>
       <c r="Q148" s="4"/>
     </row>
-    <row r="149" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="2"/>
       <c r="B149" s="3"/>
       <c r="C149" s="3"/>
@@ -3935,7 +3955,7 @@
       <c r="P149" s="5"/>
       <c r="Q149" s="4"/>
     </row>
-    <row r="150" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A150" s="2"/>
       <c r="B150" s="3"/>
       <c r="C150" s="3"/>
@@ -3954,7 +3974,7 @@
       <c r="P150" s="5"/>
       <c r="Q150" s="4"/>
     </row>
-    <row r="151" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A151" s="2"/>
       <c r="B151" s="3"/>
       <c r="C151" s="3"/>
@@ -3973,7 +3993,7 @@
       <c r="P151" s="5"/>
       <c r="Q151" s="4"/>
     </row>
-    <row r="152" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A152" s="2"/>
       <c r="B152" s="3"/>
       <c r="C152" s="3"/>
@@ -3992,7 +4012,7 @@
       <c r="P152" s="5"/>
       <c r="Q152" s="4"/>
     </row>
-    <row r="153" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A153" s="2"/>
       <c r="B153" s="3"/>
       <c r="C153" s="3"/>
@@ -4011,7 +4031,7 @@
       <c r="P153" s="5"/>
       <c r="Q153" s="4"/>
     </row>
-    <row r="154" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A154" s="2"/>
       <c r="B154" s="3"/>
       <c r="C154" s="3"/>
@@ -4030,7 +4050,7 @@
       <c r="P154" s="5"/>
       <c r="Q154" s="4"/>
     </row>
-    <row r="155" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A155" s="2"/>
       <c r="B155" s="3"/>
       <c r="C155" s="3"/>
@@ -4049,7 +4069,7 @@
       <c r="P155" s="5"/>
       <c r="Q155" s="4"/>
     </row>
-    <row r="156" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A156" s="2"/>
       <c r="B156" s="3"/>
       <c r="C156" s="3"/>
@@ -4068,7 +4088,7 @@
       <c r="P156" s="5"/>
       <c r="Q156" s="4"/>
     </row>
-    <row r="157" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="2"/>
       <c r="B157" s="3"/>
       <c r="C157" s="3"/>
@@ -4087,7 +4107,7 @@
       <c r="P157" s="5"/>
       <c r="Q157" s="4"/>
     </row>
-    <row r="158" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A158" s="2"/>
       <c r="B158" s="3"/>
       <c r="C158" s="3"/>
@@ -4106,7 +4126,7 @@
       <c r="P158" s="5"/>
       <c r="Q158" s="4"/>
     </row>
-    <row r="159" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A159" s="2"/>
       <c r="B159" s="3"/>
       <c r="C159" s="3"/>
@@ -4125,7 +4145,7 @@
       <c r="P159" s="5"/>
       <c r="Q159" s="4"/>
     </row>
-    <row r="160" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A160" s="2"/>
       <c r="B160" s="3"/>
       <c r="C160" s="3"/>
@@ -4144,7 +4164,7 @@
       <c r="P160" s="5"/>
       <c r="Q160" s="4"/>
     </row>
-    <row r="161" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A161" s="2"/>
       <c r="B161" s="3"/>
       <c r="C161" s="3"/>
@@ -4163,7 +4183,7 @@
       <c r="P161" s="5"/>
       <c r="Q161" s="4"/>
     </row>
-    <row r="162" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A162" s="2"/>
       <c r="B162" s="3"/>
       <c r="C162" s="3"/>
@@ -4182,7 +4202,7 @@
       <c r="P162" s="5"/>
       <c r="Q162" s="4"/>
     </row>
-    <row r="163" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A163" s="2"/>
       <c r="B163" s="3"/>
       <c r="C163" s="3"/>
@@ -4201,7 +4221,7 @@
       <c r="P163" s="5"/>
       <c r="Q163" s="4"/>
     </row>
-    <row r="164" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A164" s="2"/>
       <c r="B164" s="3"/>
       <c r="C164" s="3"/>
@@ -4220,7 +4240,7 @@
       <c r="P164" s="5"/>
       <c r="Q164" s="4"/>
     </row>
-    <row r="165" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A165" s="2"/>
       <c r="B165" s="3"/>
       <c r="C165" s="3"/>
@@ -4239,7 +4259,7 @@
       <c r="P165" s="5"/>
       <c r="Q165" s="4"/>
     </row>
-    <row r="166" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A166" s="2"/>
       <c r="B166" s="3"/>
       <c r="C166" s="3"/>
@@ -4258,7 +4278,7 @@
       <c r="P166" s="5"/>
       <c r="Q166" s="4"/>
     </row>
-    <row r="167" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A167" s="2"/>
       <c r="B167" s="3"/>
       <c r="C167" s="3"/>
@@ -4277,7 +4297,7 @@
       <c r="P167" s="5"/>
       <c r="Q167" s="4"/>
     </row>
-    <row r="168" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A168" s="2"/>
       <c r="B168" s="3"/>
       <c r="C168" s="3"/>
@@ -4296,7 +4316,7 @@
       <c r="P168" s="5"/>
       <c r="Q168" s="4"/>
     </row>
-    <row r="169" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A169" s="2"/>
       <c r="B169" s="3"/>
       <c r="C169" s="3"/>
@@ -4315,7 +4335,7 @@
       <c r="P169" s="5"/>
       <c r="Q169" s="4"/>
     </row>
-    <row r="170" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A170" s="2"/>
       <c r="B170" s="3"/>
       <c r="C170" s="3"/>
@@ -4334,7 +4354,7 @@
       <c r="P170" s="5"/>
       <c r="Q170" s="4"/>
     </row>
-    <row r="171" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A171" s="2"/>
       <c r="B171" s="3"/>
       <c r="C171" s="3"/>
@@ -4353,7 +4373,7 @@
       <c r="P171" s="5"/>
       <c r="Q171" s="4"/>
     </row>
-    <row r="172" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A172" s="2"/>
       <c r="B172" s="3"/>
       <c r="C172" s="3"/>
@@ -4372,7 +4392,7 @@
       <c r="P172" s="5"/>
       <c r="Q172" s="4"/>
     </row>
-    <row r="173" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A173" s="2"/>
       <c r="B173" s="3"/>
       <c r="C173" s="3"/>
@@ -4391,7 +4411,7 @@
       <c r="P173" s="5"/>
       <c r="Q173" s="4"/>
     </row>
-    <row r="174" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A174" s="2"/>
       <c r="B174" s="3"/>
       <c r="C174" s="3"/>
@@ -4410,7 +4430,7 @@
       <c r="P174" s="5"/>
       <c r="Q174" s="4"/>
     </row>
-    <row r="175" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A175" s="2"/>
       <c r="B175" s="3"/>
       <c r="C175" s="3"/>
@@ -4429,7 +4449,7 @@
       <c r="P175" s="5"/>
       <c r="Q175" s="4"/>
     </row>
-    <row r="176" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A176" s="2"/>
       <c r="B176" s="3"/>
       <c r="C176" s="3"/>
@@ -4448,7 +4468,7 @@
       <c r="P176" s="5"/>
       <c r="Q176" s="4"/>
     </row>
-    <row r="177" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A177" s="2"/>
       <c r="B177" s="3"/>
       <c r="C177" s="3"/>
@@ -4467,7 +4487,7 @@
       <c r="P177" s="5"/>
       <c r="Q177" s="4"/>
     </row>
-    <row r="178" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A178" s="2"/>
       <c r="B178" s="3"/>
       <c r="C178" s="3"/>
@@ -4486,7 +4506,7 @@
       <c r="P178" s="5"/>
       <c r="Q178" s="4"/>
     </row>
-    <row r="179" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A179" s="2"/>
       <c r="B179" s="3"/>
       <c r="C179" s="3"/>
@@ -4505,7 +4525,7 @@
       <c r="P179" s="5"/>
       <c r="Q179" s="4"/>
     </row>
-    <row r="180" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A180" s="2"/>
       <c r="B180" s="3"/>
       <c r="C180" s="3"/>
@@ -4524,7 +4544,7 @@
       <c r="P180" s="5"/>
       <c r="Q180" s="4"/>
     </row>
-    <row r="181" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A181" s="2"/>
       <c r="B181" s="3"/>
       <c r="C181" s="3"/>
@@ -4543,7 +4563,7 @@
       <c r="P181" s="5"/>
       <c r="Q181" s="4"/>
     </row>
-    <row r="182" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A182" s="2"/>
       <c r="B182" s="3"/>
       <c r="C182" s="3"/>
@@ -4562,7 +4582,7 @@
       <c r="P182" s="5"/>
       <c r="Q182" s="4"/>
     </row>
-    <row r="183" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A183" s="2"/>
       <c r="B183" s="3"/>
       <c r="C183" s="3"/>
@@ -4581,7 +4601,7 @@
       <c r="P183" s="5"/>
       <c r="Q183" s="4"/>
     </row>
-    <row r="184" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A184" s="2"/>
       <c r="B184" s="3"/>
       <c r="C184" s="3"/>
@@ -4600,7 +4620,7 @@
       <c r="P184" s="5"/>
       <c r="Q184" s="4"/>
     </row>
-    <row r="185" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A185" s="2"/>
       <c r="B185" s="3"/>
       <c r="C185" s="3"/>
@@ -4619,7 +4639,7 @@
       <c r="P185" s="5"/>
       <c r="Q185" s="4"/>
     </row>
-    <row r="186" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A186" s="2"/>
       <c r="B186" s="3"/>
       <c r="C186" s="3"/>
@@ -4638,7 +4658,7 @@
       <c r="P186" s="5"/>
       <c r="Q186" s="4"/>
     </row>
-    <row r="187" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A187" s="2"/>
       <c r="B187" s="3"/>
       <c r="C187" s="3"/>
@@ -4657,7 +4677,7 @@
       <c r="P187" s="5"/>
       <c r="Q187" s="4"/>
     </row>
-    <row r="188" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A188" s="2"/>
       <c r="B188" s="3"/>
       <c r="C188" s="3"/>
@@ -4676,7 +4696,7 @@
       <c r="P188" s="5"/>
       <c r="Q188" s="4"/>
     </row>
-    <row r="189" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A189" s="2"/>
       <c r="B189" s="3"/>
       <c r="C189" s="3"/>
@@ -4695,7 +4715,7 @@
       <c r="P189" s="5"/>
       <c r="Q189" s="4"/>
     </row>
-    <row r="190" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A190" s="2"/>
       <c r="B190" s="3"/>
       <c r="C190" s="3"/>
@@ -4714,7 +4734,7 @@
       <c r="P190" s="5"/>
       <c r="Q190" s="4"/>
     </row>
-    <row r="191" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A191" s="2"/>
       <c r="B191" s="3"/>
       <c r="C191" s="3"/>
@@ -4733,7 +4753,7 @@
       <c r="P191" s="5"/>
       <c r="Q191" s="4"/>
     </row>
-    <row r="192" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A192" s="2"/>
       <c r="B192" s="3"/>
       <c r="C192" s="3"/>
@@ -4752,7 +4772,7 @@
       <c r="P192" s="5"/>
       <c r="Q192" s="4"/>
     </row>
-    <row r="193" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A193" s="2"/>
       <c r="B193" s="3"/>
       <c r="C193" s="3"/>
@@ -4771,7 +4791,7 @@
       <c r="P193" s="5"/>
       <c r="Q193" s="4"/>
     </row>
-    <row r="194" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A194" s="2"/>
       <c r="B194" s="3"/>
       <c r="C194" s="3"/>
@@ -4790,7 +4810,7 @@
       <c r="P194" s="5"/>
       <c r="Q194" s="4"/>
     </row>
-    <row r="195" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A195" s="2"/>
       <c r="B195" s="3"/>
       <c r="C195" s="3"/>
@@ -4809,7 +4829,7 @@
       <c r="P195" s="5"/>
       <c r="Q195" s="4"/>
     </row>
-    <row r="196" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A196" s="2"/>
       <c r="B196" s="3"/>
       <c r="C196" s="3"/>
@@ -4828,7 +4848,7 @@
       <c r="P196" s="5"/>
       <c r="Q196" s="4"/>
     </row>
-    <row r="197" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A197" s="2"/>
       <c r="B197" s="3"/>
       <c r="C197" s="3"/>
@@ -4847,7 +4867,7 @@
       <c r="P197" s="5"/>
       <c r="Q197" s="4"/>
     </row>
-    <row r="198" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A198" s="6"/>
       <c r="B198" s="4"/>
       <c r="C198" s="4"/>
@@ -4866,7 +4886,7 @@
       <c r="P198" s="5"/>
       <c r="Q198" s="4"/>
     </row>
-    <row r="199" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A199" s="6"/>
       <c r="B199" s="4"/>
       <c r="C199" s="4"/>
@@ -4885,7 +4905,7 @@
       <c r="P199" s="5"/>
       <c r="Q199" s="4"/>
     </row>
-    <row r="200" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A200" s="6"/>
       <c r="B200" s="4"/>
       <c r="C200" s="4"/>
@@ -4904,7 +4924,7 @@
       <c r="P200" s="5"/>
       <c r="Q200" s="4"/>
     </row>
-    <row r="201" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A201" s="6"/>
       <c r="B201" s="4"/>
       <c r="C201" s="4"/>
@@ -4923,7 +4943,7 @@
       <c r="P201" s="5"/>
       <c r="Q201" s="4"/>
     </row>
-    <row r="202" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A202" s="6"/>
       <c r="B202" s="4"/>
       <c r="C202" s="4"/>
@@ -4942,7 +4962,7 @@
       <c r="P202" s="5"/>
       <c r="Q202" s="4"/>
     </row>
-    <row r="203" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A203" s="6"/>
       <c r="B203" s="4"/>
       <c r="C203" s="4"/>
@@ -4961,7 +4981,7 @@
       <c r="P203" s="5"/>
       <c r="Q203" s="4"/>
     </row>
-    <row r="204" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A204" s="6"/>
       <c r="B204" s="4"/>
       <c r="C204" s="4"/>
@@ -4980,7 +5000,7 @@
       <c r="P204" s="5"/>
       <c r="Q204" s="4"/>
     </row>
-    <row r="205" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A205" s="6"/>
       <c r="B205" s="4"/>
       <c r="C205" s="4"/>
@@ -4999,7 +5019,7 @@
       <c r="P205" s="5"/>
       <c r="Q205" s="4"/>
     </row>
-    <row r="206" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A206" s="6"/>
       <c r="B206" s="4"/>
       <c r="C206" s="4"/>
@@ -5018,7 +5038,7 @@
       <c r="P206" s="5"/>
       <c r="Q206" s="4"/>
     </row>
-    <row r="207" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A207" s="6"/>
       <c r="B207" s="4"/>
       <c r="C207" s="4"/>
@@ -5037,7 +5057,7 @@
       <c r="P207" s="5"/>
       <c r="Q207" s="4"/>
     </row>
-    <row r="208" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A208" s="6"/>
       <c r="B208" s="4"/>
       <c r="C208" s="4"/>
@@ -5056,7 +5076,7 @@
       <c r="P208" s="5"/>
       <c r="Q208" s="4"/>
     </row>
-    <row r="209" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A209" s="6"/>
       <c r="B209" s="4"/>
       <c r="C209" s="4"/>
@@ -5075,7 +5095,7 @@
       <c r="P209" s="5"/>
       <c r="Q209" s="4"/>
     </row>
-    <row r="210" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A210" s="6"/>
       <c r="B210" s="4"/>
       <c r="C210" s="4"/>
@@ -5094,7 +5114,7 @@
       <c r="P210" s="5"/>
       <c r="Q210" s="4"/>
     </row>
-    <row r="211" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A211" s="6"/>
       <c r="B211" s="4"/>
       <c r="C211" s="4"/>
@@ -5113,7 +5133,7 @@
       <c r="P211" s="5"/>
       <c r="Q211" s="4"/>
     </row>
-    <row r="212" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A212" s="6"/>
       <c r="B212" s="4"/>
       <c r="C212" s="4"/>
@@ -5132,7 +5152,7 @@
       <c r="P212" s="5"/>
       <c r="Q212" s="4"/>
     </row>
-    <row r="213" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A213" s="6"/>
       <c r="B213" s="4"/>
       <c r="C213" s="4"/>
@@ -5151,7 +5171,7 @@
       <c r="P213" s="5"/>
       <c r="Q213" s="4"/>
     </row>
-    <row r="214" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A214" s="6"/>
       <c r="B214" s="4"/>
       <c r="C214" s="4"/>
@@ -5170,7 +5190,7 @@
       <c r="P214" s="5"/>
       <c r="Q214" s="4"/>
     </row>
-    <row r="215" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A215" s="6"/>
       <c r="B215" s="4"/>
       <c r="C215" s="4"/>
@@ -5189,7 +5209,7 @@
       <c r="P215" s="5"/>
       <c r="Q215" s="4"/>
     </row>
-    <row r="216" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A216" s="6"/>
       <c r="B216" s="4"/>
       <c r="C216" s="4"/>
@@ -5208,7 +5228,7 @@
       <c r="P216" s="5"/>
       <c r="Q216" s="4"/>
     </row>
-    <row r="217" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A217" s="6"/>
       <c r="B217" s="4"/>
       <c r="C217" s="4"/>
@@ -5227,7 +5247,7 @@
       <c r="P217" s="5"/>
       <c r="Q217" s="4"/>
     </row>
-    <row r="218" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A218" s="6"/>
       <c r="B218" s="4"/>
       <c r="C218" s="4"/>
@@ -5246,7 +5266,7 @@
       <c r="P218" s="5"/>
       <c r="Q218" s="4"/>
     </row>
-    <row r="219" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A219" s="6"/>
       <c r="B219" s="4"/>
       <c r="C219" s="4"/>
@@ -5265,7 +5285,7 @@
       <c r="P219" s="5"/>
       <c r="Q219" s="4"/>
     </row>
-    <row r="220" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A220" s="6"/>
       <c r="B220" s="4"/>
       <c r="C220" s="4"/>
@@ -5284,7 +5304,7 @@
       <c r="P220" s="4"/>
       <c r="Q220" s="4"/>
     </row>
-    <row r="221" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A221" s="6"/>
       <c r="B221" s="4"/>
       <c r="C221" s="4"/>
@@ -5303,7 +5323,7 @@
       <c r="P221" s="4"/>
       <c r="Q221" s="4"/>
     </row>
-    <row r="222" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A222" s="6"/>
       <c r="B222" s="4"/>
       <c r="C222" s="4"/>
@@ -5322,7 +5342,7 @@
       <c r="P222" s="4"/>
       <c r="Q222" s="4"/>
     </row>
-    <row r="223" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A223" s="6"/>
       <c r="B223" s="4"/>
       <c r="C223" s="4"/>
@@ -5341,7 +5361,7 @@
       <c r="P223" s="4"/>
       <c r="Q223" s="4"/>
     </row>
-    <row r="224" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A224" s="6"/>
       <c r="B224" s="4"/>
       <c r="C224" s="4"/>
@@ -5360,7 +5380,7 @@
       <c r="P224" s="4"/>
       <c r="Q224" s="4"/>
     </row>
-    <row r="225" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A225" s="6"/>
       <c r="B225" s="4"/>
       <c r="C225" s="4"/>
@@ -5379,7 +5399,7 @@
       <c r="P225" s="4"/>
       <c r="Q225" s="4"/>
     </row>
-    <row r="226" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A226" s="6"/>
       <c r="B226" s="4"/>
       <c r="C226" s="4"/>
@@ -5398,7 +5418,7 @@
       <c r="P226" s="4"/>
       <c r="Q226" s="4"/>
     </row>
-    <row r="227" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A227" s="6"/>
       <c r="B227" s="4"/>
       <c r="C227" s="4"/>
@@ -5417,7 +5437,7 @@
       <c r="P227" s="4"/>
       <c r="Q227" s="4"/>
     </row>
-    <row r="228" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A228" s="6"/>
       <c r="B228" s="4"/>
       <c r="C228" s="4"/>
@@ -5436,7 +5456,7 @@
       <c r="P228" s="4"/>
       <c r="Q228" s="4"/>
     </row>
-    <row r="229" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A229" s="6"/>
       <c r="B229" s="4"/>
       <c r="C229" s="4"/>
@@ -5455,7 +5475,7 @@
       <c r="P229" s="4"/>
       <c r="Q229" s="4"/>
     </row>
-    <row r="230" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A230" s="6"/>
       <c r="B230" s="4"/>
       <c r="C230" s="4"/>
@@ -5474,7 +5494,7 @@
       <c r="P230" s="4"/>
       <c r="Q230" s="4"/>
     </row>
-    <row r="231" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A231" s="6"/>
       <c r="B231" s="4"/>
       <c r="C231" s="4"/>
@@ -5493,7 +5513,7 @@
       <c r="P231" s="4"/>
       <c r="Q231" s="4"/>
     </row>
-    <row r="232" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A232" s="6"/>
       <c r="B232" s="4"/>
       <c r="C232" s="4"/>
@@ -5512,7 +5532,7 @@
       <c r="P232" s="4"/>
       <c r="Q232" s="4"/>
     </row>
-    <row r="233" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A233" s="6"/>
       <c r="B233" s="4"/>
       <c r="C233" s="4"/>
@@ -5531,7 +5551,7 @@
       <c r="P233" s="4"/>
       <c r="Q233" s="4"/>
     </row>
-    <row r="234" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A234" s="6"/>
       <c r="B234" s="4"/>
       <c r="C234" s="4"/>
@@ -5550,7 +5570,7 @@
       <c r="P234" s="4"/>
       <c r="Q234" s="4"/>
     </row>
-    <row r="235" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A235" s="6"/>
       <c r="B235" s="4"/>
       <c r="C235" s="4"/>
@@ -5569,7 +5589,7 @@
       <c r="P235" s="4"/>
       <c r="Q235" s="4"/>
     </row>
-    <row r="236" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A236" s="6"/>
       <c r="B236" s="4"/>
       <c r="C236" s="4"/>
@@ -5588,7 +5608,7 @@
       <c r="P236" s="4"/>
       <c r="Q236" s="4"/>
     </row>
-    <row r="237" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A237" s="6"/>
       <c r="B237" s="4"/>
       <c r="C237" s="4"/>
@@ -5607,7 +5627,7 @@
       <c r="P237" s="4"/>
       <c r="Q237" s="4"/>
     </row>
-    <row r="238" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A238" s="6"/>
       <c r="B238" s="4"/>
       <c r="C238" s="4"/>
@@ -5626,7 +5646,7 @@
       <c r="P238" s="4"/>
       <c r="Q238" s="4"/>
     </row>
-    <row r="239" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A239" s="6"/>
       <c r="B239" s="4"/>
       <c r="C239" s="4"/>
@@ -5645,7 +5665,7 @@
       <c r="P239" s="4"/>
       <c r="Q239" s="4"/>
     </row>
-    <row r="240" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A240" s="6"/>
       <c r="B240" s="4"/>
       <c r="C240" s="4"/>
@@ -5664,7 +5684,7 @@
       <c r="P240" s="4"/>
       <c r="Q240" s="4"/>
     </row>
-    <row r="241" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A241" s="6"/>
       <c r="B241" s="4"/>
       <c r="C241" s="4"/>
@@ -5683,7 +5703,7 @@
       <c r="P241" s="4"/>
       <c r="Q241" s="4"/>
     </row>
-    <row r="242" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A242" s="6"/>
       <c r="B242" s="4"/>
       <c r="C242" s="4"/>
@@ -5702,7 +5722,7 @@
       <c r="P242" s="4"/>
       <c r="Q242" s="4"/>
     </row>
-    <row r="243" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A243" s="6"/>
       <c r="B243" s="4"/>
       <c r="C243" s="4"/>
@@ -5721,7 +5741,7 @@
       <c r="P243" s="4"/>
       <c r="Q243" s="4"/>
     </row>
-    <row r="244" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A244" s="6"/>
       <c r="B244" s="4"/>
       <c r="C244" s="4"/>
@@ -5740,7 +5760,7 @@
       <c r="P244" s="4"/>
       <c r="Q244" s="4"/>
     </row>
-    <row r="245" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A245" s="6"/>
       <c r="B245" s="4"/>
       <c r="C245" s="4"/>
@@ -5759,7 +5779,7 @@
       <c r="P245" s="4"/>
       <c r="Q245" s="4"/>
     </row>
-    <row r="246" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A246" s="6"/>
       <c r="B246" s="4"/>
       <c r="C246" s="4"/>
@@ -5778,7 +5798,7 @@
       <c r="P246" s="4"/>
       <c r="Q246" s="4"/>
     </row>
-    <row r="247" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A247" s="6"/>
       <c r="B247" s="4"/>
       <c r="C247" s="4"/>
@@ -5797,7 +5817,7 @@
       <c r="P247" s="4"/>
       <c r="Q247" s="4"/>
     </row>
-    <row r="248" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A248" s="6"/>
       <c r="B248" s="4"/>
       <c r="C248" s="4"/>
@@ -5816,7 +5836,7 @@
       <c r="P248" s="4"/>
       <c r="Q248" s="4"/>
     </row>
-    <row r="249" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A249" s="6"/>
       <c r="B249" s="4"/>
       <c r="C249" s="4"/>
@@ -5835,7 +5855,7 @@
       <c r="P249" s="4"/>
       <c r="Q249" s="4"/>
     </row>
-    <row r="250" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A250" s="6"/>
       <c r="B250" s="4"/>
       <c r="C250" s="4"/>
@@ -5854,7 +5874,7 @@
       <c r="P250" s="4"/>
       <c r="Q250" s="4"/>
     </row>
-    <row r="251" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A251" s="6"/>
       <c r="B251" s="4"/>
       <c r="C251" s="4"/>
@@ -5873,7 +5893,7 @@
       <c r="P251" s="4"/>
       <c r="Q251" s="4"/>
     </row>
-    <row r="252" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A252" s="6"/>
       <c r="B252" s="4"/>
       <c r="C252" s="4"/>
@@ -5892,7 +5912,7 @@
       <c r="P252" s="4"/>
       <c r="Q252" s="4"/>
     </row>
-    <row r="253" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A253" s="6"/>
       <c r="B253" s="4"/>
       <c r="C253" s="4"/>
@@ -5911,7 +5931,7 @@
       <c r="P253" s="4"/>
       <c r="Q253" s="4"/>
     </row>
-    <row r="254" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A254" s="6"/>
       <c r="B254" s="4"/>
       <c r="C254" s="4"/>
@@ -5930,7 +5950,7 @@
       <c r="P254" s="4"/>
       <c r="Q254" s="4"/>
     </row>
-    <row r="255" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A255" s="6"/>
       <c r="B255" s="4"/>
       <c r="C255" s="4"/>
@@ -5949,7 +5969,7 @@
       <c r="P255" s="4"/>
       <c r="Q255" s="4"/>
     </row>
-    <row r="256" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A256" s="6"/>
       <c r="B256" s="4"/>
       <c r="C256" s="4"/>
@@ -5968,7 +5988,7 @@
       <c r="P256" s="4"/>
       <c r="Q256" s="4"/>
     </row>
-    <row r="257" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A257" s="6"/>
       <c r="B257" s="4"/>
       <c r="C257" s="4"/>
@@ -5987,7 +6007,7 @@
       <c r="P257" s="4"/>
       <c r="Q257" s="4"/>
     </row>
-    <row r="258" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A258" s="6"/>
       <c r="B258" s="4"/>
       <c r="C258" s="4"/>
@@ -6006,7 +6026,7 @@
       <c r="P258" s="4"/>
       <c r="Q258" s="4"/>
     </row>
-    <row r="259" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A259" s="6"/>
       <c r="B259" s="4"/>
       <c r="C259" s="4"/>
@@ -6025,7 +6045,7 @@
       <c r="P259" s="4"/>
       <c r="Q259" s="4"/>
     </row>
-    <row r="260" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A260" s="6"/>
       <c r="B260" s="4"/>
       <c r="C260" s="4"/>
@@ -6044,7 +6064,7 @@
       <c r="P260" s="4"/>
       <c r="Q260" s="4"/>
     </row>
-    <row r="261" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A261" s="6"/>
       <c r="B261" s="4"/>
       <c r="C261" s="4"/>
@@ -6063,7 +6083,7 @@
       <c r="P261" s="4"/>
       <c r="Q261" s="4"/>
     </row>
-    <row r="262" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A262" s="6"/>
       <c r="B262" s="4"/>
       <c r="C262" s="4"/>
@@ -6082,7 +6102,7 @@
       <c r="P262" s="4"/>
       <c r="Q262" s="4"/>
     </row>
-    <row r="263" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A263" s="6"/>
       <c r="B263" s="4"/>
       <c r="C263" s="4"/>
@@ -6101,7 +6121,7 @@
       <c r="P263" s="4"/>
       <c r="Q263" s="4"/>
     </row>
-    <row r="264" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A264" s="6"/>
       <c r="B264" s="4"/>
       <c r="C264" s="4"/>
@@ -6120,7 +6140,7 @@
       <c r="P264" s="4"/>
       <c r="Q264" s="4"/>
     </row>
-    <row r="265" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A265" s="6"/>
       <c r="B265" s="4"/>
       <c r="C265" s="4"/>
@@ -6139,7 +6159,7 @@
       <c r="P265" s="4"/>
       <c r="Q265" s="4"/>
     </row>
-    <row r="266" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A266" s="6"/>
       <c r="B266" s="4"/>
       <c r="C266" s="4"/>
@@ -6158,7 +6178,7 @@
       <c r="P266" s="4"/>
       <c r="Q266" s="4"/>
     </row>
-    <row r="267" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A267" s="6"/>
       <c r="B267" s="4"/>
       <c r="C267" s="4"/>
@@ -6177,7 +6197,7 @@
       <c r="P267" s="4"/>
       <c r="Q267" s="4"/>
     </row>
-    <row r="268" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A268" s="6"/>
       <c r="B268" s="4"/>
       <c r="C268" s="4"/>
@@ -6196,7 +6216,7 @@
       <c r="P268" s="4"/>
       <c r="Q268" s="4"/>
     </row>
-    <row r="269" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A269" s="6"/>
       <c r="B269" s="4"/>
       <c r="C269" s="4"/>
@@ -6215,7 +6235,7 @@
       <c r="P269" s="4"/>
       <c r="Q269" s="4"/>
     </row>
-    <row r="270" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A270" s="6"/>
       <c r="B270" s="4"/>
       <c r="C270" s="4"/>
@@ -6234,7 +6254,7 @@
       <c r="P270" s="4"/>
       <c r="Q270" s="4"/>
     </row>
-    <row r="271" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A271" s="6"/>
       <c r="B271" s="4"/>
       <c r="C271" s="4"/>
@@ -6253,7 +6273,7 @@
       <c r="P271" s="4"/>
       <c r="Q271" s="4"/>
     </row>
-    <row r="272" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A272" s="6"/>
       <c r="B272" s="4"/>
       <c r="C272" s="4"/>
@@ -6272,7 +6292,7 @@
       <c r="P272" s="4"/>
       <c r="Q272" s="4"/>
     </row>
-    <row r="273" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A273" s="6"/>
       <c r="B273" s="4"/>
       <c r="C273" s="4"/>
@@ -6291,7 +6311,7 @@
       <c r="P273" s="4"/>
       <c r="Q273" s="4"/>
     </row>
-    <row r="274" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A274" s="6"/>
       <c r="B274" s="4"/>
       <c r="C274" s="4"/>
@@ -6310,7 +6330,7 @@
       <c r="P274" s="4"/>
       <c r="Q274" s="4"/>
     </row>
-    <row r="275" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A275" s="6"/>
       <c r="B275" s="4"/>
       <c r="C275" s="4"/>
@@ -6329,7 +6349,7 @@
       <c r="P275" s="4"/>
       <c r="Q275" s="4"/>
     </row>
-    <row r="276" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A276" s="6"/>
       <c r="B276" s="4"/>
       <c r="C276" s="4"/>
@@ -6348,7 +6368,7 @@
       <c r="P276" s="4"/>
       <c r="Q276" s="4"/>
     </row>
-    <row r="277" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A277" s="6"/>
       <c r="B277" s="4"/>
       <c r="C277" s="4"/>
@@ -6367,7 +6387,7 @@
       <c r="P277" s="4"/>
       <c r="Q277" s="4"/>
     </row>
-    <row r="278" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A278" s="6"/>
       <c r="B278" s="4"/>
       <c r="C278" s="4"/>
@@ -6386,7 +6406,7 @@
       <c r="P278" s="4"/>
       <c r="Q278" s="4"/>
     </row>
-    <row r="279" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A279" s="6"/>
       <c r="B279" s="4"/>
       <c r="C279" s="4"/>
@@ -6405,7 +6425,7 @@
       <c r="P279" s="4"/>
       <c r="Q279" s="4"/>
     </row>
-    <row r="280" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A280" s="6"/>
       <c r="B280" s="4"/>
       <c r="C280" s="4"/>
@@ -6424,7 +6444,7 @@
       <c r="P280" s="4"/>
       <c r="Q280" s="4"/>
     </row>
-    <row r="281" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A281" s="6"/>
       <c r="B281" s="4"/>
       <c r="C281" s="4"/>
@@ -6443,7 +6463,7 @@
       <c r="P281" s="4"/>
       <c r="Q281" s="4"/>
     </row>
-    <row r="282" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A282" s="6"/>
       <c r="B282" s="4"/>
       <c r="C282" s="4"/>
@@ -6462,7 +6482,7 @@
       <c r="P282" s="4"/>
       <c r="Q282" s="4"/>
     </row>
-    <row r="283" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A283" s="6"/>
       <c r="B283" s="4"/>
       <c r="C283" s="4"/>
@@ -6481,7 +6501,7 @@
       <c r="P283" s="4"/>
       <c r="Q283" s="4"/>
     </row>
-    <row r="284" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A284" s="6"/>
       <c r="B284" s="4"/>
       <c r="C284" s="4"/>
@@ -6500,7 +6520,7 @@
       <c r="P284" s="4"/>
       <c r="Q284" s="4"/>
     </row>
-    <row r="285" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A285" s="6"/>
       <c r="B285" s="4"/>
       <c r="C285" s="4"/>
@@ -6519,7 +6539,7 @@
       <c r="P285" s="4"/>
       <c r="Q285" s="4"/>
     </row>
-    <row r="286" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A286" s="6"/>
       <c r="B286" s="4"/>
       <c r="C286" s="4"/>
@@ -6538,7 +6558,7 @@
       <c r="P286" s="4"/>
       <c r="Q286" s="4"/>
     </row>
-    <row r="287" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A287" s="6"/>
       <c r="B287" s="4"/>
       <c r="C287" s="4"/>
@@ -6557,7 +6577,7 @@
       <c r="P287" s="4"/>
       <c r="Q287" s="4"/>
     </row>
-    <row r="288" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A288" s="6"/>
       <c r="B288" s="4"/>
       <c r="C288" s="4"/>
@@ -6576,7 +6596,7 @@
       <c r="P288" s="4"/>
       <c r="Q288" s="4"/>
     </row>
-    <row r="289" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A289" s="6"/>
       <c r="B289" s="4"/>
       <c r="C289" s="4"/>
@@ -6595,7 +6615,7 @@
       <c r="P289" s="4"/>
       <c r="Q289" s="4"/>
     </row>
-    <row r="290" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A290" s="6"/>
       <c r="B290" s="4"/>
       <c r="C290" s="4"/>
@@ -6614,7 +6634,7 @@
       <c r="P290" s="4"/>
       <c r="Q290" s="4"/>
     </row>
-    <row r="291" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A291" s="6"/>
       <c r="B291" s="4"/>
       <c r="C291" s="4"/>
@@ -6633,7 +6653,7 @@
       <c r="P291" s="4"/>
       <c r="Q291" s="4"/>
     </row>
-    <row r="292" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A292" s="6"/>
       <c r="B292" s="4"/>
       <c r="C292" s="4"/>
@@ -6652,7 +6672,7 @@
       <c r="P292" s="4"/>
       <c r="Q292" s="4"/>
     </row>
-    <row r="293" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A293" s="6"/>
       <c r="B293" s="4"/>
       <c r="C293" s="4"/>
@@ -6671,7 +6691,7 @@
       <c r="P293" s="4"/>
       <c r="Q293" s="4"/>
     </row>
-    <row r="294" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A294" s="6"/>
       <c r="B294" s="4"/>
       <c r="C294" s="4"/>
@@ -6690,7 +6710,7 @@
       <c r="P294" s="4"/>
       <c r="Q294" s="4"/>
     </row>
-    <row r="295" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A295" s="6"/>
       <c r="B295" s="4"/>
       <c r="C295" s="4"/>
@@ -6709,7 +6729,7 @@
       <c r="P295" s="4"/>
       <c r="Q295" s="4"/>
     </row>
-    <row r="296" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A296" s="6"/>
       <c r="B296" s="4"/>
       <c r="C296" s="4"/>
@@ -6728,7 +6748,7 @@
       <c r="P296" s="4"/>
       <c r="Q296" s="4"/>
     </row>
-    <row r="297" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A297" s="6"/>
       <c r="B297" s="4"/>
       <c r="C297" s="4"/>
@@ -6747,7 +6767,7 @@
       <c r="P297" s="4"/>
       <c r="Q297" s="4"/>
     </row>
-    <row r="298" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A298" s="6"/>
       <c r="B298" s="4"/>
       <c r="C298" s="4"/>
@@ -6766,7 +6786,7 @@
       <c r="P298" s="4"/>
       <c r="Q298" s="4"/>
     </row>
-    <row r="299" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A299" s="6"/>
       <c r="B299" s="4"/>
       <c r="C299" s="4"/>
@@ -6785,7 +6805,7 @@
       <c r="P299" s="4"/>
       <c r="Q299" s="4"/>
     </row>
-    <row r="300" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A300" s="6"/>
       <c r="B300" s="4"/>
       <c r="C300" s="4"/>
@@ -6804,7 +6824,7 @@
       <c r="P300" s="4"/>
       <c r="Q300" s="4"/>
     </row>
-    <row r="301" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A301" s="6"/>
       <c r="B301" s="4"/>
       <c r="C301" s="4"/>
@@ -6823,7 +6843,7 @@
       <c r="P301" s="4"/>
       <c r="Q301" s="4"/>
     </row>
-    <row r="302" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A302" s="6"/>
       <c r="B302" s="4"/>
       <c r="C302" s="4"/>
@@ -6842,7 +6862,7 @@
       <c r="P302" s="4"/>
       <c r="Q302" s="4"/>
     </row>
-    <row r="303" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A303" s="6"/>
       <c r="B303" s="4"/>
       <c r="C303" s="4"/>
@@ -6861,7 +6881,7 @@
       <c r="P303" s="4"/>
       <c r="Q303" s="4"/>
     </row>
-    <row r="304" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A304" s="6"/>
       <c r="B304" s="4"/>
       <c r="C304" s="4"/>
@@ -6880,7 +6900,7 @@
       <c r="P304" s="4"/>
       <c r="Q304" s="4"/>
     </row>
-    <row r="305" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A305" s="6"/>
       <c r="B305" s="4"/>
       <c r="C305" s="4"/>
@@ -6899,7 +6919,7 @@
       <c r="P305" s="4"/>
       <c r="Q305" s="4"/>
     </row>
-    <row r="306" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A306" s="6"/>
       <c r="B306" s="4"/>
       <c r="C306" s="4"/>
@@ -6918,7 +6938,7 @@
       <c r="P306" s="4"/>
       <c r="Q306" s="4"/>
     </row>
-    <row r="307" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A307" s="6"/>
       <c r="B307" s="4"/>
       <c r="C307" s="4"/>
@@ -6937,7 +6957,7 @@
       <c r="P307" s="4"/>
       <c r="Q307" s="4"/>
     </row>
-    <row r="308" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A308" s="6"/>
       <c r="B308" s="4"/>
       <c r="C308" s="4"/>
@@ -6956,7 +6976,7 @@
       <c r="P308" s="4"/>
       <c r="Q308" s="4"/>
     </row>
-    <row r="309" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A309" s="6"/>
       <c r="B309" s="4"/>
       <c r="C309" s="4"/>
@@ -6975,7 +6995,7 @@
       <c r="P309" s="4"/>
       <c r="Q309" s="4"/>
     </row>
-    <row r="310" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A310" s="6"/>
       <c r="B310" s="4"/>
       <c r="C310" s="4"/>
@@ -6994,7 +7014,7 @@
       <c r="P310" s="4"/>
       <c r="Q310" s="4"/>
     </row>
-    <row r="311" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A311" s="6"/>
       <c r="B311" s="4"/>
       <c r="C311" s="4"/>
@@ -7013,7 +7033,7 @@
       <c r="P311" s="4"/>
       <c r="Q311" s="4"/>
     </row>
-    <row r="312" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A312" s="6"/>
       <c r="B312" s="4"/>
       <c r="C312" s="4"/>
@@ -7032,7 +7052,7 @@
       <c r="P312" s="4"/>
       <c r="Q312" s="4"/>
     </row>
-    <row r="313" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A313" s="6"/>
       <c r="B313" s="4"/>
       <c r="C313" s="4"/>
@@ -7051,7 +7071,7 @@
       <c r="P313" s="4"/>
       <c r="Q313" s="4"/>
     </row>
-    <row r="314" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A314" s="6"/>
       <c r="B314" s="4"/>
       <c r="C314" s="4"/>
@@ -7070,7 +7090,7 @@
       <c r="P314" s="4"/>
       <c r="Q314" s="4"/>
     </row>
-    <row r="315" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A315" s="6"/>
       <c r="B315" s="4"/>
       <c r="C315" s="4"/>
@@ -7089,7 +7109,7 @@
       <c r="P315" s="4"/>
       <c r="Q315" s="4"/>
     </row>
-    <row r="316" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A316" s="6"/>
       <c r="B316" s="4"/>
       <c r="C316" s="4"/>
@@ -7108,7 +7128,7 @@
       <c r="P316" s="4"/>
       <c r="Q316" s="4"/>
     </row>
-    <row r="317" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A317" s="6"/>
       <c r="B317" s="4"/>
       <c r="C317" s="4"/>
@@ -7127,7 +7147,7 @@
       <c r="P317" s="4"/>
       <c r="Q317" s="4"/>
     </row>
-    <row r="318" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A318" s="6"/>
       <c r="B318" s="4"/>
       <c r="C318" s="4"/>
@@ -7146,7 +7166,7 @@
       <c r="P318" s="4"/>
       <c r="Q318" s="4"/>
     </row>
-    <row r="319" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A319" s="6"/>
       <c r="B319" s="4"/>
       <c r="C319" s="4"/>
@@ -7165,7 +7185,7 @@
       <c r="P319" s="4"/>
       <c r="Q319" s="4"/>
     </row>
-    <row r="320" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A320" s="6"/>
       <c r="B320" s="4"/>
       <c r="C320" s="4"/>
@@ -7184,7 +7204,7 @@
       <c r="P320" s="4"/>
       <c r="Q320" s="4"/>
     </row>
-    <row r="321" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A321" s="6"/>
       <c r="B321" s="4"/>
       <c r="C321" s="4"/>
@@ -7203,7 +7223,7 @@
       <c r="P321" s="4"/>
       <c r="Q321" s="4"/>
     </row>
-    <row r="322" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A322" s="6"/>
       <c r="B322" s="4"/>
       <c r="C322" s="4"/>
@@ -7222,7 +7242,7 @@
       <c r="P322" s="4"/>
       <c r="Q322" s="4"/>
     </row>
-    <row r="323" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A323" s="6"/>
       <c r="B323" s="4"/>
       <c r="C323" s="4"/>
@@ -7241,7 +7261,7 @@
       <c r="P323" s="4"/>
       <c r="Q323" s="4"/>
     </row>
-    <row r="324" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A324" s="6"/>
       <c r="B324" s="4"/>
       <c r="C324" s="4"/>
@@ -7260,7 +7280,7 @@
       <c r="P324" s="4"/>
       <c r="Q324" s="4"/>
     </row>
-    <row r="325" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A325" s="6"/>
       <c r="B325" s="4"/>
       <c r="C325" s="4"/>
@@ -7279,7 +7299,7 @@
       <c r="P325" s="4"/>
       <c r="Q325" s="4"/>
     </row>
-    <row r="326" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A326" s="6"/>
       <c r="B326" s="4"/>
       <c r="C326" s="4"/>
@@ -7298,7 +7318,7 @@
       <c r="P326" s="4"/>
       <c r="Q326" s="4"/>
     </row>
-    <row r="327" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A327" s="6"/>
       <c r="B327" s="4"/>
       <c r="C327" s="4"/>
@@ -7317,7 +7337,7 @@
       <c r="P327" s="4"/>
       <c r="Q327" s="4"/>
     </row>
-    <row r="328" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A328" s="6"/>
       <c r="B328" s="4"/>
       <c r="C328" s="4"/>
@@ -7336,7 +7356,7 @@
       <c r="P328" s="4"/>
       <c r="Q328" s="4"/>
     </row>
-    <row r="329" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A329" s="6"/>
       <c r="B329" s="4"/>
       <c r="C329" s="4"/>
@@ -7355,7 +7375,7 @@
       <c r="P329" s="4"/>
       <c r="Q329" s="4"/>
     </row>
-    <row r="330" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A330" s="6"/>
       <c r="B330" s="4"/>
       <c r="C330" s="4"/>
@@ -7374,7 +7394,7 @@
       <c r="P330" s="4"/>
       <c r="Q330" s="4"/>
     </row>
-    <row r="331" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A331" s="6"/>
       <c r="B331" s="4"/>
       <c r="C331" s="4"/>
@@ -7393,7 +7413,7 @@
       <c r="P331" s="4"/>
       <c r="Q331" s="4"/>
     </row>
-    <row r="332" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A332" s="6"/>
       <c r="B332" s="4"/>
       <c r="C332" s="4"/>
@@ -7412,7 +7432,7 @@
       <c r="P332" s="4"/>
       <c r="Q332" s="4"/>
     </row>
-    <row r="333" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A333" s="6"/>
       <c r="B333" s="4"/>
       <c r="C333" s="4"/>
@@ -7431,7 +7451,7 @@
       <c r="P333" s="4"/>
       <c r="Q333" s="4"/>
     </row>
-    <row r="334" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A334" s="6"/>
       <c r="B334" s="4"/>
       <c r="C334" s="4"/>
@@ -7450,7 +7470,7 @@
       <c r="P334" s="4"/>
       <c r="Q334" s="4"/>
     </row>
-    <row r="335" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A335" s="6"/>
       <c r="B335" s="4"/>
       <c r="C335" s="4"/>
@@ -7469,7 +7489,7 @@
       <c r="P335" s="4"/>
       <c r="Q335" s="4"/>
     </row>
-    <row r="336" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A336" s="6"/>
       <c r="B336" s="4"/>
       <c r="C336" s="4"/>
@@ -7488,7 +7508,7 @@
       <c r="P336" s="4"/>
       <c r="Q336" s="4"/>
     </row>
-    <row r="337" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A337" s="6"/>
       <c r="B337" s="4"/>
       <c r="C337" s="4"/>
@@ -7507,7 +7527,7 @@
       <c r="P337" s="4"/>
       <c r="Q337" s="4"/>
     </row>
-    <row r="338" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A338" s="6"/>
       <c r="B338" s="4"/>
       <c r="C338" s="4"/>
@@ -7526,7 +7546,7 @@
       <c r="P338" s="4"/>
       <c r="Q338" s="4"/>
     </row>
-    <row r="339" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A339" s="6"/>
       <c r="B339" s="4"/>
       <c r="C339" s="4"/>
@@ -7545,7 +7565,7 @@
       <c r="P339" s="4"/>
       <c r="Q339" s="4"/>
     </row>
-    <row r="340" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A340" s="6"/>
       <c r="B340" s="4"/>
       <c r="C340" s="4"/>
@@ -7564,7 +7584,7 @@
       <c r="P340" s="4"/>
       <c r="Q340" s="4"/>
     </row>
-    <row r="341" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A341" s="6"/>
       <c r="B341" s="4"/>
       <c r="C341" s="4"/>
@@ -7583,7 +7603,7 @@
       <c r="P341" s="4"/>
       <c r="Q341" s="4"/>
     </row>
-    <row r="342" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A342" s="6"/>
       <c r="B342" s="4"/>
       <c r="C342" s="4"/>
@@ -7602,7 +7622,7 @@
       <c r="P342" s="4"/>
       <c r="Q342" s="4"/>
     </row>
-    <row r="343" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A343" s="6"/>
       <c r="B343" s="4"/>
       <c r="C343" s="4"/>
@@ -7621,7 +7641,7 @@
       <c r="P343" s="4"/>
       <c r="Q343" s="4"/>
     </row>
-    <row r="344" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A344" s="6"/>
       <c r="B344" s="4"/>
       <c r="C344" s="4"/>
@@ -7640,7 +7660,7 @@
       <c r="P344" s="4"/>
       <c r="Q344" s="4"/>
     </row>
-    <row r="345" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A345" s="6"/>
       <c r="B345" s="4"/>
       <c r="C345" s="4"/>
@@ -7659,7 +7679,7 @@
       <c r="P345" s="4"/>
       <c r="Q345" s="4"/>
     </row>
-    <row r="346" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A346" s="6"/>
       <c r="B346" s="4"/>
       <c r="C346" s="4"/>
@@ -7678,7 +7698,7 @@
       <c r="P346" s="4"/>
       <c r="Q346" s="4"/>
     </row>
-    <row r="347" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A347" s="6"/>
       <c r="B347" s="4"/>
       <c r="C347" s="4"/>
@@ -7697,7 +7717,7 @@
       <c r="P347" s="4"/>
       <c r="Q347" s="4"/>
     </row>
-    <row r="348" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A348" s="6"/>
       <c r="B348" s="4"/>
       <c r="C348" s="4"/>
@@ -7716,7 +7736,7 @@
       <c r="P348" s="4"/>
       <c r="Q348" s="4"/>
     </row>
-    <row r="349" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A349" s="6"/>
       <c r="B349" s="4"/>
       <c r="C349" s="4"/>
@@ -7735,7 +7755,7 @@
       <c r="P349" s="4"/>
       <c r="Q349" s="4"/>
     </row>
-    <row r="350" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A350" s="6"/>
       <c r="B350" s="4"/>
       <c r="C350" s="4"/>
@@ -7754,7 +7774,7 @@
       <c r="P350" s="4"/>
       <c r="Q350" s="4"/>
     </row>
-    <row r="351" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A351" s="6"/>
       <c r="B351" s="4"/>
       <c r="C351" s="4"/>
@@ -7773,7 +7793,7 @@
       <c r="P351" s="4"/>
       <c r="Q351" s="4"/>
     </row>
-    <row r="352" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A352" s="6"/>
       <c r="B352" s="4"/>
       <c r="C352" s="4"/>
@@ -7792,7 +7812,7 @@
       <c r="P352" s="4"/>
       <c r="Q352" s="4"/>
     </row>
-    <row r="353" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A353" s="6"/>
       <c r="B353" s="4"/>
       <c r="C353" s="4"/>
@@ -7811,7 +7831,7 @@
       <c r="P353" s="4"/>
       <c r="Q353" s="4"/>
     </row>
-    <row r="354" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A354" s="6"/>
       <c r="B354" s="4"/>
       <c r="C354" s="4"/>
@@ -7830,7 +7850,7 @@
       <c r="P354" s="4"/>
       <c r="Q354" s="4"/>
     </row>
-    <row r="355" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A355" s="6"/>
       <c r="B355" s="4"/>
       <c r="C355" s="4"/>
@@ -7849,7 +7869,7 @@
       <c r="P355" s="4"/>
       <c r="Q355" s="4"/>
     </row>
-    <row r="356" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A356" s="6"/>
       <c r="B356" s="4"/>
       <c r="C356" s="4"/>
@@ -7868,7 +7888,7 @@
       <c r="P356" s="4"/>
       <c r="Q356" s="4"/>
     </row>
-    <row r="357" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A357" s="6"/>
       <c r="B357" s="4"/>
       <c r="C357" s="4"/>
@@ -7887,7 +7907,7 @@
       <c r="P357" s="4"/>
       <c r="Q357" s="4"/>
     </row>
-    <row r="358" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A358" s="6"/>
       <c r="B358" s="4"/>
       <c r="C358" s="4"/>
@@ -7906,7 +7926,7 @@
       <c r="P358" s="4"/>
       <c r="Q358" s="4"/>
     </row>
-    <row r="359" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A359" s="6"/>
       <c r="B359" s="4"/>
       <c r="C359" s="4"/>
@@ -7925,7 +7945,7 @@
       <c r="P359" s="4"/>
       <c r="Q359" s="4"/>
     </row>
-    <row r="360" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A360" s="6"/>
       <c r="B360" s="4"/>
       <c r="C360" s="4"/>
@@ -7944,7 +7964,7 @@
       <c r="P360" s="4"/>
       <c r="Q360" s="4"/>
     </row>
-    <row r="361" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A361" s="6"/>
       <c r="B361" s="4"/>
       <c r="C361" s="4"/>
@@ -7963,7 +7983,7 @@
       <c r="P361" s="4"/>
       <c r="Q361" s="4"/>
     </row>
-    <row r="362" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A362" s="6"/>
       <c r="B362" s="4"/>
       <c r="C362" s="4"/>
@@ -7982,7 +8002,7 @@
       <c r="P362" s="4"/>
       <c r="Q362" s="4"/>
     </row>
-    <row r="363" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A363" s="6"/>
       <c r="B363" s="4"/>
       <c r="C363" s="4"/>
@@ -8001,7 +8021,7 @@
       <c r="P363" s="4"/>
       <c r="Q363" s="4"/>
     </row>
-    <row r="364" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A364" s="6"/>
       <c r="B364" s="4"/>
       <c r="C364" s="4"/>
@@ -8020,7 +8040,7 @@
       <c r="P364" s="4"/>
       <c r="Q364" s="4"/>
     </row>
-    <row r="365" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A365" s="6"/>
       <c r="B365" s="4"/>
       <c r="C365" s="4"/>
@@ -8039,7 +8059,7 @@
       <c r="P365" s="4"/>
       <c r="Q365" s="4"/>
     </row>
-    <row r="366" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A366" s="6"/>
       <c r="B366" s="4"/>
       <c r="C366" s="4"/>
@@ -8058,7 +8078,7 @@
       <c r="P366" s="4"/>
       <c r="Q366" s="4"/>
     </row>
-    <row r="367" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A367" s="6"/>
       <c r="B367" s="4"/>
       <c r="C367" s="4"/>
@@ -8077,7 +8097,7 @@
       <c r="P367" s="4"/>
       <c r="Q367" s="4"/>
     </row>
-    <row r="368" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A368" s="6"/>
       <c r="B368" s="4"/>
       <c r="C368" s="4"/>
@@ -8096,7 +8116,7 @@
       <c r="P368" s="4"/>
       <c r="Q368" s="4"/>
     </row>
-    <row r="369" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A369" s="6"/>
       <c r="B369" s="4"/>
       <c r="C369" s="4"/>
@@ -8115,7 +8135,7 @@
       <c r="P369" s="4"/>
       <c r="Q369" s="4"/>
     </row>
-    <row r="370" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A370" s="6"/>
       <c r="B370" s="4"/>
       <c r="C370" s="4"/>
@@ -8134,7 +8154,7 @@
       <c r="P370" s="4"/>
       <c r="Q370" s="4"/>
     </row>
-    <row r="371" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A371" s="6"/>
       <c r="B371" s="4"/>
       <c r="C371" s="4"/>
@@ -8153,7 +8173,7 @@
       <c r="P371" s="4"/>
       <c r="Q371" s="4"/>
     </row>
-    <row r="372" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A372" s="6"/>
       <c r="B372" s="4"/>
       <c r="C372" s="4"/>
@@ -8172,7 +8192,7 @@
       <c r="P372" s="4"/>
       <c r="Q372" s="4"/>
     </row>
-    <row r="373" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A373" s="6"/>
       <c r="B373" s="4"/>
       <c r="C373" s="4"/>
@@ -8191,7 +8211,7 @@
       <c r="P373" s="4"/>
       <c r="Q373" s="4"/>
     </row>
-    <row r="374" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A374" s="6"/>
       <c r="B374" s="4"/>
       <c r="C374" s="4"/>
@@ -8210,7 +8230,7 @@
       <c r="P374" s="4"/>
       <c r="Q374" s="4"/>
     </row>
-    <row r="375" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A375" s="6"/>
       <c r="B375" s="4"/>
       <c r="C375" s="4"/>
@@ -8229,7 +8249,7 @@
       <c r="P375" s="4"/>
       <c r="Q375" s="4"/>
     </row>
-    <row r="376" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A376" s="6"/>
       <c r="B376" s="4"/>
       <c r="C376" s="4"/>
@@ -8248,7 +8268,7 @@
       <c r="P376" s="4"/>
       <c r="Q376" s="4"/>
     </row>
-    <row r="377" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A377" s="6"/>
       <c r="B377" s="4"/>
       <c r="C377" s="4"/>
@@ -8267,7 +8287,7 @@
       <c r="P377" s="4"/>
       <c r="Q377" s="4"/>
     </row>
-    <row r="378" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A378" s="6"/>
       <c r="B378" s="4"/>
       <c r="C378" s="4"/>
@@ -8286,7 +8306,7 @@
       <c r="P378" s="4"/>
       <c r="Q378" s="4"/>
     </row>
-    <row r="379" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A379" s="6"/>
       <c r="B379" s="4"/>
       <c r="C379" s="4"/>
@@ -8305,7 +8325,7 @@
       <c r="P379" s="4"/>
       <c r="Q379" s="4"/>
     </row>
-    <row r="380" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A380" s="6"/>
       <c r="B380" s="4"/>
       <c r="C380" s="4"/>
@@ -8324,7 +8344,7 @@
       <c r="P380" s="4"/>
       <c r="Q380" s="4"/>
     </row>
-    <row r="381" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A381" s="6"/>
       <c r="B381" s="4"/>
       <c r="C381" s="4"/>
@@ -8343,7 +8363,7 @@
       <c r="P381" s="4"/>
       <c r="Q381" s="4"/>
     </row>
-    <row r="382" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A382" s="6"/>
       <c r="B382" s="4"/>
       <c r="C382" s="4"/>
@@ -8362,7 +8382,7 @@
       <c r="P382" s="4"/>
       <c r="Q382" s="4"/>
     </row>
-    <row r="383" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A383" s="6"/>
       <c r="B383" s="4"/>
       <c r="C383" s="4"/>
@@ -8381,7 +8401,7 @@
       <c r="P383" s="4"/>
       <c r="Q383" s="4"/>
     </row>
-    <row r="384" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A384" s="6"/>
       <c r="B384" s="4"/>
       <c r="C384" s="4"/>
@@ -8400,7 +8420,7 @@
       <c r="P384" s="4"/>
       <c r="Q384" s="4"/>
     </row>
-    <row r="385" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A385" s="6"/>
       <c r="B385" s="4"/>
       <c r="C385" s="4"/>
@@ -8419,7 +8439,7 @@
       <c r="P385" s="4"/>
       <c r="Q385" s="4"/>
     </row>
-    <row r="386" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A386" s="6"/>
       <c r="B386" s="4"/>
       <c r="C386" s="4"/>
@@ -8438,7 +8458,7 @@
       <c r="P386" s="4"/>
       <c r="Q386" s="4"/>
     </row>
-    <row r="387" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A387" s="6"/>
       <c r="B387" s="4"/>
       <c r="C387" s="4"/>
@@ -8457,7 +8477,7 @@
       <c r="P387" s="4"/>
       <c r="Q387" s="4"/>
     </row>
-    <row r="388" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A388" s="6"/>
       <c r="B388" s="4"/>
       <c r="C388" s="4"/>
@@ -8476,7 +8496,7 @@
       <c r="P388" s="4"/>
       <c r="Q388" s="4"/>
     </row>
-    <row r="389" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A389" s="6"/>
       <c r="B389" s="4"/>
       <c r="C389" s="4"/>
@@ -8495,7 +8515,7 @@
       <c r="P389" s="4"/>
       <c r="Q389" s="4"/>
     </row>
-    <row r="390" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A390" s="6"/>
       <c r="B390" s="4"/>
       <c r="C390" s="4"/>
@@ -8514,7 +8534,7 @@
       <c r="P390" s="4"/>
       <c r="Q390" s="4"/>
     </row>
-    <row r="391" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A391" s="6"/>
       <c r="B391" s="4"/>
       <c r="C391" s="4"/>
@@ -8533,7 +8553,7 @@
       <c r="P391" s="4"/>
       <c r="Q391" s="4"/>
     </row>
-    <row r="392" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A392" s="6"/>
       <c r="B392" s="4"/>
       <c r="C392" s="4"/>
@@ -8552,7 +8572,7 @@
       <c r="P392" s="4"/>
       <c r="Q392" s="4"/>
     </row>
-    <row r="393" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A393" s="6"/>
       <c r="B393" s="4"/>
       <c r="C393" s="4"/>
@@ -8571,7 +8591,7 @@
       <c r="P393" s="4"/>
       <c r="Q393" s="4"/>
     </row>
-    <row r="394" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A394" s="6"/>
       <c r="B394" s="4"/>
       <c r="C394" s="4"/>
@@ -8590,7 +8610,7 @@
       <c r="P394" s="4"/>
       <c r="Q394" s="4"/>
     </row>
-    <row r="395" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A395" s="6"/>
       <c r="B395" s="4"/>
       <c r="C395" s="4"/>
@@ -8609,7 +8629,7 @@
       <c r="P395" s="4"/>
       <c r="Q395" s="4"/>
     </row>
-    <row r="396" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A396" s="6"/>
       <c r="B396" s="4"/>
       <c r="C396" s="4"/>
@@ -8628,7 +8648,7 @@
       <c r="P396" s="4"/>
       <c r="Q396" s="4"/>
     </row>
-    <row r="397" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A397" s="6"/>
       <c r="B397" s="4"/>
       <c r="C397" s="4"/>
@@ -8647,7 +8667,7 @@
       <c r="P397" s="4"/>
       <c r="Q397" s="4"/>
     </row>
-    <row r="398" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A398" s="6"/>
       <c r="B398" s="4"/>
       <c r="C398" s="4"/>
@@ -8666,7 +8686,7 @@
       <c r="P398" s="4"/>
       <c r="Q398" s="4"/>
     </row>
-    <row r="399" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A399" s="6"/>
       <c r="B399" s="4"/>
       <c r="C399" s="4"/>
@@ -8685,7 +8705,7 @@
       <c r="P399" s="4"/>
       <c r="Q399" s="4"/>
     </row>
-    <row r="400" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A400" s="6"/>
       <c r="B400" s="4"/>
       <c r="C400" s="4"/>
@@ -8704,7 +8724,7 @@
       <c r="P400" s="4"/>
       <c r="Q400" s="4"/>
     </row>
-    <row r="401" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A401" s="6"/>
       <c r="B401" s="4"/>
       <c r="C401" s="4"/>
@@ -8723,7 +8743,7 @@
       <c r="P401" s="4"/>
       <c r="Q401" s="4"/>
     </row>
-    <row r="402" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A402" s="6"/>
       <c r="B402" s="4"/>
       <c r="C402" s="4"/>
@@ -8742,7 +8762,7 @@
       <c r="P402" s="4"/>
       <c r="Q402" s="4"/>
     </row>
-    <row r="403" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A403" s="6"/>
       <c r="B403" s="4"/>
       <c r="C403" s="4"/>
@@ -8761,7 +8781,7 @@
       <c r="P403" s="4"/>
       <c r="Q403" s="4"/>
     </row>
-    <row r="404" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A404" s="6"/>
       <c r="B404" s="4"/>
       <c r="C404" s="4"/>
@@ -8780,7 +8800,7 @@
       <c r="P404" s="4"/>
       <c r="Q404" s="4"/>
     </row>
-    <row r="405" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A405" s="6"/>
       <c r="B405" s="4"/>
       <c r="C405" s="4"/>
@@ -8799,7 +8819,7 @@
       <c r="P405" s="4"/>
       <c r="Q405" s="4"/>
     </row>
-    <row r="406" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A406" s="6"/>
       <c r="B406" s="4"/>
       <c r="C406" s="4"/>
@@ -8818,7 +8838,7 @@
       <c r="P406" s="4"/>
       <c r="Q406" s="4"/>
     </row>
-    <row r="407" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A407" s="6"/>
       <c r="B407" s="4"/>
       <c r="C407" s="4"/>
@@ -8837,7 +8857,7 @@
       <c r="P407" s="4"/>
       <c r="Q407" s="4"/>
     </row>
-    <row r="408" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A408" s="6"/>
       <c r="B408" s="4"/>
       <c r="C408" s="4"/>
@@ -8856,7 +8876,7 @@
       <c r="P408" s="4"/>
       <c r="Q408" s="4"/>
     </row>
-    <row r="409" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A409" s="6"/>
       <c r="B409" s="4"/>
       <c r="C409" s="4"/>
@@ -8875,7 +8895,7 @@
       <c r="P409" s="4"/>
       <c r="Q409" s="4"/>
     </row>
-    <row r="410" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A410" s="6"/>
       <c r="B410" s="4"/>
       <c r="C410" s="4"/>
@@ -8894,7 +8914,7 @@
       <c r="P410" s="4"/>
       <c r="Q410" s="4"/>
     </row>
-    <row r="411" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A411" s="6"/>
       <c r="B411" s="4"/>
       <c r="C411" s="4"/>
@@ -8913,7 +8933,7 @@
       <c r="P411" s="4"/>
       <c r="Q411" s="4"/>
     </row>
-    <row r="412" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A412" s="6"/>
       <c r="B412" s="4"/>
       <c r="C412" s="4"/>
@@ -8932,7 +8952,7 @@
       <c r="P412" s="4"/>
       <c r="Q412" s="4"/>
     </row>
-    <row r="413" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A413" s="6"/>
       <c r="B413" s="4"/>
       <c r="C413" s="4"/>
@@ -8951,7 +8971,7 @@
       <c r="P413" s="4"/>
       <c r="Q413" s="4"/>
     </row>
-    <row r="414" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A414" s="6"/>
       <c r="B414" s="4"/>
       <c r="C414" s="4"/>
@@ -8970,7 +8990,7 @@
       <c r="P414" s="4"/>
       <c r="Q414" s="4"/>
     </row>
-    <row r="415" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A415" s="6"/>
       <c r="B415" s="4"/>
       <c r="C415" s="4"/>
@@ -8989,7 +9009,7 @@
       <c r="P415" s="4"/>
       <c r="Q415" s="4"/>
     </row>
-    <row r="416" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A416" s="6"/>
       <c r="B416" s="4"/>
       <c r="C416" s="4"/>
@@ -9008,7 +9028,7 @@
       <c r="P416" s="4"/>
       <c r="Q416" s="4"/>
     </row>
-    <row r="417" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A417" s="6"/>
       <c r="B417" s="4"/>
       <c r="C417" s="4"/>
@@ -9027,7 +9047,7 @@
       <c r="P417" s="4"/>
       <c r="Q417" s="4"/>
     </row>
-    <row r="418" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A418" s="6"/>
       <c r="B418" s="4"/>
       <c r="C418" s="4"/>
@@ -9046,7 +9066,7 @@
       <c r="P418" s="4"/>
       <c r="Q418" s="4"/>
     </row>
-    <row r="419" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A419" s="6"/>
       <c r="B419" s="4"/>
       <c r="C419" s="4"/>
@@ -9065,7 +9085,7 @@
       <c r="P419" s="4"/>
       <c r="Q419" s="4"/>
     </row>
-    <row r="420" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A420" s="6"/>
       <c r="B420" s="4"/>
       <c r="C420" s="4"/>
@@ -9084,7 +9104,7 @@
       <c r="P420" s="4"/>
       <c r="Q420" s="4"/>
     </row>
-    <row r="421" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A421" s="6"/>
       <c r="B421" s="4"/>
       <c r="C421" s="4"/>
@@ -9103,7 +9123,7 @@
       <c r="P421" s="4"/>
       <c r="Q421" s="4"/>
     </row>
-    <row r="422" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A422" s="6"/>
       <c r="B422" s="4"/>
       <c r="C422" s="4"/>
@@ -9122,7 +9142,7 @@
       <c r="P422" s="4"/>
       <c r="Q422" s="4"/>
     </row>
-    <row r="423" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A423" s="6"/>
       <c r="B423" s="4"/>
       <c r="C423" s="4"/>
@@ -9141,7 +9161,7 @@
       <c r="P423" s="4"/>
       <c r="Q423" s="4"/>
     </row>
-    <row r="424" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A424" s="6"/>
       <c r="B424" s="4"/>
       <c r="C424" s="4"/>
@@ -9160,7 +9180,7 @@
       <c r="P424" s="4"/>
       <c r="Q424" s="4"/>
     </row>
-    <row r="425" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A425" s="6"/>
       <c r="B425" s="4"/>
       <c r="C425" s="4"/>
@@ -9179,7 +9199,7 @@
       <c r="P425" s="4"/>
       <c r="Q425" s="4"/>
     </row>
-    <row r="426" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A426" s="6"/>
       <c r="B426" s="4"/>
       <c r="C426" s="4"/>
@@ -9198,7 +9218,7 @@
       <c r="P426" s="4"/>
       <c r="Q426" s="4"/>
     </row>
-    <row r="427" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A427" s="6"/>
       <c r="B427" s="4"/>
       <c r="C427" s="4"/>
@@ -9217,7 +9237,7 @@
       <c r="P427" s="4"/>
       <c r="Q427" s="4"/>
     </row>
-    <row r="428" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A428" s="6"/>
       <c r="B428" s="4"/>
       <c r="C428" s="4"/>
@@ -9236,7 +9256,7 @@
       <c r="P428" s="4"/>
       <c r="Q428" s="4"/>
     </row>
-    <row r="429" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A429" s="6"/>
       <c r="B429" s="4"/>
       <c r="C429" s="4"/>
@@ -9255,7 +9275,7 @@
       <c r="P429" s="4"/>
       <c r="Q429" s="4"/>
     </row>
-    <row r="430" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A430" s="6"/>
       <c r="B430" s="4"/>
       <c r="C430" s="4"/>
@@ -9274,7 +9294,7 @@
       <c r="P430" s="4"/>
       <c r="Q430" s="4"/>
     </row>
-    <row r="431" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A431" s="6"/>
       <c r="B431" s="4"/>
       <c r="C431" s="4"/>
@@ -9293,7 +9313,7 @@
       <c r="P431" s="4"/>
       <c r="Q431" s="4"/>
     </row>
-    <row r="432" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A432" s="6"/>
       <c r="B432" s="4"/>
       <c r="C432" s="4"/>
@@ -9312,7 +9332,7 @@
       <c r="P432" s="4"/>
       <c r="Q432" s="4"/>
     </row>
-    <row r="433" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A433" s="6"/>
       <c r="B433" s="4"/>
       <c r="C433" s="4"/>
@@ -9331,7 +9351,7 @@
       <c r="P433" s="4"/>
       <c r="Q433" s="4"/>
     </row>
-    <row r="434" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A434" s="6"/>
       <c r="B434" s="4"/>
       <c r="C434" s="4"/>
@@ -9350,7 +9370,7 @@
       <c r="P434" s="4"/>
       <c r="Q434" s="4"/>
     </row>
-    <row r="435" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A435" s="6"/>
       <c r="B435" s="4"/>
       <c r="C435" s="4"/>
@@ -9369,7 +9389,7 @@
       <c r="P435" s="4"/>
       <c r="Q435" s="4"/>
     </row>
-    <row r="436" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A436" s="6"/>
       <c r="B436" s="4"/>
       <c r="C436" s="4"/>
@@ -9388,7 +9408,7 @@
       <c r="P436" s="4"/>
       <c r="Q436" s="4"/>
     </row>
-    <row r="437" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A437" s="6"/>
       <c r="B437" s="4"/>
       <c r="C437" s="4"/>
@@ -9407,7 +9427,7 @@
       <c r="P437" s="4"/>
       <c r="Q437" s="4"/>
     </row>
-    <row r="438" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A438" s="6"/>
       <c r="B438" s="4"/>
       <c r="C438" s="4"/>
@@ -9426,7 +9446,7 @@
       <c r="P438" s="4"/>
       <c r="Q438" s="4"/>
     </row>
-    <row r="439" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A439" s="6"/>
       <c r="B439" s="4"/>
       <c r="C439" s="4"/>
@@ -9445,7 +9465,7 @@
       <c r="P439" s="4"/>
       <c r="Q439" s="4"/>
     </row>
-    <row r="440" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A440" s="6"/>
       <c r="B440" s="4"/>
       <c r="C440" s="4"/>
@@ -9464,7 +9484,7 @@
       <c r="P440" s="4"/>
       <c r="Q440" s="4"/>
     </row>
-    <row r="441" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A441" s="6"/>
       <c r="B441" s="4"/>
       <c r="C441" s="4"/>
@@ -9483,7 +9503,7 @@
       <c r="P441" s="4"/>
       <c r="Q441" s="4"/>
     </row>
-    <row r="442" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A442" s="6"/>
       <c r="B442" s="4"/>
       <c r="C442" s="4"/>
@@ -9502,7 +9522,7 @@
       <c r="P442" s="4"/>
       <c r="Q442" s="4"/>
     </row>
-    <row r="443" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A443" s="6"/>
       <c r="B443" s="4"/>
       <c r="C443" s="4"/>
@@ -9521,7 +9541,7 @@
       <c r="P443" s="4"/>
       <c r="Q443" s="4"/>
     </row>
-    <row r="444" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A444" s="6"/>
       <c r="B444" s="4"/>
       <c r="C444" s="4"/>
@@ -9540,7 +9560,7 @@
       <c r="P444" s="4"/>
       <c r="Q444" s="4"/>
     </row>
-    <row r="445" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A445" s="6"/>
       <c r="B445" s="4"/>
       <c r="C445" s="4"/>
@@ -9559,7 +9579,7 @@
       <c r="P445" s="4"/>
       <c r="Q445" s="4"/>
     </row>
-    <row r="446" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A446" s="6"/>
       <c r="B446" s="4"/>
       <c r="C446" s="4"/>
@@ -9578,7 +9598,7 @@
       <c r="P446" s="4"/>
       <c r="Q446" s="4"/>
     </row>
-    <row r="447" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A447" s="6"/>
       <c r="B447" s="4"/>
       <c r="C447" s="4"/>
@@ -9597,7 +9617,7 @@
       <c r="P447" s="4"/>
       <c r="Q447" s="4"/>
     </row>
-    <row r="448" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A448" s="6"/>
       <c r="B448" s="4"/>
       <c r="C448" s="4"/>
@@ -9616,7 +9636,7 @@
       <c r="P448" s="4"/>
       <c r="Q448" s="4"/>
     </row>
-    <row r="449" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A449" s="6"/>
       <c r="B449" s="4"/>
       <c r="C449" s="4"/>
@@ -9635,7 +9655,7 @@
       <c r="P449" s="4"/>
       <c r="Q449" s="4"/>
     </row>
-    <row r="450" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A450" s="6"/>
       <c r="B450" s="4"/>
       <c r="C450" s="4"/>
@@ -9654,7 +9674,7 @@
       <c r="P450" s="4"/>
       <c r="Q450" s="4"/>
     </row>
-    <row r="451" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A451" s="6"/>
       <c r="B451" s="4"/>
       <c r="C451" s="4"/>
@@ -9673,7 +9693,7 @@
       <c r="P451" s="4"/>
       <c r="Q451" s="4"/>
     </row>
-    <row r="452" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A452" s="6"/>
       <c r="B452" s="4"/>
       <c r="C452" s="4"/>
@@ -9692,7 +9712,7 @@
       <c r="P452" s="4"/>
       <c r="Q452" s="4"/>
     </row>
-    <row r="453" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A453" s="6"/>
       <c r="B453" s="4"/>
       <c r="C453" s="4"/>
@@ -9711,7 +9731,7 @@
       <c r="P453" s="4"/>
       <c r="Q453" s="4"/>
     </row>
-    <row r="454" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A454" s="6"/>
       <c r="B454" s="4"/>
       <c r="C454" s="4"/>
@@ -9730,7 +9750,7 @@
       <c r="P454" s="4"/>
       <c r="Q454" s="4"/>
     </row>
-    <row r="455" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A455" s="6"/>
       <c r="B455" s="4"/>
       <c r="C455" s="4"/>
@@ -9749,7 +9769,7 @@
       <c r="P455" s="4"/>
       <c r="Q455" s="4"/>
     </row>
-    <row r="456" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A456" s="6"/>
       <c r="B456" s="4"/>
       <c r="C456" s="4"/>
@@ -9768,7 +9788,7 @@
       <c r="P456" s="4"/>
       <c r="Q456" s="4"/>
     </row>
-    <row r="457" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A457" s="6"/>
       <c r="B457" s="4"/>
       <c r="C457" s="4"/>
@@ -9787,7 +9807,7 @@
       <c r="P457" s="4"/>
       <c r="Q457" s="4"/>
     </row>
-    <row r="458" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A458" s="6"/>
       <c r="B458" s="4"/>
       <c r="C458" s="4"/>
@@ -9806,7 +9826,7 @@
       <c r="P458" s="4"/>
       <c r="Q458" s="4"/>
     </row>
-    <row r="459" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A459" s="6"/>
       <c r="B459" s="4"/>
       <c r="C459" s="4"/>
@@ -9825,7 +9845,7 @@
       <c r="P459" s="4"/>
       <c r="Q459" s="4"/>
     </row>
-    <row r="460" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A460" s="6"/>
       <c r="B460" s="4"/>
       <c r="C460" s="4"/>
@@ -9844,7 +9864,7 @@
       <c r="P460" s="4"/>
       <c r="Q460" s="4"/>
     </row>
-    <row r="461" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A461" s="6"/>
       <c r="B461" s="4"/>
       <c r="C461" s="4"/>
@@ -9863,7 +9883,7 @@
       <c r="P461" s="4"/>
       <c r="Q461" s="4"/>
     </row>
-    <row r="462" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A462" s="6"/>
       <c r="B462" s="4"/>
       <c r="C462" s="4"/>
@@ -9882,7 +9902,7 @@
       <c r="P462" s="4"/>
       <c r="Q462" s="4"/>
     </row>
-    <row r="463" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A463" s="6"/>
       <c r="B463" s="4"/>
       <c r="C463" s="4"/>
@@ -9901,7 +9921,7 @@
       <c r="P463" s="4"/>
       <c r="Q463" s="4"/>
     </row>
-    <row r="464" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A464" s="6"/>
       <c r="B464" s="4"/>
       <c r="C464" s="4"/>
@@ -9920,7 +9940,7 @@
       <c r="P464" s="4"/>
       <c r="Q464" s="4"/>
     </row>
-    <row r="465" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A465" s="6"/>
       <c r="B465" s="4"/>
       <c r="C465" s="4"/>
@@ -9939,7 +9959,7 @@
       <c r="P465" s="4"/>
       <c r="Q465" s="4"/>
     </row>
-    <row r="466" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A466" s="6"/>
       <c r="B466" s="4"/>
       <c r="C466" s="4"/>
@@ -9958,7 +9978,7 @@
       <c r="P466" s="4"/>
       <c r="Q466" s="4"/>
     </row>
-    <row r="467" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A467" s="6"/>
       <c r="B467" s="4"/>
       <c r="C467" s="4"/>
@@ -9977,7 +9997,7 @@
       <c r="P467" s="4"/>
       <c r="Q467" s="4"/>
     </row>
-    <row r="468" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A468" s="6"/>
       <c r="B468" s="4"/>
       <c r="C468" s="4"/>
@@ -9996,7 +10016,7 @@
       <c r="P468" s="4"/>
       <c r="Q468" s="4"/>
     </row>
-    <row r="469" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A469" s="6"/>
       <c r="B469" s="4"/>
       <c r="C469" s="4"/>
@@ -10015,7 +10035,7 @@
       <c r="P469" s="4"/>
       <c r="Q469" s="4"/>
     </row>
-    <row r="470" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A470" s="6"/>
       <c r="B470" s="4"/>
       <c r="C470" s="4"/>
@@ -10034,7 +10054,7 @@
       <c r="P470" s="4"/>
       <c r="Q470" s="4"/>
     </row>
-    <row r="471" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A471" s="6"/>
       <c r="B471" s="4"/>
       <c r="C471" s="4"/>
@@ -10053,7 +10073,7 @@
       <c r="P471" s="4"/>
       <c r="Q471" s="4"/>
     </row>
-    <row r="472" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A472" s="6"/>
       <c r="B472" s="4"/>
       <c r="C472" s="4"/>
@@ -10072,7 +10092,7 @@
       <c r="P472" s="4"/>
       <c r="Q472" s="4"/>
     </row>
-    <row r="473" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A473" s="6"/>
       <c r="B473" s="4"/>
       <c r="C473" s="4"/>
@@ -10091,7 +10111,7 @@
       <c r="P473" s="4"/>
       <c r="Q473" s="4"/>
     </row>
-    <row r="474" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A474" s="6"/>
       <c r="B474" s="4"/>
       <c r="C474" s="4"/>
@@ -10110,7 +10130,7 @@
       <c r="P474" s="4"/>
       <c r="Q474" s="4"/>
     </row>
-    <row r="475" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A475" s="6"/>
       <c r="B475" s="4"/>
       <c r="C475" s="4"/>
@@ -10129,7 +10149,7 @@
       <c r="P475" s="4"/>
       <c r="Q475" s="4"/>
     </row>
-    <row r="476" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A476" s="6"/>
       <c r="B476" s="4"/>
       <c r="C476" s="4"/>
@@ -10148,7 +10168,7 @@
       <c r="P476" s="4"/>
       <c r="Q476" s="4"/>
     </row>
-    <row r="477" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A477" s="6"/>
       <c r="B477" s="4"/>
       <c r="C477" s="4"/>
@@ -10167,7 +10187,7 @@
       <c r="P477" s="4"/>
       <c r="Q477" s="4"/>
     </row>
-    <row r="478" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A478" s="6"/>
       <c r="B478" s="4"/>
       <c r="C478" s="4"/>
@@ -10186,7 +10206,7 @@
       <c r="P478" s="4"/>
       <c r="Q478" s="4"/>
     </row>
-    <row r="479" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A479" s="6"/>
       <c r="B479" s="4"/>
       <c r="C479" s="4"/>
@@ -10205,7 +10225,7 @@
       <c r="P479" s="4"/>
       <c r="Q479" s="4"/>
     </row>
-    <row r="480" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A480" s="6"/>
       <c r="B480" s="4"/>
       <c r="C480" s="4"/>
@@ -10224,7 +10244,7 @@
       <c r="P480" s="4"/>
       <c r="Q480" s="4"/>
     </row>
-    <row r="481" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A481" s="6"/>
       <c r="B481" s="4"/>
       <c r="C481" s="4"/>
@@ -10243,7 +10263,7 @@
       <c r="P481" s="4"/>
       <c r="Q481" s="4"/>
     </row>
-    <row r="482" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A482" s="6"/>
       <c r="B482" s="4"/>
       <c r="C482" s="4"/>
@@ -10262,7 +10282,7 @@
       <c r="P482" s="4"/>
       <c r="Q482" s="4"/>
     </row>
-    <row r="483" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A483" s="6"/>
       <c r="B483" s="4"/>
       <c r="C483" s="4"/>
@@ -10281,7 +10301,7 @@
       <c r="P483" s="4"/>
       <c r="Q483" s="4"/>
     </row>
-    <row r="484" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A484" s="6"/>
       <c r="B484" s="4"/>
       <c r="C484" s="4"/>
@@ -10300,7 +10320,7 @@
       <c r="P484" s="4"/>
       <c r="Q484" s="4"/>
     </row>
-    <row r="485" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A485" s="6"/>
       <c r="B485" s="4"/>
       <c r="C485" s="4"/>
@@ -10319,7 +10339,7 @@
       <c r="P485" s="4"/>
       <c r="Q485" s="4"/>
     </row>
-    <row r="486" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A486" s="6"/>
       <c r="B486" s="4"/>
       <c r="C486" s="4"/>
@@ -10338,7 +10358,7 @@
       <c r="P486" s="4"/>
       <c r="Q486" s="4"/>
     </row>
-    <row r="487" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A487" s="6"/>
       <c r="B487" s="4"/>
       <c r="C487" s="4"/>
@@ -10357,7 +10377,7 @@
       <c r="P487" s="4"/>
       <c r="Q487" s="4"/>
     </row>
-    <row r="488" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A488" s="6"/>
       <c r="B488" s="4"/>
       <c r="C488" s="4"/>
@@ -10376,7 +10396,7 @@
       <c r="P488" s="4"/>
       <c r="Q488" s="4"/>
     </row>
-    <row r="489" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A489" s="6"/>
       <c r="B489" s="4"/>
       <c r="C489" s="4"/>
@@ -10395,7 +10415,7 @@
       <c r="P489" s="4"/>
       <c r="Q489" s="4"/>
     </row>
-    <row r="490" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A490" s="6"/>
       <c r="B490" s="4"/>
       <c r="C490" s="4"/>
@@ -10414,7 +10434,7 @@
       <c r="P490" s="4"/>
       <c r="Q490" s="4"/>
     </row>
-    <row r="491" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A491" s="6"/>
       <c r="B491" s="4"/>
       <c r="C491" s="4"/>
@@ -10433,7 +10453,7 @@
       <c r="P491" s="4"/>
       <c r="Q491" s="4"/>
     </row>
-    <row r="492" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A492" s="6"/>
       <c r="B492" s="4"/>
       <c r="C492" s="4"/>
@@ -10452,7 +10472,7 @@
       <c r="P492" s="4"/>
       <c r="Q492" s="4"/>
     </row>
-    <row r="493" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A493" s="6"/>
       <c r="B493" s="4"/>
       <c r="C493" s="4"/>
@@ -10471,7 +10491,7 @@
       <c r="P493" s="4"/>
       <c r="Q493" s="4"/>
     </row>
-    <row r="494" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A494" s="6"/>
       <c r="B494" s="4"/>
       <c r="C494" s="4"/>
@@ -10490,7 +10510,7 @@
       <c r="P494" s="4"/>
       <c r="Q494" s="4"/>
     </row>
-    <row r="495" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A495" s="6"/>
       <c r="B495" s="4"/>
       <c r="C495" s="4"/>
@@ -10509,7 +10529,7 @@
       <c r="P495" s="4"/>
       <c r="Q495" s="4"/>
     </row>
-    <row r="496" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A496" s="6"/>
       <c r="B496" s="4"/>
       <c r="C496" s="4"/>
@@ -10528,7 +10548,7 @@
       <c r="P496" s="4"/>
       <c r="Q496" s="4"/>
     </row>
-    <row r="497" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A497" s="6"/>
       <c r="B497" s="4"/>
       <c r="C497" s="4"/>
@@ -10547,7 +10567,7 @@
       <c r="P497" s="4"/>
       <c r="Q497" s="4"/>
     </row>
-    <row r="498" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A498" s="6"/>
       <c r="B498" s="4"/>
       <c r="C498" s="4"/>
@@ -10566,7 +10586,7 @@
       <c r="P498" s="4"/>
       <c r="Q498" s="4"/>
     </row>
-    <row r="499" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A499" s="6"/>
       <c r="B499" s="4"/>
       <c r="C499" s="4"/>
@@ -10585,7 +10605,7 @@
       <c r="P499" s="4"/>
       <c r="Q499" s="4"/>
     </row>
-    <row r="500" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A500" s="6"/>
       <c r="B500" s="4"/>
       <c r="C500" s="4"/>
@@ -10604,7 +10624,7 @@
       <c r="P500" s="4"/>
       <c r="Q500" s="4"/>
     </row>
-    <row r="501" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A501" s="6"/>
       <c r="B501" s="4"/>
       <c r="C501" s="4"/>
@@ -10623,7 +10643,7 @@
       <c r="P501" s="4"/>
       <c r="Q501" s="4"/>
     </row>
-    <row r="502" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A502" s="6"/>
       <c r="B502" s="4"/>
       <c r="C502" s="4"/>
@@ -10642,7 +10662,7 @@
       <c r="P502" s="4"/>
       <c r="Q502" s="4"/>
     </row>
-    <row r="503" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A503" s="6"/>
       <c r="B503" s="4"/>
       <c r="C503" s="4"/>
@@ -10661,7 +10681,7 @@
       <c r="P503" s="4"/>
       <c r="Q503" s="4"/>
     </row>
-    <row r="504" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A504" s="6"/>
       <c r="B504" s="4"/>
       <c r="C504" s="4"/>
@@ -10680,7 +10700,7 @@
       <c r="P504" s="4"/>
       <c r="Q504" s="4"/>
     </row>
-    <row r="505" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A505" s="6"/>
       <c r="B505" s="4"/>
       <c r="C505" s="4"/>
@@ -10699,7 +10719,7 @@
       <c r="P505" s="4"/>
       <c r="Q505" s="4"/>
     </row>
-    <row r="506" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A506" s="6"/>
       <c r="B506" s="4"/>
       <c r="C506" s="4"/>
@@ -10718,7 +10738,7 @@
       <c r="P506" s="4"/>
       <c r="Q506" s="4"/>
     </row>
-    <row r="507" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A507" s="6"/>
       <c r="B507" s="4"/>
       <c r="C507" s="4"/>
@@ -10737,7 +10757,7 @@
       <c r="P507" s="4"/>
       <c r="Q507" s="4"/>
     </row>
-    <row r="508" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A508" s="6"/>
       <c r="B508" s="4"/>
       <c r="C508" s="4"/>
@@ -10756,7 +10776,7 @@
       <c r="P508" s="4"/>
       <c r="Q508" s="4"/>
     </row>
-    <row r="509" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A509" s="6"/>
       <c r="B509" s="4"/>
       <c r="C509" s="4"/>
@@ -10775,7 +10795,7 @@
       <c r="P509" s="4"/>
       <c r="Q509" s="4"/>
     </row>
-    <row r="510" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A510" s="6"/>
       <c r="B510" s="4"/>
       <c r="C510" s="4"/>
@@ -10794,7 +10814,7 @@
       <c r="P510" s="4"/>
       <c r="Q510" s="4"/>
     </row>
-    <row r="511" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A511" s="6"/>
       <c r="B511" s="4"/>
       <c r="C511" s="4"/>
@@ -10813,7 +10833,7 @@
       <c r="P511" s="4"/>
       <c r="Q511" s="4"/>
     </row>
-    <row r="512" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A512" s="6"/>
       <c r="B512" s="4"/>
       <c r="C512" s="4"/>
@@ -10832,7 +10852,7 @@
       <c r="P512" s="4"/>
       <c r="Q512" s="4"/>
     </row>
-    <row r="513" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A513" s="6"/>
       <c r="B513" s="4"/>
       <c r="C513" s="4"/>
@@ -10851,7 +10871,7 @@
       <c r="P513" s="4"/>
       <c r="Q513" s="4"/>
     </row>
-    <row r="514" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A514" s="6"/>
       <c r="B514" s="4"/>
       <c r="C514" s="4"/>
@@ -10870,7 +10890,7 @@
       <c r="P514" s="4"/>
       <c r="Q514" s="4"/>
     </row>
-    <row r="515" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A515" s="6"/>
       <c r="B515" s="4"/>
       <c r="C515" s="4"/>
@@ -10889,7 +10909,7 @@
       <c r="P515" s="4"/>
       <c r="Q515" s="4"/>
     </row>
-    <row r="516" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A516" s="6"/>
       <c r="B516" s="4"/>
       <c r="C516" s="4"/>
@@ -10908,7 +10928,7 @@
       <c r="P516" s="4"/>
       <c r="Q516" s="4"/>
     </row>
-    <row r="517" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A517" s="6"/>
       <c r="B517" s="4"/>
       <c r="C517" s="4"/>
@@ -10927,7 +10947,7 @@
       <c r="P517" s="4"/>
       <c r="Q517" s="4"/>
     </row>
-    <row r="518" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A518" s="6"/>
       <c r="B518" s="4"/>
       <c r="C518" s="4"/>
@@ -10946,7 +10966,7 @@
       <c r="P518" s="4"/>
       <c r="Q518" s="4"/>
     </row>
-    <row r="519" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A519" s="6"/>
       <c r="B519" s="4"/>
       <c r="C519" s="4"/>
@@ -10965,7 +10985,7 @@
       <c r="P519" s="4"/>
       <c r="Q519" s="4"/>
     </row>
-    <row r="520" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A520" s="6"/>
       <c r="B520" s="4"/>
       <c r="C520" s="4"/>
@@ -10984,7 +11004,7 @@
       <c r="P520" s="4"/>
       <c r="Q520" s="4"/>
     </row>
-    <row r="521" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A521" s="6"/>
       <c r="B521" s="4"/>
       <c r="C521" s="4"/>
@@ -11003,7 +11023,7 @@
       <c r="P521" s="4"/>
       <c r="Q521" s="4"/>
     </row>
-    <row r="522" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A522" s="6"/>
       <c r="B522" s="4"/>
       <c r="C522" s="4"/>
@@ -11022,7 +11042,7 @@
       <c r="P522" s="4"/>
       <c r="Q522" s="4"/>
     </row>
-    <row r="523" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A523" s="6"/>
       <c r="B523" s="4"/>
       <c r="C523" s="4"/>
@@ -11041,7 +11061,7 @@
       <c r="P523" s="4"/>
       <c r="Q523" s="4"/>
     </row>
-    <row r="524" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A524" s="6"/>
       <c r="B524" s="4"/>
       <c r="C524" s="4"/>
@@ -11060,7 +11080,7 @@
       <c r="P524" s="4"/>
       <c r="Q524" s="4"/>
     </row>
-    <row r="525" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A525" s="6"/>
       <c r="B525" s="4"/>
       <c r="C525" s="4"/>
@@ -11079,7 +11099,7 @@
       <c r="P525" s="4"/>
       <c r="Q525" s="4"/>
     </row>
-    <row r="526" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A526" s="6"/>
       <c r="B526" s="4"/>
       <c r="C526" s="4"/>
@@ -11098,7 +11118,7 @@
       <c r="P526" s="4"/>
       <c r="Q526" s="4"/>
     </row>
-    <row r="527" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A527" s="6"/>
       <c r="B527" s="4"/>
       <c r="C527" s="4"/>
@@ -11117,7 +11137,7 @@
       <c r="P527" s="4"/>
       <c r="Q527" s="4"/>
     </row>
-    <row r="528" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A528" s="6"/>
       <c r="B528" s="4"/>
       <c r="C528" s="4"/>
@@ -11136,7 +11156,7 @@
       <c r="P528" s="4"/>
       <c r="Q528" s="4"/>
     </row>
-    <row r="529" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A529" s="6"/>
       <c r="B529" s="4"/>
       <c r="C529" s="4"/>
@@ -11155,7 +11175,7 @@
       <c r="P529" s="4"/>
       <c r="Q529" s="4"/>
     </row>
-    <row r="530" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A530" s="6"/>
       <c r="B530" s="4"/>
       <c r="C530" s="4"/>
@@ -11174,7 +11194,7 @@
       <c r="P530" s="4"/>
       <c r="Q530" s="4"/>
     </row>
-    <row r="531" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A531" s="6"/>
       <c r="B531" s="4"/>
       <c r="C531" s="4"/>
@@ -11193,7 +11213,7 @@
       <c r="P531" s="4"/>
       <c r="Q531" s="4"/>
     </row>
-    <row r="532" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A532" s="6"/>
       <c r="B532" s="4"/>
       <c r="C532" s="4"/>
@@ -11212,7 +11232,7 @@
       <c r="P532" s="4"/>
       <c r="Q532" s="4"/>
     </row>
-    <row r="533" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A533" s="6"/>
       <c r="B533" s="4"/>
       <c r="C533" s="4"/>
@@ -11231,7 +11251,7 @@
       <c r="P533" s="4"/>
       <c r="Q533" s="4"/>
     </row>
-    <row r="534" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A534" s="6"/>
       <c r="B534" s="4"/>
       <c r="C534" s="4"/>
@@ -11250,7 +11270,7 @@
       <c r="P534" s="4"/>
       <c r="Q534" s="4"/>
     </row>
-    <row r="535" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A535" s="6"/>
       <c r="B535" s="4"/>
       <c r="C535" s="4"/>
@@ -11269,7 +11289,7 @@
       <c r="P535" s="4"/>
       <c r="Q535" s="4"/>
     </row>
-    <row r="536" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A536" s="6"/>
       <c r="B536" s="4"/>
       <c r="C536" s="4"/>
@@ -11288,7 +11308,7 @@
       <c r="P536" s="4"/>
       <c r="Q536" s="4"/>
     </row>
-    <row r="537" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A537" s="6"/>
       <c r="B537" s="4"/>
       <c r="C537" s="4"/>
@@ -11307,7 +11327,7 @@
       <c r="P537" s="4"/>
       <c r="Q537" s="4"/>
     </row>
-    <row r="538" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A538" s="6"/>
       <c r="B538" s="4"/>
       <c r="C538" s="4"/>
@@ -11326,7 +11346,7 @@
       <c r="P538" s="4"/>
       <c r="Q538" s="4"/>
     </row>
-    <row r="539" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A539" s="6"/>
       <c r="B539" s="4"/>
       <c r="C539" s="4"/>
@@ -11345,7 +11365,7 @@
       <c r="P539" s="4"/>
       <c r="Q539" s="4"/>
     </row>
-    <row r="540" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A540" s="6"/>
       <c r="B540" s="4"/>
       <c r="C540" s="4"/>
@@ -11364,7 +11384,7 @@
       <c r="P540" s="4"/>
       <c r="Q540" s="4"/>
     </row>
-    <row r="541" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A541" s="6"/>
       <c r="B541" s="4"/>
       <c r="C541" s="4"/>
@@ -11383,7 +11403,7 @@
       <c r="P541" s="4"/>
       <c r="Q541" s="4"/>
     </row>
-    <row r="542" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A542" s="6"/>
       <c r="B542" s="4"/>
       <c r="C542" s="4"/>
@@ -11402,7 +11422,7 @@
       <c r="P542" s="4"/>
       <c r="Q542" s="4"/>
     </row>
-    <row r="543" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A543" s="6"/>
       <c r="B543" s="4"/>
       <c r="C543" s="4"/>
@@ -11421,7 +11441,7 @@
       <c r="P543" s="4"/>
       <c r="Q543" s="4"/>
     </row>
-    <row r="544" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A544" s="6"/>
       <c r="B544" s="4"/>
       <c r="C544" s="4"/>
@@ -11440,7 +11460,7 @@
       <c r="P544" s="4"/>
       <c r="Q544" s="4"/>
     </row>
-    <row r="545" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A545" s="6"/>
       <c r="B545" s="4"/>
       <c r="C545" s="4"/>
@@ -11459,7 +11479,7 @@
       <c r="P545" s="4"/>
       <c r="Q545" s="4"/>
     </row>
-    <row r="546" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A546" s="6"/>
       <c r="B546" s="4"/>
       <c r="C546" s="4"/>
@@ -11478,7 +11498,7 @@
       <c r="P546" s="4"/>
       <c r="Q546" s="4"/>
     </row>
-    <row r="547" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A547" s="6"/>
       <c r="B547" s="4"/>
       <c r="C547" s="4"/>
@@ -11497,7 +11517,7 @@
       <c r="P547" s="4"/>
       <c r="Q547" s="4"/>
     </row>
-    <row r="548" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A548" s="6"/>
       <c r="B548" s="4"/>
       <c r="C548" s="4"/>
@@ -11516,7 +11536,7 @@
       <c r="P548" s="4"/>
       <c r="Q548" s="4"/>
     </row>
-    <row r="549" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A549" s="6"/>
       <c r="B549" s="4"/>
       <c r="C549" s="4"/>
@@ -11535,7 +11555,7 @@
       <c r="P549" s="4"/>
       <c r="Q549" s="4"/>
     </row>
-    <row r="550" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A550" s="6"/>
       <c r="B550" s="4"/>
       <c r="C550" s="4"/>
@@ -11554,7 +11574,7 @@
       <c r="P550" s="4"/>
       <c r="Q550" s="4"/>
     </row>
-    <row r="551" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A551" s="6"/>
       <c r="B551" s="4"/>
       <c r="C551" s="4"/>
@@ -11573,7 +11593,7 @@
       <c r="P551" s="4"/>
       <c r="Q551" s="4"/>
     </row>
-    <row r="552" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A552" s="6"/>
       <c r="B552" s="4"/>
       <c r="C552" s="4"/>
@@ -11592,7 +11612,7 @@
       <c r="P552" s="4"/>
       <c r="Q552" s="4"/>
     </row>
-    <row r="553" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A553" s="6"/>
       <c r="B553" s="4"/>
       <c r="C553" s="4"/>
@@ -11611,7 +11631,7 @@
       <c r="P553" s="4"/>
       <c r="Q553" s="4"/>
     </row>
-    <row r="554" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A554" s="6"/>
       <c r="B554" s="4"/>
       <c r="C554" s="4"/>
@@ -11630,7 +11650,7 @@
       <c r="P554" s="4"/>
       <c r="Q554" s="4"/>
     </row>
-    <row r="555" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A555" s="6"/>
       <c r="B555" s="4"/>
       <c r="C555" s="4"/>
@@ -11649,7 +11669,7 @@
       <c r="P555" s="4"/>
       <c r="Q555" s="4"/>
     </row>
-    <row r="556" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A556" s="6"/>
       <c r="B556" s="4"/>
       <c r="C556" s="4"/>
@@ -11668,7 +11688,7 @@
       <c r="P556" s="4"/>
       <c r="Q556" s="4"/>
     </row>
-    <row r="557" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A557" s="6"/>
       <c r="B557" s="4"/>
       <c r="C557" s="4"/>
@@ -11687,7 +11707,7 @@
       <c r="P557" s="4"/>
       <c r="Q557" s="4"/>
     </row>
-    <row r="558" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A558" s="6"/>
       <c r="B558" s="4"/>
       <c r="C558" s="4"/>
@@ -11706,7 +11726,7 @@
       <c r="P558" s="4"/>
       <c r="Q558" s="4"/>
     </row>
-    <row r="559" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A559" s="6"/>
       <c r="B559" s="4"/>
       <c r="C559" s="4"/>
@@ -11725,7 +11745,7 @@
       <c r="P559" s="4"/>
       <c r="Q559" s="4"/>
     </row>
-    <row r="560" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A560" s="6"/>
       <c r="B560" s="4"/>
       <c r="C560" s="4"/>
@@ -11744,7 +11764,7 @@
       <c r="P560" s="4"/>
       <c r="Q560" s="4"/>
     </row>
-    <row r="561" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A561" s="6"/>
       <c r="B561" s="4"/>
       <c r="C561" s="4"/>
@@ -11763,7 +11783,7 @@
       <c r="P561" s="4"/>
       <c r="Q561" s="4"/>
     </row>
-    <row r="562" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A562" s="6"/>
       <c r="B562" s="4"/>
       <c r="C562" s="4"/>
@@ -11782,7 +11802,7 @@
       <c r="P562" s="4"/>
       <c r="Q562" s="4"/>
     </row>
-    <row r="563" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A563" s="6"/>
       <c r="B563" s="4"/>
       <c r="C563" s="4"/>
@@ -11801,7 +11821,7 @@
       <c r="P563" s="4"/>
       <c r="Q563" s="4"/>
     </row>
-    <row r="564" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A564" s="6"/>
       <c r="B564" s="4"/>
       <c r="C564" s="4"/>
@@ -11820,7 +11840,7 @@
       <c r="P564" s="4"/>
       <c r="Q564" s="4"/>
     </row>
-    <row r="565" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A565" s="6"/>
       <c r="B565" s="4"/>
       <c r="C565" s="4"/>
@@ -11839,7 +11859,7 @@
       <c r="P565" s="4"/>
       <c r="Q565" s="4"/>
     </row>
-    <row r="566" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A566" s="6"/>
       <c r="B566" s="4"/>
       <c r="C566" s="4"/>
@@ -11858,7 +11878,7 @@
       <c r="P566" s="4"/>
       <c r="Q566" s="4"/>
     </row>
-    <row r="567" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A567" s="6"/>
       <c r="B567" s="4"/>
       <c r="C567" s="4"/>
@@ -11877,7 +11897,7 @@
       <c r="P567" s="4"/>
       <c r="Q567" s="4"/>
     </row>
-    <row r="568" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A568" s="6"/>
       <c r="B568" s="4"/>
       <c r="C568" s="4"/>
@@ -11896,7 +11916,7 @@
       <c r="P568" s="4"/>
       <c r="Q568" s="4"/>
     </row>
-    <row r="569" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A569" s="6"/>
       <c r="B569" s="4"/>
       <c r="C569" s="4"/>
@@ -11915,7 +11935,7 @@
       <c r="P569" s="4"/>
       <c r="Q569" s="4"/>
     </row>
-    <row r="570" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A570" s="6"/>
       <c r="B570" s="4"/>
       <c r="C570" s="4"/>
@@ -11934,7 +11954,7 @@
       <c r="P570" s="4"/>
       <c r="Q570" s="4"/>
     </row>
-    <row r="571" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A571" s="6"/>
       <c r="B571" s="4"/>
       <c r="C571" s="4"/>
@@ -11953,7 +11973,7 @@
       <c r="P571" s="4"/>
       <c r="Q571" s="4"/>
     </row>
-    <row r="572" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A572" s="6"/>
       <c r="B572" s="4"/>
       <c r="C572" s="4"/>
@@ -11972,7 +11992,7 @@
       <c r="P572" s="4"/>
       <c r="Q572" s="4"/>
     </row>
-    <row r="573" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A573" s="6"/>
       <c r="B573" s="4"/>
       <c r="C573" s="4"/>
@@ -11991,7 +12011,7 @@
       <c r="P573" s="4"/>
       <c r="Q573" s="4"/>
     </row>
-    <row r="574" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A574" s="6"/>
       <c r="B574" s="4"/>
       <c r="C574" s="4"/>
@@ -12010,7 +12030,7 @@
       <c r="P574" s="4"/>
       <c r="Q574" s="4"/>
     </row>
-    <row r="575" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A575" s="6"/>
       <c r="B575" s="4"/>
       <c r="C575" s="4"/>
@@ -12029,7 +12049,7 @@
       <c r="P575" s="4"/>
       <c r="Q575" s="4"/>
     </row>
-    <row r="576" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A576" s="6"/>
       <c r="B576" s="4"/>
       <c r="C576" s="4"/>
@@ -12048,7 +12068,7 @@
       <c r="P576" s="4"/>
       <c r="Q576" s="4"/>
     </row>
-    <row r="577" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A577" s="6"/>
       <c r="B577" s="4"/>
       <c r="C577" s="4"/>
@@ -12067,7 +12087,7 @@
       <c r="P577" s="4"/>
       <c r="Q577" s="4"/>
     </row>
-    <row r="578" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A578" s="6"/>
       <c r="B578" s="4"/>
       <c r="C578" s="4"/>
@@ -12086,7 +12106,7 @@
       <c r="P578" s="4"/>
       <c r="Q578" s="4"/>
     </row>
-    <row r="579" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A579" s="6"/>
       <c r="B579" s="4"/>
       <c r="C579" s="4"/>
@@ -12105,7 +12125,7 @@
       <c r="P579" s="4"/>
       <c r="Q579" s="4"/>
     </row>
-    <row r="580" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A580" s="6"/>
       <c r="B580" s="4"/>
       <c r="C580" s="4"/>
@@ -12124,7 +12144,7 @@
       <c r="P580" s="4"/>
       <c r="Q580" s="4"/>
     </row>
-    <row r="581" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A581" s="6"/>
       <c r="B581" s="4"/>
       <c r="C581" s="4"/>
@@ -12143,7 +12163,7 @@
       <c r="P581" s="4"/>
       <c r="Q581" s="4"/>
     </row>
-    <row r="582" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A582" s="6"/>
       <c r="B582" s="4"/>
       <c r="C582" s="4"/>
@@ -12162,7 +12182,7 @@
       <c r="P582" s="4"/>
       <c r="Q582" s="4"/>
     </row>
-    <row r="583" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A583" s="6"/>
       <c r="B583" s="4"/>
       <c r="C583" s="4"/>
@@ -12181,7 +12201,7 @@
       <c r="P583" s="4"/>
       <c r="Q583" s="4"/>
     </row>
-    <row r="584" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A584" s="6"/>
       <c r="B584" s="4"/>
       <c r="C584" s="4"/>
@@ -12200,7 +12220,7 @@
       <c r="P584" s="4"/>
       <c r="Q584" s="4"/>
     </row>
-    <row r="585" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A585" s="6"/>
       <c r="B585" s="4"/>
       <c r="C585" s="4"/>
@@ -12219,7 +12239,7 @@
       <c r="P585" s="4"/>
       <c r="Q585" s="4"/>
     </row>
-    <row r="586" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A586" s="6"/>
       <c r="B586" s="4"/>
       <c r="C586" s="4"/>
@@ -12238,7 +12258,7 @@
       <c r="P586" s="4"/>
       <c r="Q586" s="4"/>
     </row>
-    <row r="587" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A587" s="6"/>
       <c r="B587" s="4"/>
       <c r="C587" s="4"/>
@@ -12257,7 +12277,7 @@
       <c r="P587" s="4"/>
       <c r="Q587" s="4"/>
     </row>
-    <row r="588" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A588" s="6"/>
       <c r="B588" s="4"/>
       <c r="C588" s="4"/>
@@ -12276,7 +12296,7 @@
       <c r="P588" s="4"/>
       <c r="Q588" s="4"/>
     </row>
-    <row r="589" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A589" s="6"/>
       <c r="B589" s="4"/>
       <c r="C589" s="4"/>
@@ -12295,7 +12315,7 @@
       <c r="P589" s="4"/>
       <c r="Q589" s="4"/>
     </row>
-    <row r="590" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A590" s="6"/>
       <c r="B590" s="4"/>
       <c r="C590" s="4"/>
@@ -12314,7 +12334,7 @@
       <c r="P590" s="4"/>
       <c r="Q590" s="4"/>
     </row>
-    <row r="591" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A591" s="6"/>
       <c r="B591" s="4"/>
       <c r="C591" s="4"/>
@@ -12333,7 +12353,7 @@
       <c r="P591" s="4"/>
       <c r="Q591" s="4"/>
     </row>
-    <row r="592" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A592" s="6"/>
       <c r="B592" s="4"/>
       <c r="C592" s="4"/>
@@ -12352,7 +12372,7 @@
       <c r="P592" s="4"/>
       <c r="Q592" s="4"/>
     </row>
-    <row r="593" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A593" s="6"/>
       <c r="B593" s="4"/>
       <c r="C593" s="4"/>
@@ -12371,7 +12391,7 @@
       <c r="P593" s="4"/>
       <c r="Q593" s="4"/>
     </row>
-    <row r="594" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A594" s="6"/>
       <c r="B594" s="4"/>
       <c r="C594" s="4"/>
@@ -12390,7 +12410,7 @@
       <c r="P594" s="4"/>
       <c r="Q594" s="4"/>
     </row>
-    <row r="595" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A595" s="6"/>
       <c r="B595" s="4"/>
       <c r="C595" s="4"/>
@@ -12409,7 +12429,7 @@
       <c r="P595" s="4"/>
       <c r="Q595" s="4"/>
     </row>
-    <row r="596" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A596" s="6"/>
       <c r="B596" s="4"/>
       <c r="C596" s="4"/>
@@ -12428,7 +12448,7 @@
       <c r="P596" s="4"/>
       <c r="Q596" s="4"/>
     </row>
-    <row r="597" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A597" s="6"/>
       <c r="B597" s="4"/>
       <c r="C597" s="4"/>
@@ -12447,7 +12467,7 @@
       <c r="P597" s="4"/>
       <c r="Q597" s="4"/>
     </row>
-    <row r="598" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A598" s="6"/>
       <c r="B598" s="4"/>
       <c r="C598" s="4"/>
@@ -12466,7 +12486,7 @@
       <c r="P598" s="4"/>
       <c r="Q598" s="4"/>
     </row>
-    <row r="599" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A599" s="6"/>
       <c r="B599" s="4"/>
       <c r="C599" s="4"/>
@@ -12485,7 +12505,7 @@
       <c r="P599" s="4"/>
       <c r="Q599" s="4"/>
     </row>
-    <row r="600" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A600" s="6"/>
       <c r="B600" s="4"/>
       <c r="C600" s="4"/>
@@ -12504,7 +12524,7 @@
       <c r="P600" s="4"/>
       <c r="Q600" s="4"/>
     </row>
-    <row r="601" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A601" s="6"/>
       <c r="B601" s="4"/>
       <c r="C601" s="4"/>
@@ -12523,7 +12543,7 @@
       <c r="P601" s="4"/>
       <c r="Q601" s="4"/>
     </row>
-    <row r="602" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A602" s="6"/>
       <c r="B602" s="4"/>
       <c r="C602" s="4"/>
@@ -12542,7 +12562,7 @@
       <c r="P602" s="4"/>
       <c r="Q602" s="4"/>
     </row>
-    <row r="603" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A603" s="6"/>
       <c r="B603" s="4"/>
       <c r="C603" s="4"/>
@@ -12561,7 +12581,7 @@
       <c r="P603" s="4"/>
       <c r="Q603" s="4"/>
     </row>
-    <row r="604" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A604" s="6"/>
       <c r="B604" s="4"/>
       <c r="C604" s="4"/>
@@ -12580,7 +12600,7 @@
       <c r="P604" s="4"/>
       <c r="Q604" s="4"/>
     </row>
-    <row r="605" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A605" s="6"/>
       <c r="B605" s="4"/>
       <c r="C605" s="4"/>
@@ -12599,7 +12619,7 @@
       <c r="P605" s="4"/>
       <c r="Q605" s="4"/>
     </row>
-    <row r="606" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A606" s="6"/>
       <c r="B606" s="4"/>
       <c r="C606" s="4"/>
@@ -12618,7 +12638,7 @@
       <c r="P606" s="4"/>
       <c r="Q606" s="4"/>
     </row>
-    <row r="607" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A607" s="6"/>
       <c r="B607" s="4"/>
       <c r="C607" s="4"/>
@@ -12637,7 +12657,7 @@
       <c r="P607" s="4"/>
       <c r="Q607" s="4"/>
     </row>
-    <row r="608" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A608" s="6"/>
       <c r="B608" s="4"/>
       <c r="C608" s="4"/>
@@ -12656,7 +12676,7 @@
       <c r="P608" s="4"/>
       <c r="Q608" s="4"/>
     </row>
-    <row r="609" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A609" s="6"/>
       <c r="B609" s="4"/>
       <c r="C609" s="4"/>
@@ -12675,7 +12695,7 @@
       <c r="P609" s="4"/>
       <c r="Q609" s="4"/>
     </row>
-    <row r="610" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A610" s="6"/>
       <c r="B610" s="4"/>
       <c r="C610" s="4"/>
@@ -12694,7 +12714,7 @@
       <c r="P610" s="4"/>
       <c r="Q610" s="4"/>
     </row>
-    <row r="611" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A611" s="6"/>
       <c r="B611" s="4"/>
       <c r="C611" s="4"/>
@@ -12713,7 +12733,7 @@
       <c r="P611" s="4"/>
       <c r="Q611" s="4"/>
     </row>
-    <row r="612" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A612" s="6"/>
       <c r="B612" s="4"/>
       <c r="C612" s="4"/>
@@ -12732,7 +12752,7 @@
       <c r="P612" s="4"/>
       <c r="Q612" s="4"/>
     </row>
-    <row r="613" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="613" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A613" s="6"/>
       <c r="B613" s="4"/>
       <c r="C613" s="4"/>
@@ -12751,7 +12771,7 @@
       <c r="P613" s="4"/>
       <c r="Q613" s="4"/>
     </row>
-    <row r="614" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="614" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A614" s="6"/>
       <c r="B614" s="4"/>
       <c r="C614" s="4"/>
@@ -12770,7 +12790,7 @@
       <c r="P614" s="4"/>
       <c r="Q614" s="4"/>
     </row>
-    <row r="615" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="615" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A615" s="6"/>
       <c r="B615" s="4"/>
       <c r="C615" s="4"/>
@@ -12789,7 +12809,7 @@
       <c r="P615" s="4"/>
       <c r="Q615" s="4"/>
     </row>
-    <row r="616" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="616" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A616" s="6"/>
       <c r="B616" s="4"/>
       <c r="C616" s="4"/>
@@ -12808,7 +12828,7 @@
       <c r="P616" s="4"/>
       <c r="Q616" s="4"/>
     </row>
-    <row r="617" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="617" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A617" s="6"/>
       <c r="B617" s="4"/>
       <c r="C617" s="4"/>
@@ -12827,7 +12847,7 @@
       <c r="P617" s="4"/>
       <c r="Q617" s="4"/>
     </row>
-    <row r="618" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="618" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A618" s="6"/>
       <c r="B618" s="4"/>
       <c r="C618" s="4"/>
@@ -12846,7 +12866,7 @@
       <c r="P618" s="4"/>
       <c r="Q618" s="4"/>
     </row>
-    <row r="619" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="619" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A619" s="6"/>
       <c r="B619" s="4"/>
       <c r="C619" s="4"/>
@@ -12865,7 +12885,7 @@
       <c r="P619" s="4"/>
       <c r="Q619" s="4"/>
     </row>
-    <row r="620" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="620" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A620" s="6"/>
       <c r="B620" s="4"/>
       <c r="C620" s="4"/>
@@ -12884,7 +12904,7 @@
       <c r="P620" s="4"/>
       <c r="Q620" s="4"/>
     </row>
-    <row r="621" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="621" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A621" s="6"/>
       <c r="B621" s="4"/>
       <c r="C621" s="4"/>
@@ -12903,7 +12923,7 @@
       <c r="P621" s="4"/>
       <c r="Q621" s="4"/>
     </row>
-    <row r="622" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="622" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A622" s="6"/>
       <c r="B622" s="4"/>
       <c r="C622" s="4"/>
@@ -12922,7 +12942,7 @@
       <c r="P622" s="4"/>
       <c r="Q622" s="4"/>
     </row>
-    <row r="623" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="623" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A623" s="6"/>
       <c r="B623" s="4"/>
       <c r="C623" s="4"/>
@@ -12941,7 +12961,7 @@
       <c r="P623" s="4"/>
       <c r="Q623" s="4"/>
     </row>
-    <row r="624" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="624" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A624" s="6"/>
       <c r="B624" s="4"/>
       <c r="C624" s="4"/>
@@ -12960,7 +12980,7 @@
       <c r="P624" s="4"/>
       <c r="Q624" s="4"/>
     </row>
-    <row r="625" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="625" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A625" s="6"/>
       <c r="B625" s="4"/>
       <c r="C625" s="4"/>
@@ -12979,7 +12999,7 @@
       <c r="P625" s="4"/>
       <c r="Q625" s="4"/>
     </row>
-    <row r="626" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="626" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A626" s="6"/>
       <c r="B626" s="4"/>
       <c r="C626" s="4"/>
@@ -12998,7 +13018,7 @@
       <c r="P626" s="4"/>
       <c r="Q626" s="4"/>
     </row>
-    <row r="627" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="627" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A627" s="6"/>
       <c r="B627" s="4"/>
       <c r="C627" s="4"/>
@@ -13017,7 +13037,7 @@
       <c r="P627" s="4"/>
       <c r="Q627" s="4"/>
     </row>
-    <row r="628" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="628" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A628" s="6"/>
       <c r="B628" s="4"/>
       <c r="C628" s="4"/>
@@ -13036,7 +13056,7 @@
       <c r="P628" s="4"/>
       <c r="Q628" s="4"/>
     </row>
-    <row r="629" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="629" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A629" s="6"/>
       <c r="B629" s="4"/>
       <c r="C629" s="4"/>
@@ -13055,7 +13075,7 @@
       <c r="P629" s="4"/>
       <c r="Q629" s="4"/>
     </row>
-    <row r="630" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="630" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A630" s="6"/>
       <c r="B630" s="4"/>
       <c r="C630" s="4"/>
@@ -13074,7 +13094,7 @@
       <c r="P630" s="4"/>
       <c r="Q630" s="4"/>
     </row>
-    <row r="631" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="631" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A631" s="6"/>
       <c r="B631" s="4"/>
       <c r="C631" s="4"/>
@@ -13093,7 +13113,7 @@
       <c r="P631" s="4"/>
       <c r="Q631" s="4"/>
     </row>
-    <row r="632" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="632" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A632" s="6"/>
       <c r="B632" s="4"/>
       <c r="C632" s="4"/>
@@ -13112,7 +13132,7 @@
       <c r="P632" s="4"/>
       <c r="Q632" s="4"/>
     </row>
-    <row r="633" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="633" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A633" s="6"/>
       <c r="B633" s="4"/>
       <c r="C633" s="4"/>
@@ -13131,7 +13151,7 @@
       <c r="P633" s="4"/>
       <c r="Q633" s="4"/>
     </row>
-    <row r="634" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="634" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A634" s="6"/>
       <c r="B634" s="4"/>
       <c r="C634" s="4"/>
@@ -13150,7 +13170,7 @@
       <c r="P634" s="4"/>
       <c r="Q634" s="4"/>
     </row>
-    <row r="635" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="635" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A635" s="6"/>
       <c r="B635" s="4"/>
       <c r="C635" s="4"/>
@@ -13169,7 +13189,7 @@
       <c r="P635" s="4"/>
       <c r="Q635" s="4"/>
     </row>
-    <row r="636" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="636" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A636" s="6"/>
       <c r="B636" s="4"/>
       <c r="C636" s="4"/>
@@ -13188,7 +13208,7 @@
       <c r="P636" s="4"/>
       <c r="Q636" s="4"/>
     </row>
-    <row r="637" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="637" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A637" s="6"/>
       <c r="B637" s="4"/>
       <c r="C637" s="4"/>
@@ -13207,7 +13227,7 @@
       <c r="P637" s="4"/>
       <c r="Q637" s="4"/>
     </row>
-    <row r="638" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="638" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A638" s="6"/>
       <c r="B638" s="4"/>
       <c r="C638" s="4"/>
@@ -13226,7 +13246,7 @@
       <c r="P638" s="4"/>
       <c r="Q638" s="4"/>
     </row>
-    <row r="639" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="639" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A639" s="6"/>
       <c r="B639" s="4"/>
       <c r="C639" s="4"/>
@@ -13245,7 +13265,7 @@
       <c r="P639" s="4"/>
       <c r="Q639" s="4"/>
     </row>
-    <row r="640" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="640" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A640" s="6"/>
       <c r="B640" s="4"/>
       <c r="C640" s="4"/>
@@ -13264,7 +13284,7 @@
       <c r="P640" s="4"/>
       <c r="Q640" s="4"/>
     </row>
-    <row r="641" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="641" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A641" s="6"/>
       <c r="B641" s="4"/>
       <c r="C641" s="4"/>
@@ -13283,7 +13303,7 @@
       <c r="P641" s="4"/>
       <c r="Q641" s="4"/>
     </row>
-    <row r="642" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="642" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A642" s="6"/>
       <c r="B642" s="4"/>
       <c r="C642" s="4"/>
@@ -13302,7 +13322,7 @@
       <c r="P642" s="4"/>
       <c r="Q642" s="4"/>
     </row>
-    <row r="643" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="643" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A643" s="6"/>
       <c r="B643" s="4"/>
       <c r="C643" s="4"/>
@@ -13321,7 +13341,7 @@
       <c r="P643" s="4"/>
       <c r="Q643" s="4"/>
     </row>
-    <row r="644" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="644" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A644" s="6"/>
       <c r="B644" s="4"/>
       <c r="C644" s="4"/>
@@ -13340,7 +13360,7 @@
       <c r="P644" s="4"/>
       <c r="Q644" s="4"/>
     </row>
-    <row r="645" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="645" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A645" s="6"/>
       <c r="B645" s="4"/>
       <c r="C645" s="4"/>
@@ -13359,7 +13379,7 @@
       <c r="P645" s="4"/>
       <c r="Q645" s="4"/>
     </row>
-    <row r="646" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="646" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A646" s="6"/>
       <c r="B646" s="4"/>
       <c r="C646" s="4"/>
@@ -13378,7 +13398,7 @@
       <c r="P646" s="4"/>
       <c r="Q646" s="4"/>
     </row>
-    <row r="647" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="647" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A647" s="6"/>
       <c r="B647" s="4"/>
       <c r="C647" s="4"/>
@@ -13397,7 +13417,7 @@
       <c r="P647" s="4"/>
       <c r="Q647" s="4"/>
     </row>
-    <row r="648" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="648" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A648" s="6"/>
       <c r="B648" s="4"/>
       <c r="C648" s="4"/>
@@ -13416,7 +13436,7 @@
       <c r="P648" s="4"/>
       <c r="Q648" s="4"/>
     </row>
-    <row r="649" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="649" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A649" s="6"/>
       <c r="B649" s="4"/>
       <c r="C649" s="4"/>
@@ -13435,7 +13455,7 @@
       <c r="P649" s="4"/>
       <c r="Q649" s="4"/>
     </row>
-    <row r="650" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="650" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A650" s="6"/>
       <c r="B650" s="4"/>
       <c r="C650" s="4"/>
@@ -13454,7 +13474,7 @@
       <c r="P650" s="4"/>
       <c r="Q650" s="4"/>
     </row>
-    <row r="651" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="651" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A651" s="6"/>
       <c r="B651" s="4"/>
       <c r="C651" s="4"/>
@@ -13473,7 +13493,7 @@
       <c r="P651" s="4"/>
       <c r="Q651" s="4"/>
     </row>
-    <row r="652" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="652" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A652" s="6"/>
       <c r="B652" s="4"/>
       <c r="C652" s="4"/>
@@ -13492,7 +13512,7 @@
       <c r="P652" s="4"/>
       <c r="Q652" s="4"/>
     </row>
-    <row r="653" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="653" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A653" s="6"/>
       <c r="B653" s="4"/>
       <c r="C653" s="4"/>
@@ -13511,7 +13531,7 @@
       <c r="P653" s="4"/>
       <c r="Q653" s="4"/>
     </row>
-    <row r="654" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="654" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A654" s="6"/>
       <c r="B654" s="4"/>
       <c r="C654" s="4"/>
@@ -13530,7 +13550,7 @@
       <c r="P654" s="4"/>
       <c r="Q654" s="4"/>
     </row>
-    <row r="655" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="655" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A655" s="6"/>
       <c r="B655" s="4"/>
       <c r="C655" s="4"/>
@@ -13549,7 +13569,7 @@
       <c r="P655" s="4"/>
       <c r="Q655" s="4"/>
     </row>
-    <row r="656" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="656" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A656" s="6"/>
       <c r="B656" s="4"/>
       <c r="C656" s="4"/>
@@ -13568,7 +13588,7 @@
       <c r="P656" s="4"/>
       <c r="Q656" s="4"/>
     </row>
-    <row r="657" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="657" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A657" s="6"/>
       <c r="B657" s="4"/>
       <c r="C657" s="4"/>
@@ -13587,7 +13607,7 @@
       <c r="P657" s="4"/>
       <c r="Q657" s="4"/>
     </row>
-    <row r="658" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="658" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A658" s="6"/>
       <c r="B658" s="4"/>
       <c r="C658" s="4"/>
@@ -13606,7 +13626,7 @@
       <c r="P658" s="4"/>
       <c r="Q658" s="4"/>
     </row>
-    <row r="659" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="659" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A659" s="6"/>
       <c r="B659" s="4"/>
       <c r="C659" s="4"/>
@@ -13625,7 +13645,7 @@
       <c r="P659" s="4"/>
       <c r="Q659" s="4"/>
     </row>
-    <row r="660" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="660" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A660" s="6"/>
       <c r="B660" s="4"/>
       <c r="C660" s="4"/>
@@ -13644,7 +13664,7 @@
       <c r="P660" s="4"/>
       <c r="Q660" s="4"/>
     </row>
-    <row r="661" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="661" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A661" s="6"/>
       <c r="B661" s="4"/>
       <c r="C661" s="4"/>
@@ -13663,7 +13683,7 @@
       <c r="P661" s="4"/>
       <c r="Q661" s="4"/>
     </row>
-    <row r="662" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="662" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A662" s="6"/>
       <c r="B662" s="4"/>
       <c r="C662" s="4"/>
@@ -13682,7 +13702,7 @@
       <c r="P662" s="4"/>
       <c r="Q662" s="4"/>
     </row>
-    <row r="663" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="663" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A663" s="6"/>
       <c r="B663" s="4"/>
       <c r="C663" s="4"/>
@@ -13701,7 +13721,7 @@
       <c r="P663" s="4"/>
       <c r="Q663" s="4"/>
     </row>
-    <row r="664" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="664" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A664" s="6"/>
       <c r="B664" s="4"/>
       <c r="C664" s="4"/>
@@ -13720,7 +13740,7 @@
       <c r="P664" s="4"/>
       <c r="Q664" s="4"/>
     </row>
-    <row r="665" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="665" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A665" s="6"/>
       <c r="B665" s="4"/>
       <c r="C665" s="4"/>
@@ -13739,7 +13759,7 @@
       <c r="P665" s="4"/>
       <c r="Q665" s="4"/>
     </row>
-    <row r="666" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="666" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A666" s="6"/>
       <c r="B666" s="4"/>
       <c r="C666" s="4"/>
@@ -13758,7 +13778,7 @@
       <c r="P666" s="4"/>
       <c r="Q666" s="4"/>
     </row>
-    <row r="667" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="667" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A667" s="6"/>
       <c r="B667" s="4"/>
       <c r="C667" s="4"/>
@@ -13777,7 +13797,7 @@
       <c r="P667" s="4"/>
       <c r="Q667" s="4"/>
     </row>
-    <row r="668" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="668" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A668" s="6"/>
       <c r="B668" s="4"/>
       <c r="C668" s="4"/>
@@ -13796,7 +13816,7 @@
       <c r="P668" s="4"/>
       <c r="Q668" s="4"/>
     </row>
-    <row r="669" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="669" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A669" s="6"/>
       <c r="B669" s="4"/>
       <c r="C669" s="4"/>
@@ -13815,7 +13835,7 @@
       <c r="P669" s="4"/>
       <c r="Q669" s="4"/>
     </row>
-    <row r="670" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="670" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A670" s="6"/>
       <c r="B670" s="4"/>
       <c r="C670" s="4"/>
@@ -13834,7 +13854,7 @@
       <c r="P670" s="4"/>
       <c r="Q670" s="4"/>
     </row>
-    <row r="671" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="671" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A671" s="6"/>
       <c r="B671" s="4"/>
       <c r="C671" s="4"/>
@@ -13853,7 +13873,7 @@
       <c r="P671" s="4"/>
       <c r="Q671" s="4"/>
     </row>
-    <row r="672" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="672" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A672" s="6"/>
       <c r="B672" s="4"/>
       <c r="C672" s="4"/>
@@ -13872,7 +13892,7 @@
       <c r="P672" s="4"/>
       <c r="Q672" s="4"/>
     </row>
-    <row r="673" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="673" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A673" s="6"/>
       <c r="B673" s="4"/>
       <c r="C673" s="4"/>
@@ -13891,7 +13911,7 @@
       <c r="P673" s="4"/>
       <c r="Q673" s="4"/>
     </row>
-    <row r="674" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="674" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A674" s="6"/>
       <c r="B674" s="4"/>
       <c r="C674" s="4"/>
@@ -13910,7 +13930,7 @@
       <c r="P674" s="4"/>
       <c r="Q674" s="4"/>
     </row>
-    <row r="675" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="675" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A675" s="6"/>
       <c r="B675" s="4"/>
       <c r="C675" s="4"/>
@@ -13929,7 +13949,7 @@
       <c r="P675" s="4"/>
       <c r="Q675" s="4"/>
     </row>
-    <row r="676" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="676" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A676" s="6"/>
       <c r="B676" s="4"/>
       <c r="C676" s="4"/>
@@ -13948,7 +13968,7 @@
       <c r="P676" s="4"/>
       <c r="Q676" s="4"/>
     </row>
-    <row r="677" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="677" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A677" s="6"/>
       <c r="B677" s="4"/>
       <c r="C677" s="4"/>
@@ -13967,7 +13987,7 @@
       <c r="P677" s="4"/>
       <c r="Q677" s="4"/>
     </row>
-    <row r="678" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="678" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A678" s="6"/>
       <c r="B678" s="4"/>
       <c r="C678" s="4"/>
@@ -13986,7 +14006,7 @@
       <c r="P678" s="4"/>
       <c r="Q678" s="4"/>
     </row>
-    <row r="679" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="679" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A679" s="6"/>
       <c r="B679" s="4"/>
       <c r="C679" s="4"/>
@@ -14005,7 +14025,7 @@
       <c r="P679" s="4"/>
       <c r="Q679" s="4"/>
     </row>
-    <row r="680" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="680" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A680" s="6"/>
       <c r="B680" s="4"/>
       <c r="C680" s="4"/>
@@ -14024,7 +14044,7 @@
       <c r="P680" s="4"/>
       <c r="Q680" s="4"/>
     </row>
-    <row r="681" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="681" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A681" s="6"/>
       <c r="B681" s="4"/>
       <c r="C681" s="4"/>
@@ -14043,7 +14063,7 @@
       <c r="P681" s="4"/>
       <c r="Q681" s="4"/>
     </row>
-    <row r="682" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="682" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A682" s="6"/>
       <c r="B682" s="4"/>
       <c r="C682" s="4"/>
@@ -14062,7 +14082,7 @@
       <c r="P682" s="4"/>
       <c r="Q682" s="4"/>
     </row>
-    <row r="683" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="683" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A683" s="6"/>
       <c r="B683" s="4"/>
       <c r="C683" s="4"/>
@@ -14081,7 +14101,7 @@
       <c r="P683" s="4"/>
       <c r="Q683" s="4"/>
     </row>
-    <row r="684" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="684" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A684" s="6"/>
       <c r="B684" s="4"/>
       <c r="C684" s="4"/>
@@ -14100,7 +14120,7 @@
       <c r="P684" s="4"/>
       <c r="Q684" s="4"/>
     </row>
-    <row r="685" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="685" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A685" s="6"/>
       <c r="B685" s="4"/>
       <c r="C685" s="4"/>
@@ -14119,7 +14139,7 @@
       <c r="P685" s="4"/>
       <c r="Q685" s="4"/>
     </row>
-    <row r="686" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="686" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A686" s="6"/>
       <c r="B686" s="4"/>
       <c r="C686" s="4"/>
@@ -14138,7 +14158,7 @@
       <c r="P686" s="4"/>
       <c r="Q686" s="4"/>
     </row>
-    <row r="687" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="687" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A687" s="6"/>
       <c r="B687" s="4"/>
       <c r="C687" s="4"/>
@@ -14157,7 +14177,7 @@
       <c r="P687" s="4"/>
       <c r="Q687" s="4"/>
     </row>
-    <row r="688" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="688" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A688" s="6"/>
       <c r="B688" s="4"/>
       <c r="C688" s="4"/>
@@ -14176,7 +14196,7 @@
       <c r="P688" s="4"/>
       <c r="Q688" s="4"/>
     </row>
-    <row r="689" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="689" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A689" s="6"/>
       <c r="B689" s="4"/>
       <c r="C689" s="4"/>
@@ -14195,7 +14215,7 @@
       <c r="P689" s="4"/>
       <c r="Q689" s="4"/>
     </row>
-    <row r="690" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="690" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A690" s="6"/>
       <c r="B690" s="4"/>
       <c r="C690" s="4"/>
@@ -14214,7 +14234,7 @@
       <c r="P690" s="4"/>
       <c r="Q690" s="4"/>
     </row>
-    <row r="691" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="691" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A691" s="6"/>
       <c r="B691" s="4"/>
       <c r="C691" s="4"/>
@@ -14233,7 +14253,7 @@
       <c r="P691" s="4"/>
       <c r="Q691" s="4"/>
     </row>
-    <row r="692" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="692" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A692" s="6"/>
       <c r="B692" s="4"/>
       <c r="C692" s="4"/>
@@ -14252,7 +14272,7 @@
       <c r="P692" s="4"/>
       <c r="Q692" s="4"/>
     </row>
-    <row r="693" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="693" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A693" s="6"/>
       <c r="B693" s="4"/>
       <c r="C693" s="4"/>
@@ -14271,7 +14291,7 @@
       <c r="P693" s="4"/>
       <c r="Q693" s="4"/>
     </row>
-    <row r="694" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="694" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A694" s="6"/>
       <c r="B694" s="4"/>
       <c r="C694" s="4"/>
@@ -14290,7 +14310,7 @@
       <c r="P694" s="4"/>
       <c r="Q694" s="4"/>
     </row>
-    <row r="695" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="695" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A695" s="6"/>
       <c r="B695" s="4"/>
       <c r="C695" s="4"/>
@@ -14309,7 +14329,7 @@
       <c r="P695" s="4"/>
       <c r="Q695" s="4"/>
     </row>
-    <row r="696" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="696" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A696" s="6"/>
       <c r="B696" s="4"/>
       <c r="C696" s="4"/>
@@ -14328,7 +14348,7 @@
       <c r="P696" s="4"/>
       <c r="Q696" s="4"/>
     </row>
-    <row r="697" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="697" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A697" s="6"/>
       <c r="B697" s="4"/>
       <c r="C697" s="4"/>
@@ -14347,7 +14367,7 @@
       <c r="P697" s="4"/>
       <c r="Q697" s="4"/>
     </row>
-    <row r="698" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="698" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A698" s="6"/>
       <c r="B698" s="4"/>
       <c r="C698" s="4"/>
@@ -14366,7 +14386,7 @@
       <c r="P698" s="4"/>
       <c r="Q698" s="4"/>
     </row>
-    <row r="699" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="699" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A699" s="6"/>
       <c r="B699" s="4"/>
       <c r="C699" s="4"/>
@@ -14385,7 +14405,7 @@
       <c r="P699" s="4"/>
       <c r="Q699" s="4"/>
     </row>
-    <row r="700" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="700" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A700" s="6"/>
       <c r="B700" s="4"/>
       <c r="C700" s="4"/>
@@ -14404,7 +14424,7 @@
       <c r="P700" s="4"/>
       <c r="Q700" s="4"/>
     </row>
-    <row r="701" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="701" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A701" s="6"/>
       <c r="B701" s="4"/>
       <c r="C701" s="4"/>
@@ -14423,7 +14443,7 @@
       <c r="P701" s="4"/>
       <c r="Q701" s="4"/>
     </row>
-    <row r="702" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="702" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A702" s="6"/>
       <c r="B702" s="4"/>
       <c r="C702" s="4"/>
@@ -14442,7 +14462,7 @@
       <c r="P702" s="4"/>
       <c r="Q702" s="4"/>
     </row>
-    <row r="703" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="703" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A703" s="6"/>
       <c r="B703" s="4"/>
       <c r="C703" s="4"/>
@@ -14461,7 +14481,7 @@
       <c r="P703" s="4"/>
       <c r="Q703" s="4"/>
     </row>
-    <row r="704" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="704" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A704" s="6"/>
       <c r="B704" s="4"/>
       <c r="C704" s="4"/>
@@ -14480,7 +14500,7 @@
       <c r="P704" s="4"/>
       <c r="Q704" s="4"/>
     </row>
-    <row r="705" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="705" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A705" s="6"/>
       <c r="B705" s="4"/>
       <c r="C705" s="4"/>
@@ -14499,7 +14519,7 @@
       <c r="P705" s="4"/>
       <c r="Q705" s="4"/>
     </row>
-    <row r="706" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="706" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A706" s="6"/>
       <c r="B706" s="4"/>
       <c r="C706" s="4"/>
@@ -14518,7 +14538,7 @@
       <c r="P706" s="4"/>
       <c r="Q706" s="4"/>
     </row>
-    <row r="707" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="707" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A707" s="6"/>
       <c r="B707" s="4"/>
       <c r="C707" s="4"/>
@@ -14537,7 +14557,7 @@
       <c r="P707" s="4"/>
       <c r="Q707" s="4"/>
     </row>
-    <row r="708" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="708" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A708" s="6"/>
       <c r="B708" s="4"/>
       <c r="C708" s="4"/>
@@ -14556,7 +14576,7 @@
       <c r="P708" s="4"/>
       <c r="Q708" s="4"/>
     </row>
-    <row r="709" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="709" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A709" s="6"/>
       <c r="B709" s="4"/>
       <c r="C709" s="4"/>
@@ -14575,7 +14595,7 @@
       <c r="P709" s="4"/>
       <c r="Q709" s="4"/>
     </row>
-    <row r="710" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="710" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A710" s="6"/>
       <c r="B710" s="4"/>
       <c r="C710" s="4"/>
@@ -14594,7 +14614,7 @@
       <c r="P710" s="4"/>
       <c r="Q710" s="4"/>
     </row>
-    <row r="711" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="711" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A711" s="6"/>
       <c r="B711" s="4"/>
       <c r="C711" s="4"/>
@@ -14613,7 +14633,7 @@
       <c r="P711" s="4"/>
       <c r="Q711" s="4"/>
     </row>
-    <row r="712" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="712" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A712" s="6"/>
       <c r="B712" s="4"/>
       <c r="C712" s="4"/>
@@ -14632,7 +14652,7 @@
       <c r="P712" s="4"/>
       <c r="Q712" s="4"/>
     </row>
-    <row r="713" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="713" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A713" s="6"/>
       <c r="B713" s="4"/>
       <c r="C713" s="4"/>
@@ -14651,7 +14671,7 @@
       <c r="P713" s="4"/>
       <c r="Q713" s="4"/>
     </row>
-    <row r="714" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="714" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A714" s="6"/>
       <c r="B714" s="4"/>
       <c r="C714" s="4"/>
@@ -14670,7 +14690,7 @@
       <c r="P714" s="4"/>
       <c r="Q714" s="4"/>
     </row>
-    <row r="715" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="715" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A715" s="6"/>
       <c r="B715" s="4"/>
       <c r="C715" s="4"/>
@@ -14689,7 +14709,7 @@
       <c r="P715" s="4"/>
       <c r="Q715" s="4"/>
     </row>
-    <row r="716" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="716" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A716" s="6"/>
       <c r="B716" s="4"/>
       <c r="C716" s="4"/>
@@ -14708,7 +14728,7 @@
       <c r="P716" s="4"/>
       <c r="Q716" s="4"/>
     </row>
-    <row r="717" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="717" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A717" s="6"/>
       <c r="B717" s="4"/>
       <c r="C717" s="4"/>
@@ -14727,7 +14747,7 @@
       <c r="P717" s="4"/>
       <c r="Q717" s="4"/>
     </row>
-    <row r="718" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="718" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A718" s="6"/>
       <c r="B718" s="4"/>
       <c r="C718" s="4"/>
@@ -14746,7 +14766,7 @@
       <c r="P718" s="4"/>
       <c r="Q718" s="4"/>
     </row>
-    <row r="719" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="719" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A719" s="6"/>
       <c r="B719" s="4"/>
       <c r="C719" s="4"/>
@@ -14765,7 +14785,7 @@
       <c r="P719" s="4"/>
       <c r="Q719" s="4"/>
     </row>
-    <row r="720" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="720" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A720" s="6"/>
       <c r="B720" s="4"/>
       <c r="C720" s="4"/>
@@ -14784,7 +14804,7 @@
       <c r="P720" s="4"/>
       <c r="Q720" s="4"/>
     </row>
-    <row r="721" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="721" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A721" s="6"/>
       <c r="B721" s="4"/>
       <c r="C721" s="4"/>
@@ -14803,7 +14823,7 @@
       <c r="P721" s="4"/>
       <c r="Q721" s="4"/>
     </row>
-    <row r="722" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="722" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A722" s="6"/>
       <c r="B722" s="4"/>
       <c r="C722" s="4"/>
@@ -14822,7 +14842,7 @@
       <c r="P722" s="4"/>
       <c r="Q722" s="4"/>
     </row>
-    <row r="723" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="723" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A723" s="6"/>
       <c r="B723" s="4"/>
       <c r="C723" s="4"/>
@@ -14841,7 +14861,7 @@
       <c r="P723" s="4"/>
       <c r="Q723" s="4"/>
     </row>
-    <row r="724" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="724" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A724" s="6"/>
       <c r="B724" s="4"/>
       <c r="C724" s="4"/>
@@ -14860,7 +14880,7 @@
       <c r="P724" s="4"/>
       <c r="Q724" s="4"/>
     </row>
-    <row r="725" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="725" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A725" s="6"/>
       <c r="B725" s="4"/>
       <c r="C725" s="4"/>
@@ -14879,7 +14899,7 @@
       <c r="P725" s="4"/>
       <c r="Q725" s="4"/>
     </row>
-    <row r="726" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="726" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A726" s="6"/>
       <c r="B726" s="4"/>
       <c r="C726" s="4"/>
@@ -14898,7 +14918,7 @@
       <c r="P726" s="4"/>
       <c r="Q726" s="4"/>
     </row>
-    <row r="727" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="727" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A727" s="6"/>
       <c r="B727" s="4"/>
       <c r="C727" s="4"/>
@@ -14917,7 +14937,7 @@
       <c r="P727" s="4"/>
       <c r="Q727" s="4"/>
     </row>
-    <row r="728" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="728" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A728" s="6"/>
       <c r="B728" s="4"/>
       <c r="C728" s="4"/>
@@ -14936,7 +14956,7 @@
       <c r="P728" s="4"/>
       <c r="Q728" s="4"/>
     </row>
-    <row r="729" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="729" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A729" s="6"/>
       <c r="B729" s="4"/>
       <c r="C729" s="4"/>
@@ -14955,7 +14975,7 @@
       <c r="P729" s="4"/>
       <c r="Q729" s="4"/>
     </row>
-    <row r="730" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="730" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A730" s="6"/>
       <c r="B730" s="4"/>
       <c r="C730" s="4"/>
@@ -14974,7 +14994,7 @@
       <c r="P730" s="4"/>
       <c r="Q730" s="4"/>
     </row>
-    <row r="731" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="731" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A731" s="6"/>
       <c r="B731" s="4"/>
       <c r="C731" s="4"/>
@@ -14993,7 +15013,7 @@
       <c r="P731" s="4"/>
       <c r="Q731" s="4"/>
     </row>
-    <row r="732" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="732" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A732" s="6"/>
       <c r="B732" s="4"/>
       <c r="C732" s="4"/>
@@ -15012,7 +15032,7 @@
       <c r="P732" s="4"/>
       <c r="Q732" s="4"/>
     </row>
-    <row r="733" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="733" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A733" s="6"/>
       <c r="B733" s="4"/>
       <c r="C733" s="4"/>
@@ -15031,7 +15051,7 @@
       <c r="P733" s="4"/>
       <c r="Q733" s="4"/>
     </row>
-    <row r="734" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="734" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A734" s="6"/>
       <c r="B734" s="4"/>
       <c r="C734" s="4"/>
@@ -15050,7 +15070,7 @@
       <c r="P734" s="4"/>
       <c r="Q734" s="4"/>
     </row>
-    <row r="735" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="735" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A735" s="6"/>
       <c r="B735" s="4"/>
       <c r="C735" s="4"/>
@@ -15069,7 +15089,7 @@
       <c r="P735" s="4"/>
       <c r="Q735" s="4"/>
     </row>
-    <row r="736" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="736" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A736" s="6"/>
       <c r="B736" s="4"/>
       <c r="C736" s="4"/>
@@ -15088,7 +15108,7 @@
       <c r="P736" s="4"/>
       <c r="Q736" s="4"/>
     </row>
-    <row r="737" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="737" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A737" s="6"/>
       <c r="B737" s="4"/>
       <c r="C737" s="4"/>
@@ -15107,7 +15127,7 @@
       <c r="P737" s="4"/>
       <c r="Q737" s="4"/>
     </row>
-    <row r="738" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="738" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A738" s="6"/>
       <c r="B738" s="4"/>
       <c r="C738" s="4"/>
@@ -15126,7 +15146,7 @@
       <c r="P738" s="4"/>
       <c r="Q738" s="4"/>
     </row>
-    <row r="739" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="739" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A739" s="6"/>
       <c r="B739" s="4"/>
       <c r="C739" s="4"/>
@@ -15145,7 +15165,7 @@
       <c r="P739" s="4"/>
       <c r="Q739" s="4"/>
     </row>
-    <row r="740" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="740" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A740" s="6"/>
       <c r="B740" s="4"/>
       <c r="C740" s="4"/>
@@ -15164,7 +15184,7 @@
       <c r="P740" s="4"/>
       <c r="Q740" s="4"/>
     </row>
-    <row r="741" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="741" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A741" s="6"/>
       <c r="B741" s="4"/>
       <c r="C741" s="4"/>
@@ -15183,7 +15203,7 @@
       <c r="P741" s="4"/>
       <c r="Q741" s="4"/>
     </row>
-    <row r="742" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="742" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A742" s="6"/>
       <c r="B742" s="4"/>
       <c r="C742" s="4"/>
@@ -15202,7 +15222,7 @@
       <c r="P742" s="4"/>
       <c r="Q742" s="4"/>
     </row>
-    <row r="743" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="743" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A743" s="6"/>
       <c r="B743" s="4"/>
       <c r="C743" s="4"/>
@@ -15221,7 +15241,7 @@
       <c r="P743" s="4"/>
       <c r="Q743" s="4"/>
     </row>
-    <row r="744" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="744" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A744" s="6"/>
       <c r="B744" s="4"/>
       <c r="C744" s="4"/>
@@ -15240,7 +15260,7 @@
       <c r="P744" s="4"/>
       <c r="Q744" s="4"/>
     </row>
-    <row r="745" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="745" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A745" s="6"/>
       <c r="B745" s="4"/>
       <c r="C745" s="4"/>
@@ -15259,7 +15279,7 @@
       <c r="P745" s="4"/>
       <c r="Q745" s="4"/>
     </row>
-    <row r="746" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="746" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A746" s="6"/>
       <c r="B746" s="4"/>
       <c r="C746" s="4"/>
@@ -15278,7 +15298,7 @@
       <c r="P746" s="4"/>
       <c r="Q746" s="4"/>
     </row>
-    <row r="747" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="747" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A747" s="6"/>
       <c r="B747" s="4"/>
       <c r="C747" s="4"/>
@@ -15297,7 +15317,7 @@
       <c r="P747" s="4"/>
       <c r="Q747" s="4"/>
     </row>
-    <row r="748" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="748" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A748" s="6"/>
       <c r="B748" s="4"/>
       <c r="C748" s="4"/>
@@ -15316,7 +15336,7 @@
       <c r="P748" s="4"/>
       <c r="Q748" s="4"/>
     </row>
-    <row r="749" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="749" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A749" s="6"/>
       <c r="B749" s="4"/>
       <c r="C749" s="4"/>
@@ -15335,7 +15355,7 @@
       <c r="P749" s="4"/>
       <c r="Q749" s="4"/>
     </row>
-    <row r="750" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="750" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A750" s="6"/>
       <c r="B750" s="4"/>
       <c r="C750" s="4"/>
@@ -15354,7 +15374,7 @@
       <c r="P750" s="4"/>
       <c r="Q750" s="4"/>
     </row>
-    <row r="751" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="751" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A751" s="6"/>
       <c r="B751" s="4"/>
       <c r="C751" s="4"/>
@@ -15373,7 +15393,7 @@
       <c r="P751" s="4"/>
       <c r="Q751" s="4"/>
     </row>
-    <row r="752" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="752" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A752" s="6"/>
       <c r="B752" s="4"/>
       <c r="C752" s="4"/>
@@ -15392,7 +15412,7 @@
       <c r="P752" s="4"/>
       <c r="Q752" s="4"/>
     </row>
-    <row r="753" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="753" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A753" s="6"/>
       <c r="B753" s="4"/>
       <c r="C753" s="4"/>
@@ -15411,7 +15431,7 @@
       <c r="P753" s="4"/>
       <c r="Q753" s="4"/>
     </row>
-    <row r="754" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="754" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A754" s="6"/>
       <c r="B754" s="4"/>
       <c r="C754" s="4"/>
@@ -15430,7 +15450,7 @@
       <c r="P754" s="4"/>
       <c r="Q754" s="4"/>
     </row>
-    <row r="755" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="755" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A755" s="6"/>
       <c r="B755" s="4"/>
       <c r="C755" s="4"/>
@@ -15449,7 +15469,7 @@
       <c r="P755" s="4"/>
       <c r="Q755" s="4"/>
     </row>
-    <row r="756" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="756" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A756" s="6"/>
       <c r="B756" s="4"/>
       <c r="C756" s="4"/>
@@ -15468,7 +15488,7 @@
       <c r="P756" s="4"/>
       <c r="Q756" s="4"/>
     </row>
-    <row r="757" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="757" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A757" s="6"/>
       <c r="B757" s="4"/>
       <c r="C757" s="4"/>
@@ -15487,7 +15507,7 @@
       <c r="P757" s="4"/>
       <c r="Q757" s="4"/>
     </row>
-    <row r="758" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="758" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A758" s="6"/>
       <c r="B758" s="4"/>
       <c r="C758" s="4"/>
@@ -15506,7 +15526,7 @@
       <c r="P758" s="4"/>
       <c r="Q758" s="4"/>
     </row>
-    <row r="759" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="759" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A759" s="6"/>
       <c r="B759" s="4"/>
       <c r="C759" s="4"/>
@@ -15525,7 +15545,7 @@
       <c r="P759" s="4"/>
       <c r="Q759" s="4"/>
     </row>
-    <row r="760" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="760" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A760" s="6"/>
       <c r="B760" s="4"/>
       <c r="C760" s="4"/>
@@ -15544,7 +15564,7 @@
       <c r="P760" s="4"/>
       <c r="Q760" s="4"/>
     </row>
-    <row r="761" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="761" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A761" s="6"/>
       <c r="B761" s="4"/>
       <c r="C761" s="4"/>
@@ -15563,7 +15583,7 @@
       <c r="P761" s="4"/>
       <c r="Q761" s="4"/>
     </row>
-    <row r="762" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="762" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A762" s="6"/>
       <c r="B762" s="4"/>
       <c r="C762" s="4"/>
@@ -15582,7 +15602,7 @@
       <c r="P762" s="4"/>
       <c r="Q762" s="4"/>
     </row>
-    <row r="763" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="763" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A763" s="6"/>
       <c r="B763" s="4"/>
       <c r="C763" s="4"/>
@@ -15601,7 +15621,7 @@
       <c r="P763" s="4"/>
       <c r="Q763" s="4"/>
     </row>
-    <row r="764" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="764" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A764" s="6"/>
       <c r="B764" s="4"/>
       <c r="C764" s="4"/>
@@ -15620,7 +15640,7 @@
       <c r="P764" s="4"/>
       <c r="Q764" s="4"/>
     </row>
-    <row r="765" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="765" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A765" s="6"/>
       <c r="B765" s="4"/>
       <c r="C765" s="4"/>
@@ -15639,7 +15659,7 @@
       <c r="P765" s="4"/>
       <c r="Q765" s="4"/>
     </row>
-    <row r="766" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="766" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A766" s="6"/>
       <c r="B766" s="4"/>
       <c r="C766" s="4"/>
@@ -15658,7 +15678,7 @@
       <c r="P766" s="4"/>
       <c r="Q766" s="4"/>
     </row>
-    <row r="767" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="767" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A767" s="6"/>
       <c r="B767" s="4"/>
       <c r="C767" s="4"/>
@@ -15677,7 +15697,7 @@
       <c r="P767" s="4"/>
       <c r="Q767" s="4"/>
     </row>
-    <row r="768" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="768" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A768" s="6"/>
       <c r="B768" s="4"/>
       <c r="C768" s="4"/>
@@ -15696,7 +15716,7 @@
       <c r="P768" s="4"/>
       <c r="Q768" s="4"/>
     </row>
-    <row r="769" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="769" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A769" s="6"/>
       <c r="B769" s="4"/>
       <c r="C769" s="4"/>
@@ -15715,7 +15735,7 @@
       <c r="P769" s="4"/>
       <c r="Q769" s="4"/>
     </row>
-    <row r="770" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="770" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A770" s="6"/>
       <c r="B770" s="4"/>
       <c r="C770" s="4"/>
@@ -15734,7 +15754,7 @@
       <c r="P770" s="4"/>
       <c r="Q770" s="4"/>
     </row>
-    <row r="771" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="771" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A771" s="6"/>
       <c r="B771" s="4"/>
       <c r="C771" s="4"/>
@@ -15753,7 +15773,7 @@
       <c r="P771" s="4"/>
       <c r="Q771" s="4"/>
     </row>
-    <row r="772" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="772" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A772" s="6"/>
       <c r="B772" s="4"/>
       <c r="C772" s="4"/>
@@ -15772,7 +15792,7 @@
       <c r="P772" s="4"/>
       <c r="Q772" s="4"/>
     </row>
-    <row r="773" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="773" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A773" s="6"/>
       <c r="B773" s="4"/>
       <c r="C773" s="4"/>
@@ -15791,7 +15811,7 @@
       <c r="P773" s="4"/>
       <c r="Q773" s="4"/>
     </row>
-    <row r="774" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="774" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A774" s="6"/>
       <c r="B774" s="4"/>
       <c r="C774" s="4"/>
@@ -15810,7 +15830,7 @@
       <c r="P774" s="4"/>
       <c r="Q774" s="4"/>
     </row>
-    <row r="775" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="775" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A775" s="6"/>
       <c r="B775" s="4"/>
       <c r="C775" s="4"/>
@@ -15829,7 +15849,7 @@
       <c r="P775" s="4"/>
       <c r="Q775" s="4"/>
     </row>
-    <row r="776" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="776" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A776" s="6"/>
       <c r="B776" s="4"/>
       <c r="C776" s="4"/>
@@ -15848,7 +15868,7 @@
       <c r="P776" s="4"/>
       <c r="Q776" s="4"/>
     </row>
-    <row r="777" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="777" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A777" s="6"/>
       <c r="B777" s="4"/>
       <c r="C777" s="4"/>
@@ -15867,7 +15887,7 @@
       <c r="P777" s="4"/>
       <c r="Q777" s="4"/>
     </row>
-    <row r="778" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="778" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A778" s="6"/>
       <c r="B778" s="4"/>
       <c r="C778" s="4"/>
@@ -15886,7 +15906,7 @@
       <c r="P778" s="4"/>
       <c r="Q778" s="4"/>
     </row>
-    <row r="779" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="779" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A779" s="6"/>
       <c r="B779" s="4"/>
       <c r="C779" s="4"/>
@@ -15905,7 +15925,7 @@
       <c r="P779" s="4"/>
       <c r="Q779" s="4"/>
     </row>
-    <row r="780" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="780" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A780" s="6"/>
       <c r="B780" s="4"/>
       <c r="C780" s="4"/>
@@ -15924,7 +15944,7 @@
       <c r="P780" s="4"/>
       <c r="Q780" s="4"/>
     </row>
-    <row r="781" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="781" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A781" s="6"/>
       <c r="B781" s="4"/>
       <c r="C781" s="4"/>
@@ -15943,7 +15963,7 @@
       <c r="P781" s="4"/>
       <c r="Q781" s="4"/>
     </row>
-    <row r="782" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="782" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A782" s="6"/>
       <c r="B782" s="4"/>
       <c r="C782" s="4"/>
@@ -15962,7 +15982,7 @@
       <c r="P782" s="4"/>
       <c r="Q782" s="4"/>
     </row>
-    <row r="783" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="783" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A783" s="6"/>
       <c r="B783" s="4"/>
       <c r="C783" s="4"/>
@@ -15981,7 +16001,7 @@
       <c r="P783" s="4"/>
       <c r="Q783" s="4"/>
     </row>
-    <row r="784" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="784" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A784" s="6"/>
       <c r="B784" s="4"/>
       <c r="C784" s="4"/>
@@ -16000,7 +16020,7 @@
       <c r="P784" s="4"/>
       <c r="Q784" s="4"/>
     </row>
-    <row r="785" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="785" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A785" s="6"/>
       <c r="B785" s="4"/>
       <c r="C785" s="4"/>
@@ -16019,7 +16039,7 @@
       <c r="P785" s="4"/>
       <c r="Q785" s="4"/>
     </row>
-    <row r="786" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="786" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A786" s="6"/>
       <c r="B786" s="4"/>
       <c r="C786" s="4"/>
@@ -16038,7 +16058,7 @@
       <c r="P786" s="4"/>
       <c r="Q786" s="4"/>
     </row>
-    <row r="787" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="787" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A787" s="6"/>
       <c r="B787" s="4"/>
       <c r="C787" s="4"/>
@@ -16057,7 +16077,7 @@
       <c r="P787" s="4"/>
       <c r="Q787" s="4"/>
     </row>
-    <row r="788" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="788" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A788" s="6"/>
       <c r="B788" s="4"/>
       <c r="C788" s="4"/>
@@ -16076,7 +16096,7 @@
       <c r="P788" s="4"/>
       <c r="Q788" s="4"/>
     </row>
-    <row r="789" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="789" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A789" s="6"/>
       <c r="B789" s="4"/>
       <c r="C789" s="4"/>
@@ -16095,7 +16115,7 @@
       <c r="P789" s="4"/>
       <c r="Q789" s="4"/>
     </row>
-    <row r="790" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="790" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A790" s="6"/>
       <c r="B790" s="4"/>
       <c r="C790" s="4"/>
@@ -16114,7 +16134,7 @@
       <c r="P790" s="4"/>
       <c r="Q790" s="4"/>
     </row>
-    <row r="791" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="791" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A791" s="6"/>
       <c r="B791" s="4"/>
       <c r="C791" s="4"/>
@@ -16133,7 +16153,7 @@
       <c r="P791" s="4"/>
       <c r="Q791" s="4"/>
     </row>
-    <row r="792" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="792" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A792" s="6"/>
       <c r="B792" s="4"/>
       <c r="C792" s="4"/>
@@ -16152,7 +16172,7 @@
       <c r="P792" s="4"/>
       <c r="Q792" s="4"/>
     </row>
-    <row r="793" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="793" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A793" s="6"/>
       <c r="B793" s="4"/>
       <c r="C793" s="4"/>
@@ -16171,7 +16191,7 @@
       <c r="P793" s="4"/>
       <c r="Q793" s="4"/>
     </row>
-    <row r="794" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="794" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A794" s="6"/>
       <c r="B794" s="4"/>
       <c r="C794" s="4"/>
@@ -16190,7 +16210,7 @@
       <c r="P794" s="4"/>
       <c r="Q794" s="4"/>
     </row>
-    <row r="795" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="795" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A795" s="6"/>
       <c r="B795" s="4"/>
       <c r="C795" s="4"/>
@@ -16209,7 +16229,7 @@
       <c r="P795" s="4"/>
       <c r="Q795" s="4"/>
     </row>
-    <row r="796" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="796" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A796" s="6"/>
       <c r="B796" s="4"/>
       <c r="C796" s="4"/>
@@ -16228,7 +16248,7 @@
       <c r="P796" s="4"/>
       <c r="Q796" s="4"/>
     </row>
-    <row r="797" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="797" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A797" s="6"/>
       <c r="B797" s="4"/>
       <c r="C797" s="4"/>
@@ -16247,7 +16267,7 @@
       <c r="P797" s="4"/>
       <c r="Q797" s="4"/>
     </row>
-    <row r="798" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="798" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A798" s="6"/>
       <c r="B798" s="4"/>
       <c r="C798" s="4"/>
@@ -16266,7 +16286,7 @@
       <c r="P798" s="4"/>
       <c r="Q798" s="4"/>
     </row>
-    <row r="799" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="799" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A799" s="6"/>
       <c r="B799" s="4"/>
       <c r="C799" s="4"/>
@@ -16285,7 +16305,7 @@
       <c r="P799" s="4"/>
       <c r="Q799" s="4"/>
     </row>
-    <row r="800" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="800" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A800" s="6"/>
       <c r="B800" s="4"/>
       <c r="C800" s="4"/>
@@ -16304,7 +16324,7 @@
       <c r="P800" s="4"/>
       <c r="Q800" s="4"/>
     </row>
-    <row r="801" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="801" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A801" s="6"/>
       <c r="B801" s="4"/>
       <c r="C801" s="4"/>
@@ -16323,7 +16343,7 @@
       <c r="P801" s="4"/>
       <c r="Q801" s="4"/>
     </row>
-    <row r="802" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="802" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A802" s="6"/>
       <c r="B802" s="4"/>
       <c r="C802" s="4"/>
@@ -16342,7 +16362,7 @@
       <c r="P802" s="4"/>
       <c r="Q802" s="4"/>
     </row>
-    <row r="803" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="803" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A803" s="6"/>
       <c r="B803" s="4"/>
       <c r="C803" s="4"/>
@@ -16361,7 +16381,7 @@
       <c r="P803" s="4"/>
       <c r="Q803" s="4"/>
     </row>
-    <row r="804" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="804" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A804" s="6"/>
       <c r="B804" s="4"/>
       <c r="C804" s="4"/>
@@ -16380,7 +16400,7 @@
       <c r="P804" s="4"/>
       <c r="Q804" s="4"/>
     </row>
-    <row r="805" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="805" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A805" s="6"/>
       <c r="B805" s="4"/>
       <c r="C805" s="4"/>
@@ -16399,7 +16419,7 @@
       <c r="P805" s="4"/>
       <c r="Q805" s="4"/>
     </row>
-    <row r="806" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="806" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A806" s="6"/>
       <c r="B806" s="4"/>
       <c r="C806" s="4"/>
@@ -16418,7 +16438,7 @@
       <c r="P806" s="4"/>
       <c r="Q806" s="4"/>
     </row>
-    <row r="807" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="807" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A807" s="6"/>
       <c r="B807" s="4"/>
       <c r="C807" s="4"/>
@@ -16437,7 +16457,7 @@
       <c r="P807" s="4"/>
       <c r="Q807" s="4"/>
     </row>
-    <row r="808" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="808" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A808" s="6"/>
       <c r="B808" s="4"/>
       <c r="C808" s="4"/>
@@ -16456,7 +16476,7 @@
       <c r="P808" s="4"/>
       <c r="Q808" s="4"/>
     </row>
-    <row r="809" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="809" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A809" s="6"/>
       <c r="B809" s="4"/>
       <c r="C809" s="4"/>
@@ -16475,7 +16495,7 @@
       <c r="P809" s="4"/>
       <c r="Q809" s="4"/>
     </row>
-    <row r="810" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="810" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A810" s="6"/>
       <c r="B810" s="4"/>
       <c r="C810" s="4"/>
@@ -16494,7 +16514,7 @@
       <c r="P810" s="4"/>
       <c r="Q810" s="4"/>
     </row>
-    <row r="811" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="811" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A811" s="6"/>
       <c r="B811" s="4"/>
       <c r="C811" s="4"/>
@@ -16513,7 +16533,7 @@
       <c r="P811" s="4"/>
       <c r="Q811" s="4"/>
     </row>
-    <row r="812" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="812" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A812" s="6"/>
       <c r="B812" s="4"/>
       <c r="C812" s="4"/>
@@ -16532,7 +16552,7 @@
       <c r="P812" s="4"/>
       <c r="Q812" s="4"/>
     </row>
-    <row r="813" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="813" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A813" s="6"/>
       <c r="B813" s="4"/>
       <c r="C813" s="4"/>
@@ -16551,7 +16571,7 @@
       <c r="P813" s="4"/>
       <c r="Q813" s="4"/>
     </row>
-    <row r="814" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="814" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A814" s="6"/>
       <c r="B814" s="4"/>
       <c r="C814" s="4"/>
@@ -16570,7 +16590,7 @@
       <c r="P814" s="4"/>
       <c r="Q814" s="4"/>
     </row>
-    <row r="815" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="815" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A815" s="6"/>
       <c r="B815" s="4"/>
       <c r="C815" s="4"/>
@@ -16589,7 +16609,7 @@
       <c r="P815" s="4"/>
       <c r="Q815" s="4"/>
     </row>
-    <row r="816" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="816" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A816" s="6"/>
       <c r="B816" s="4"/>
       <c r="C816" s="4"/>
@@ -16608,7 +16628,7 @@
       <c r="P816" s="4"/>
       <c r="Q816" s="4"/>
     </row>
-    <row r="817" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="817" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A817" s="6"/>
       <c r="B817" s="4"/>
       <c r="C817" s="4"/>
@@ -16627,7 +16647,7 @@
       <c r="P817" s="4"/>
       <c r="Q817" s="4"/>
     </row>
-    <row r="818" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="818" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A818" s="6"/>
       <c r="B818" s="4"/>
       <c r="C818" s="4"/>
@@ -16646,7 +16666,7 @@
       <c r="P818" s="4"/>
       <c r="Q818" s="4"/>
     </row>
-    <row r="819" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="819" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A819" s="6"/>
       <c r="B819" s="4"/>
       <c r="C819" s="4"/>
@@ -16665,7 +16685,7 @@
       <c r="P819" s="4"/>
       <c r="Q819" s="4"/>
     </row>
-    <row r="820" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="820" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A820" s="6"/>
       <c r="B820" s="4"/>
       <c r="C820" s="4"/>
@@ -16684,7 +16704,7 @@
       <c r="P820" s="4"/>
       <c r="Q820" s="4"/>
     </row>
-    <row r="821" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="821" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A821" s="6"/>
       <c r="B821" s="4"/>
       <c r="C821" s="4"/>
@@ -16703,7 +16723,7 @@
       <c r="P821" s="4"/>
       <c r="Q821" s="4"/>
     </row>
-    <row r="822" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="822" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A822" s="6"/>
       <c r="B822" s="4"/>
       <c r="C822" s="4"/>
@@ -16722,7 +16742,7 @@
       <c r="P822" s="4"/>
       <c r="Q822" s="4"/>
     </row>
-    <row r="823" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="823" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A823" s="6"/>
       <c r="B823" s="4"/>
       <c r="C823" s="4"/>
@@ -16741,7 +16761,7 @@
       <c r="P823" s="4"/>
       <c r="Q823" s="4"/>
     </row>
-    <row r="824" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="824" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A824" s="6"/>
       <c r="B824" s="4"/>
       <c r="C824" s="4"/>
@@ -16760,7 +16780,7 @@
       <c r="P824" s="4"/>
       <c r="Q824" s="4"/>
     </row>
-    <row r="825" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="825" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A825" s="6"/>
       <c r="B825" s="4"/>
       <c r="C825" s="4"/>
@@ -16779,7 +16799,7 @@
       <c r="P825" s="4"/>
       <c r="Q825" s="4"/>
     </row>
-    <row r="826" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="826" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A826" s="6"/>
       <c r="B826" s="4"/>
       <c r="C826" s="4"/>
@@ -16798,7 +16818,7 @@
       <c r="P826" s="4"/>
       <c r="Q826" s="4"/>
     </row>
-    <row r="827" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="827" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A827" s="6"/>
       <c r="B827" s="4"/>
       <c r="C827" s="4"/>
@@ -16817,7 +16837,7 @@
       <c r="P827" s="4"/>
       <c r="Q827" s="4"/>
     </row>
-    <row r="828" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="828" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A828" s="6"/>
       <c r="B828" s="4"/>
       <c r="C828" s="4"/>
@@ -16836,7 +16856,7 @@
       <c r="P828" s="4"/>
       <c r="Q828" s="4"/>
     </row>
-    <row r="829" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="829" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A829" s="6"/>
       <c r="B829" s="4"/>
       <c r="C829" s="4"/>
@@ -16855,7 +16875,7 @@
       <c r="P829" s="4"/>
       <c r="Q829" s="4"/>
     </row>
-    <row r="830" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="830" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A830" s="6"/>
       <c r="B830" s="4"/>
       <c r="C830" s="4"/>
@@ -16874,7 +16894,7 @@
       <c r="P830" s="4"/>
       <c r="Q830" s="4"/>
     </row>
-    <row r="831" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="831" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A831" s="6"/>
       <c r="B831" s="4"/>
       <c r="C831" s="4"/>
@@ -16893,7 +16913,7 @@
       <c r="P831" s="4"/>
       <c r="Q831" s="4"/>
     </row>
-    <row r="832" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="832" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A832" s="6"/>
       <c r="B832" s="4"/>
       <c r="C832" s="4"/>
@@ -16912,7 +16932,7 @@
       <c r="P832" s="4"/>
       <c r="Q832" s="4"/>
     </row>
-    <row r="833" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="833" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A833" s="6"/>
       <c r="B833" s="4"/>
       <c r="C833" s="4"/>
@@ -16931,7 +16951,7 @@
       <c r="P833" s="4"/>
       <c r="Q833" s="4"/>
     </row>
-    <row r="834" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="834" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A834" s="6"/>
       <c r="B834" s="4"/>
       <c r="C834" s="4"/>
@@ -16950,7 +16970,7 @@
       <c r="P834" s="4"/>
       <c r="Q834" s="4"/>
     </row>
-    <row r="835" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="835" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A835" s="6"/>
       <c r="B835" s="4"/>
       <c r="C835" s="4"/>
@@ -16969,7 +16989,7 @@
       <c r="P835" s="4"/>
       <c r="Q835" s="4"/>
     </row>
-    <row r="836" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="836" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A836" s="6"/>
       <c r="B836" s="4"/>
       <c r="C836" s="4"/>
@@ -16988,7 +17008,7 @@
       <c r="P836" s="4"/>
       <c r="Q836" s="4"/>
     </row>
-    <row r="837" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="837" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A837" s="6"/>
       <c r="B837" s="4"/>
       <c r="C837" s="4"/>
@@ -17007,7 +17027,7 @@
       <c r="P837" s="4"/>
       <c r="Q837" s="4"/>
     </row>
-    <row r="838" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="838" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A838" s="6"/>
       <c r="B838" s="4"/>
       <c r="C838" s="4"/>
@@ -17026,7 +17046,7 @@
       <c r="P838" s="4"/>
       <c r="Q838" s="4"/>
     </row>
-    <row r="839" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="839" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A839" s="6"/>
       <c r="B839" s="4"/>
       <c r="C839" s="4"/>
@@ -17045,7 +17065,7 @@
       <c r="P839" s="4"/>
       <c r="Q839" s="4"/>
     </row>
-    <row r="840" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="840" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A840" s="6"/>
       <c r="B840" s="4"/>
       <c r="C840" s="4"/>
@@ -17064,7 +17084,7 @@
       <c r="P840" s="4"/>
       <c r="Q840" s="4"/>
     </row>
-    <row r="841" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="841" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A841" s="6"/>
       <c r="B841" s="4"/>
       <c r="C841" s="4"/>
@@ -17083,7 +17103,7 @@
       <c r="P841" s="4"/>
       <c r="Q841" s="4"/>
     </row>
-    <row r="842" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="842" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A842" s="6"/>
       <c r="B842" s="4"/>
       <c r="C842" s="4"/>
@@ -17102,7 +17122,7 @@
       <c r="P842" s="4"/>
       <c r="Q842" s="4"/>
     </row>
-    <row r="843" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="843" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A843" s="6"/>
       <c r="B843" s="4"/>
       <c r="C843" s="4"/>
@@ -17121,7 +17141,7 @@
       <c r="P843" s="4"/>
       <c r="Q843" s="4"/>
     </row>
-    <row r="844" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="844" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A844" s="6"/>
       <c r="B844" s="4"/>
       <c r="C844" s="4"/>
@@ -17140,7 +17160,7 @@
       <c r="P844" s="4"/>
       <c r="Q844" s="4"/>
     </row>
-    <row r="845" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="845" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A845" s="6"/>
       <c r="B845" s="4"/>
       <c r="C845" s="4"/>
@@ -17159,7 +17179,7 @@
       <c r="P845" s="4"/>
       <c r="Q845" s="4"/>
     </row>
-    <row r="846" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="846" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A846" s="6"/>
       <c r="B846" s="4"/>
       <c r="C846" s="4"/>
@@ -17178,7 +17198,7 @@
       <c r="P846" s="4"/>
       <c r="Q846" s="4"/>
     </row>
-    <row r="847" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="847" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A847" s="6"/>
       <c r="B847" s="4"/>
       <c r="C847" s="4"/>
@@ -17197,7 +17217,7 @@
       <c r="P847" s="4"/>
       <c r="Q847" s="4"/>
     </row>
-    <row r="848" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="848" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A848" s="6"/>
       <c r="B848" s="4"/>
       <c r="C848" s="4"/>
@@ -17216,7 +17236,7 @@
       <c r="P848" s="4"/>
       <c r="Q848" s="4"/>
     </row>
-    <row r="849" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="849" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A849" s="6"/>
       <c r="B849" s="4"/>
       <c r="C849" s="4"/>
@@ -17235,7 +17255,7 @@
       <c r="P849" s="4"/>
       <c r="Q849" s="4"/>
     </row>
-    <row r="850" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="850" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A850" s="6"/>
       <c r="B850" s="4"/>
       <c r="C850" s="4"/>
@@ -17254,7 +17274,7 @@
       <c r="P850" s="4"/>
       <c r="Q850" s="4"/>
     </row>
-    <row r="851" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="851" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A851" s="6"/>
       <c r="B851" s="4"/>
       <c r="C851" s="4"/>
@@ -17273,7 +17293,7 @@
       <c r="P851" s="4"/>
       <c r="Q851" s="4"/>
     </row>
-    <row r="852" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="852" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A852" s="6"/>
       <c r="B852" s="4"/>
       <c r="C852" s="4"/>
@@ -17292,7 +17312,7 @@
       <c r="P852" s="4"/>
       <c r="Q852" s="4"/>
     </row>
-    <row r="853" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="853" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A853" s="6"/>
       <c r="B853" s="4"/>
       <c r="C853" s="4"/>
@@ -17311,7 +17331,7 @@
       <c r="P853" s="4"/>
       <c r="Q853" s="4"/>
     </row>
-    <row r="854" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="854" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A854" s="6"/>
       <c r="B854" s="4"/>
       <c r="C854" s="4"/>
@@ -17330,7 +17350,7 @@
       <c r="P854" s="4"/>
       <c r="Q854" s="4"/>
     </row>
-    <row r="855" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="855" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A855" s="6"/>
       <c r="B855" s="4"/>
       <c r="C855" s="4"/>
@@ -17349,7 +17369,7 @@
       <c r="P855" s="4"/>
       <c r="Q855" s="4"/>
     </row>
-    <row r="856" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="856" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A856" s="6"/>
       <c r="B856" s="4"/>
       <c r="C856" s="4"/>
@@ -17368,7 +17388,7 @@
       <c r="P856" s="4"/>
       <c r="Q856" s="4"/>
     </row>
-    <row r="857" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="857" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A857" s="6"/>
       <c r="B857" s="4"/>
       <c r="C857" s="4"/>
@@ -17387,7 +17407,7 @@
       <c r="P857" s="4"/>
       <c r="Q857" s="4"/>
     </row>
-    <row r="858" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="858" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A858" s="6"/>
       <c r="B858" s="4"/>
       <c r="C858" s="4"/>
@@ -17406,7 +17426,7 @@
       <c r="P858" s="4"/>
       <c r="Q858" s="4"/>
     </row>
-    <row r="859" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="859" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A859" s="6"/>
       <c r="B859" s="4"/>
       <c r="C859" s="4"/>
@@ -17425,7 +17445,7 @@
       <c r="P859" s="4"/>
       <c r="Q859" s="4"/>
     </row>
-    <row r="860" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="860" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A860" s="6"/>
       <c r="B860" s="4"/>
       <c r="C860" s="4"/>
@@ -17444,7 +17464,7 @@
       <c r="P860" s="4"/>
       <c r="Q860" s="4"/>
     </row>
-    <row r="861" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="861" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A861" s="6"/>
       <c r="B861" s="4"/>
       <c r="C861" s="4"/>
@@ -17463,7 +17483,7 @@
       <c r="P861" s="4"/>
       <c r="Q861" s="4"/>
     </row>
-    <row r="862" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="862" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A862" s="6"/>
       <c r="B862" s="4"/>
       <c r="C862" s="4"/>
@@ -17482,7 +17502,7 @@
       <c r="P862" s="4"/>
       <c r="Q862" s="4"/>
     </row>
-    <row r="863" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="863" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A863" s="6"/>
       <c r="B863" s="4"/>
       <c r="C863" s="4"/>
@@ -17501,7 +17521,7 @@
       <c r="P863" s="4"/>
       <c r="Q863" s="4"/>
     </row>
-    <row r="864" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="864" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A864" s="6"/>
       <c r="B864" s="4"/>
       <c r="C864" s="4"/>
@@ -17520,7 +17540,7 @@
       <c r="P864" s="4"/>
       <c r="Q864" s="4"/>
     </row>
-    <row r="865" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="865" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A865" s="6"/>
       <c r="B865" s="4"/>
       <c r="C865" s="4"/>
@@ -17539,7 +17559,7 @@
       <c r="P865" s="4"/>
       <c r="Q865" s="4"/>
     </row>
-    <row r="866" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="866" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A866" s="6"/>
       <c r="B866" s="4"/>
       <c r="C866" s="4"/>
@@ -17558,7 +17578,7 @@
       <c r="P866" s="4"/>
       <c r="Q866" s="4"/>
     </row>
-    <row r="867" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="867" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A867" s="6"/>
       <c r="B867" s="4"/>
       <c r="C867" s="4"/>
@@ -17577,7 +17597,7 @@
       <c r="P867" s="4"/>
       <c r="Q867" s="4"/>
     </row>
-    <row r="868" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="868" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A868" s="6"/>
       <c r="B868" s="4"/>
       <c r="C868" s="4"/>
@@ -17596,7 +17616,7 @@
       <c r="P868" s="4"/>
       <c r="Q868" s="4"/>
     </row>
-    <row r="869" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="869" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A869" s="6"/>
       <c r="B869" s="4"/>
       <c r="C869" s="4"/>
@@ -17615,7 +17635,7 @@
       <c r="P869" s="4"/>
       <c r="Q869" s="4"/>
     </row>
-    <row r="870" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="870" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A870" s="6"/>
       <c r="B870" s="4"/>
       <c r="C870" s="4"/>
@@ -17634,7 +17654,7 @@
       <c r="P870" s="4"/>
       <c r="Q870" s="4"/>
     </row>
-    <row r="871" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="871" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A871" s="6"/>
       <c r="B871" s="4"/>
       <c r="C871" s="4"/>
@@ -17653,7 +17673,7 @@
       <c r="P871" s="4"/>
       <c r="Q871" s="4"/>
     </row>
-    <row r="872" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="872" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A872" s="6"/>
       <c r="B872" s="4"/>
       <c r="C872" s="4"/>
@@ -17672,7 +17692,7 @@
       <c r="P872" s="4"/>
       <c r="Q872" s="4"/>
     </row>
-    <row r="873" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="873" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A873" s="6"/>
       <c r="B873" s="4"/>
       <c r="C873" s="4"/>
@@ -17691,7 +17711,7 @@
       <c r="P873" s="4"/>
       <c r="Q873" s="4"/>
     </row>
-    <row r="874" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="874" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A874" s="6"/>
       <c r="B874" s="4"/>
       <c r="C874" s="4"/>
@@ -17710,7 +17730,7 @@
       <c r="P874" s="4"/>
       <c r="Q874" s="4"/>
     </row>
-    <row r="875" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="875" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A875" s="6"/>
       <c r="B875" s="4"/>
       <c r="C875" s="4"/>
@@ -17729,7 +17749,7 @@
       <c r="P875" s="4"/>
       <c r="Q875" s="4"/>
     </row>
-    <row r="876" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="876" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A876" s="6"/>
       <c r="B876" s="4"/>
       <c r="C876" s="4"/>
@@ -17748,7 +17768,7 @@
       <c r="P876" s="4"/>
       <c r="Q876" s="4"/>
     </row>
-    <row r="877" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="877" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A877" s="6"/>
       <c r="B877" s="4"/>
       <c r="C877" s="4"/>
@@ -17767,7 +17787,7 @@
       <c r="P877" s="4"/>
       <c r="Q877" s="4"/>
     </row>
-    <row r="878" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="878" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A878" s="6"/>
       <c r="B878" s="4"/>
       <c r="C878" s="4"/>
@@ -17786,7 +17806,7 @@
       <c r="P878" s="4"/>
       <c r="Q878" s="4"/>
     </row>
-    <row r="879" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="879" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A879" s="6"/>
       <c r="B879" s="4"/>
       <c r="C879" s="4"/>
@@ -17805,7 +17825,7 @@
       <c r="P879" s="4"/>
       <c r="Q879" s="4"/>
     </row>
-    <row r="880" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="880" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A880" s="6"/>
       <c r="B880" s="4"/>
       <c r="C880" s="4"/>
@@ -17824,7 +17844,7 @@
       <c r="P880" s="4"/>
       <c r="Q880" s="4"/>
     </row>
-    <row r="881" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="881" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A881" s="6"/>
       <c r="B881" s="4"/>
       <c r="C881" s="4"/>
@@ -17843,7 +17863,7 @@
       <c r="P881" s="4"/>
       <c r="Q881" s="4"/>
     </row>
-    <row r="882" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="882" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A882" s="6"/>
       <c r="B882" s="4"/>
       <c r="C882" s="4"/>
@@ -17862,7 +17882,7 @@
       <c r="P882" s="4"/>
       <c r="Q882" s="4"/>
     </row>
-    <row r="883" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="883" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A883" s="6"/>
       <c r="B883" s="4"/>
       <c r="C883" s="4"/>
@@ -17881,7 +17901,7 @@
       <c r="P883" s="4"/>
       <c r="Q883" s="4"/>
     </row>
-    <row r="884" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="884" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A884" s="6"/>
       <c r="B884" s="4"/>
       <c r="C884" s="4"/>
@@ -17900,7 +17920,7 @@
       <c r="P884" s="4"/>
       <c r="Q884" s="4"/>
     </row>
-    <row r="885" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="885" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A885" s="6"/>
       <c r="B885" s="4"/>
       <c r="C885" s="4"/>
@@ -17919,7 +17939,7 @@
       <c r="P885" s="4"/>
       <c r="Q885" s="4"/>
     </row>
-    <row r="886" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="886" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A886" s="6"/>
       <c r="B886" s="4"/>
       <c r="C886" s="4"/>
@@ -17938,7 +17958,7 @@
       <c r="P886" s="4"/>
       <c r="Q886" s="4"/>
     </row>
-    <row r="887" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="887" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A887" s="6"/>
       <c r="B887" s="4"/>
       <c r="C887" s="4"/>
@@ -17957,7 +17977,7 @@
       <c r="P887" s="4"/>
       <c r="Q887" s="4"/>
     </row>
-    <row r="888" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="888" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A888" s="6"/>
       <c r="B888" s="4"/>
       <c r="C888" s="4"/>
@@ -17976,7 +17996,7 @@
       <c r="P888" s="4"/>
       <c r="Q888" s="4"/>
     </row>
-    <row r="889" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="889" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A889" s="6"/>
       <c r="B889" s="4"/>
       <c r="C889" s="4"/>
@@ -17995,7 +18015,7 @@
       <c r="P889" s="4"/>
       <c r="Q889" s="4"/>
     </row>
-    <row r="890" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="890" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A890" s="6"/>
       <c r="B890" s="4"/>
       <c r="C890" s="4"/>
@@ -18014,7 +18034,7 @@
       <c r="P890" s="4"/>
       <c r="Q890" s="4"/>
     </row>
-    <row r="891" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="891" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A891" s="6"/>
       <c r="B891" s="4"/>
       <c r="C891" s="4"/>
@@ -18033,7 +18053,7 @@
       <c r="P891" s="4"/>
       <c r="Q891" s="4"/>
     </row>
-    <row r="892" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="892" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A892" s="6"/>
       <c r="B892" s="4"/>
       <c r="C892" s="4"/>
@@ -18052,7 +18072,7 @@
       <c r="P892" s="4"/>
       <c r="Q892" s="4"/>
     </row>
-    <row r="893" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="893" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A893" s="6"/>
       <c r="B893" s="4"/>
       <c r="C893" s="4"/>
@@ -18071,7 +18091,7 @@
       <c r="P893" s="4"/>
       <c r="Q893" s="4"/>
     </row>
-    <row r="894" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="894" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A894" s="6"/>
       <c r="B894" s="4"/>
       <c r="C894" s="4"/>
@@ -18090,7 +18110,7 @@
       <c r="P894" s="4"/>
       <c r="Q894" s="4"/>
     </row>
-    <row r="895" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="895" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A895" s="6"/>
       <c r="B895" s="4"/>
       <c r="C895" s="4"/>
@@ -18109,7 +18129,7 @@
       <c r="P895" s="4"/>
       <c r="Q895" s="4"/>
     </row>
-    <row r="896" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="896" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A896" s="6"/>
       <c r="B896" s="4"/>
       <c r="C896" s="4"/>
@@ -18128,7 +18148,7 @@
       <c r="P896" s="4"/>
       <c r="Q896" s="4"/>
     </row>
-    <row r="897" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="897" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A897" s="6"/>
       <c r="B897" s="4"/>
       <c r="C897" s="4"/>
@@ -18147,7 +18167,7 @@
       <c r="P897" s="4"/>
       <c r="Q897" s="4"/>
     </row>
-    <row r="898" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="898" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A898" s="6"/>
       <c r="B898" s="4"/>
       <c r="C898" s="4"/>
@@ -18166,7 +18186,7 @@
       <c r="P898" s="4"/>
       <c r="Q898" s="4"/>
     </row>
-    <row r="899" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="899" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A899" s="6"/>
       <c r="B899" s="4"/>
       <c r="C899" s="4"/>
@@ -18185,7 +18205,7 @@
       <c r="P899" s="4"/>
       <c r="Q899" s="4"/>
     </row>
-    <row r="900" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="900" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A900" s="6"/>
       <c r="B900" s="4"/>
       <c r="C900" s="4"/>
@@ -18204,7 +18224,7 @@
       <c r="P900" s="4"/>
       <c r="Q900" s="4"/>
     </row>
-    <row r="901" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="901" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A901" s="6"/>
       <c r="B901" s="4"/>
       <c r="C901" s="4"/>
@@ -18223,7 +18243,7 @@
       <c r="P901" s="4"/>
       <c r="Q901" s="4"/>
     </row>
-    <row r="902" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="902" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A902" s="6"/>
       <c r="B902" s="4"/>
       <c r="C902" s="4"/>
@@ -18242,7 +18262,7 @@
       <c r="P902" s="4"/>
       <c r="Q902" s="4"/>
     </row>
-    <row r="903" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="903" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A903" s="6"/>
       <c r="B903" s="4"/>
       <c r="C903" s="4"/>
@@ -18261,7 +18281,7 @@
       <c r="P903" s="4"/>
       <c r="Q903" s="4"/>
     </row>
-    <row r="904" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="904" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A904" s="6"/>
       <c r="B904" s="4"/>
       <c r="C904" s="4"/>
@@ -18280,7 +18300,7 @@
       <c r="P904" s="4"/>
       <c r="Q904" s="4"/>
     </row>
-    <row r="905" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="905" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A905" s="6"/>
       <c r="B905" s="4"/>
       <c r="C905" s="4"/>
@@ -18299,7 +18319,7 @@
       <c r="P905" s="4"/>
       <c r="Q905" s="4"/>
     </row>
-    <row r="906" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="906" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A906" s="6"/>
       <c r="B906" s="4"/>
       <c r="C906" s="4"/>
@@ -18318,7 +18338,7 @@
       <c r="P906" s="4"/>
       <c r="Q906" s="4"/>
     </row>
-    <row r="907" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="907" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A907" s="6"/>
       <c r="B907" s="4"/>
       <c r="C907" s="4"/>
@@ -18337,7 +18357,7 @@
       <c r="P907" s="4"/>
       <c r="Q907" s="4"/>
     </row>
-    <row r="908" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="908" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A908" s="6"/>
       <c r="B908" s="4"/>
       <c r="C908" s="4"/>
@@ -18356,7 +18376,7 @@
       <c r="P908" s="4"/>
       <c r="Q908" s="4"/>
     </row>
-    <row r="909" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="909" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A909" s="6"/>
       <c r="B909" s="4"/>
       <c r="C909" s="4"/>
@@ -18375,7 +18395,7 @@
       <c r="P909" s="4"/>
       <c r="Q909" s="4"/>
     </row>
-    <row r="910" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="910" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A910" s="6"/>
       <c r="B910" s="4"/>
       <c r="C910" s="4"/>
@@ -18394,7 +18414,7 @@
       <c r="P910" s="4"/>
       <c r="Q910" s="4"/>
     </row>
-    <row r="911" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="911" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A911" s="6"/>
       <c r="B911" s="4"/>
       <c r="C911" s="4"/>
@@ -18413,7 +18433,7 @@
       <c r="P911" s="4"/>
       <c r="Q911" s="4"/>
     </row>
-    <row r="912" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="912" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A912" s="6"/>
       <c r="B912" s="4"/>
       <c r="C912" s="4"/>
@@ -18432,7 +18452,7 @@
       <c r="P912" s="4"/>
       <c r="Q912" s="4"/>
     </row>
-    <row r="913" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="913" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A913" s="6"/>
       <c r="B913" s="4"/>
       <c r="C913" s="4"/>
@@ -18451,7 +18471,7 @@
       <c r="P913" s="4"/>
       <c r="Q913" s="4"/>
     </row>
-    <row r="914" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="914" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A914" s="6"/>
       <c r="B914" s="4"/>
       <c r="C914" s="4"/>
@@ -18470,7 +18490,7 @@
       <c r="P914" s="4"/>
       <c r="Q914" s="4"/>
     </row>
-    <row r="915" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="915" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A915" s="6"/>
       <c r="B915" s="4"/>
       <c r="C915" s="4"/>
@@ -18489,7 +18509,7 @@
       <c r="P915" s="4"/>
       <c r="Q915" s="4"/>
     </row>
-    <row r="916" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="916" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A916" s="6"/>
       <c r="B916" s="4"/>
       <c r="C916" s="4"/>
@@ -18508,7 +18528,7 @@
       <c r="P916" s="4"/>
       <c r="Q916" s="4"/>
     </row>
-    <row r="917" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="917" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A917" s="6"/>
       <c r="B917" s="4"/>
       <c r="C917" s="4"/>
@@ -18527,7 +18547,7 @@
       <c r="P917" s="4"/>
       <c r="Q917" s="4"/>
     </row>
-    <row r="918" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="918" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A918" s="6"/>
       <c r="B918" s="4"/>
       <c r="C918" s="4"/>
@@ -18546,7 +18566,7 @@
       <c r="P918" s="4"/>
       <c r="Q918" s="4"/>
     </row>
-    <row r="919" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="919" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A919" s="6"/>
       <c r="B919" s="4"/>
       <c r="C919" s="4"/>
@@ -18565,7 +18585,7 @@
       <c r="P919" s="4"/>
       <c r="Q919" s="4"/>
     </row>
-    <row r="920" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="920" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A920" s="6"/>
       <c r="B920" s="4"/>
       <c r="C920" s="4"/>
@@ -18584,7 +18604,7 @@
       <c r="P920" s="4"/>
       <c r="Q920" s="4"/>
     </row>
-    <row r="921" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="921" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A921" s="6"/>
       <c r="B921" s="4"/>
       <c r="C921" s="4"/>
@@ -18603,7 +18623,7 @@
       <c r="P921" s="4"/>
       <c r="Q921" s="4"/>
     </row>
-    <row r="922" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="922" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A922" s="6"/>
       <c r="B922" s="4"/>
       <c r="C922" s="4"/>
@@ -18622,7 +18642,7 @@
       <c r="P922" s="4"/>
       <c r="Q922" s="4"/>
     </row>
-    <row r="923" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="923" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A923" s="6"/>
       <c r="B923" s="4"/>
       <c r="C923" s="4"/>
@@ -18641,7 +18661,7 @@
       <c r="P923" s="4"/>
       <c r="Q923" s="4"/>
     </row>
-    <row r="924" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="924" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A924" s="6"/>
       <c r="B924" s="4"/>
       <c r="C924" s="4"/>
@@ -18660,7 +18680,7 @@
       <c r="P924" s="4"/>
       <c r="Q924" s="4"/>
     </row>
-    <row r="925" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="925" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A925" s="6"/>
       <c r="B925" s="4"/>
       <c r="C925" s="4"/>
@@ -18679,7 +18699,7 @@
       <c r="P925" s="4"/>
       <c r="Q925" s="4"/>
     </row>
-    <row r="926" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="926" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A926" s="6"/>
       <c r="B926" s="4"/>
       <c r="C926" s="4"/>
@@ -18698,7 +18718,7 @@
       <c r="P926" s="4"/>
       <c r="Q926" s="4"/>
     </row>
-    <row r="927" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="927" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A927" s="6"/>
       <c r="B927" s="4"/>
       <c r="C927" s="4"/>
@@ -18717,7 +18737,7 @@
       <c r="P927" s="4"/>
       <c r="Q927" s="4"/>
     </row>
-    <row r="928" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="928" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A928" s="6"/>
       <c r="B928" s="4"/>
       <c r="C928" s="4"/>
@@ -18736,7 +18756,7 @@
       <c r="P928" s="4"/>
       <c r="Q928" s="4"/>
     </row>
-    <row r="929" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="929" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A929" s="6"/>
       <c r="B929" s="4"/>
       <c r="C929" s="4"/>
@@ -18755,7 +18775,7 @@
       <c r="P929" s="4"/>
       <c r="Q929" s="4"/>
     </row>
-    <row r="930" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="930" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A930" s="6"/>
       <c r="B930" s="4"/>
       <c r="C930" s="4"/>
@@ -18774,7 +18794,7 @@
       <c r="P930" s="4"/>
       <c r="Q930" s="4"/>
     </row>
-    <row r="931" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="931" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A931" s="6"/>
       <c r="B931" s="4"/>
       <c r="C931" s="4"/>
@@ -18793,7 +18813,7 @@
       <c r="P931" s="4"/>
       <c r="Q931" s="4"/>
     </row>
-    <row r="932" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="932" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A932" s="6"/>
       <c r="B932" s="4"/>
       <c r="C932" s="4"/>
@@ -18812,7 +18832,7 @@
       <c r="P932" s="4"/>
       <c r="Q932" s="4"/>
     </row>
-    <row r="933" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="933" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A933" s="6"/>
       <c r="B933" s="4"/>
       <c r="C933" s="4"/>
@@ -18831,7 +18851,7 @@
       <c r="P933" s="4"/>
       <c r="Q933" s="4"/>
     </row>
-    <row r="934" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="934" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A934" s="6"/>
       <c r="B934" s="4"/>
       <c r="C934" s="4"/>
@@ -18850,7 +18870,7 @@
       <c r="P934" s="4"/>
       <c r="Q934" s="4"/>
     </row>
-    <row r="935" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="935" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A935" s="6"/>
       <c r="B935" s="4"/>
       <c r="C935" s="4"/>
@@ -18869,7 +18889,7 @@
       <c r="P935" s="4"/>
       <c r="Q935" s="4"/>
     </row>
-    <row r="936" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="936" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A936" s="6"/>
       <c r="B936" s="4"/>
       <c r="C936" s="4"/>
@@ -18888,7 +18908,7 @@
       <c r="P936" s="4"/>
       <c r="Q936" s="4"/>
     </row>
-    <row r="937" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="937" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A937" s="6"/>
       <c r="B937" s="4"/>
       <c r="C937" s="4"/>
@@ -18907,7 +18927,7 @@
       <c r="P937" s="4"/>
       <c r="Q937" s="4"/>
     </row>
-    <row r="938" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="938" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A938" s="6"/>
       <c r="B938" s="4"/>
       <c r="C938" s="4"/>
@@ -18926,7 +18946,7 @@
       <c r="P938" s="4"/>
       <c r="Q938" s="4"/>
     </row>
-    <row r="939" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="939" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A939" s="6"/>
       <c r="B939" s="4"/>
       <c r="C939" s="4"/>
@@ -18945,7 +18965,7 @@
       <c r="P939" s="4"/>
       <c r="Q939" s="4"/>
     </row>
-    <row r="940" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="940" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A940" s="6"/>
       <c r="B940" s="4"/>
       <c r="C940" s="4"/>
@@ -18964,7 +18984,7 @@
       <c r="P940" s="4"/>
       <c r="Q940" s="4"/>
     </row>
-    <row r="941" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="941" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A941" s="6"/>
       <c r="B941" s="4"/>
       <c r="C941" s="4"/>
@@ -18983,7 +19003,7 @@
       <c r="P941" s="4"/>
       <c r="Q941" s="4"/>
     </row>
-    <row r="942" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="942" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A942" s="6"/>
       <c r="B942" s="4"/>
       <c r="C942" s="4"/>
@@ -19002,7 +19022,7 @@
       <c r="P942" s="4"/>
       <c r="Q942" s="4"/>
     </row>
-    <row r="943" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="943" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A943" s="6"/>
       <c r="B943" s="4"/>
       <c r="C943" s="4"/>
@@ -19021,7 +19041,7 @@
       <c r="P943" s="4"/>
       <c r="Q943" s="4"/>
     </row>
-    <row r="944" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="944" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A944" s="6"/>
       <c r="B944" s="4"/>
       <c r="C944" s="4"/>
@@ -19040,7 +19060,7 @@
       <c r="P944" s="4"/>
       <c r="Q944" s="4"/>
     </row>
-    <row r="945" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="945" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A945" s="6"/>
       <c r="B945" s="4"/>
       <c r="C945" s="4"/>
@@ -19059,7 +19079,7 @@
       <c r="P945" s="4"/>
       <c r="Q945" s="4"/>
     </row>
-    <row r="946" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="946" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A946" s="6"/>
       <c r="B946" s="4"/>
       <c r="C946" s="4"/>
@@ -19078,7 +19098,7 @@
       <c r="P946" s="4"/>
       <c r="Q946" s="4"/>
     </row>
-    <row r="947" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="947" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A947" s="6"/>
       <c r="B947" s="4"/>
       <c r="C947" s="4"/>
@@ -19097,7 +19117,7 @@
       <c r="P947" s="4"/>
       <c r="Q947" s="4"/>
     </row>
-    <row r="948" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="948" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A948" s="6"/>
       <c r="B948" s="4"/>
       <c r="C948" s="4"/>
@@ -19116,7 +19136,7 @@
       <c r="P948" s="4"/>
       <c r="Q948" s="4"/>
     </row>
-    <row r="949" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="949" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A949" s="6"/>
       <c r="B949" s="4"/>
       <c r="C949" s="4"/>
@@ -19135,7 +19155,7 @@
       <c r="P949" s="4"/>
       <c r="Q949" s="4"/>
     </row>
-    <row r="950" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="950" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A950" s="6"/>
       <c r="B950" s="4"/>
       <c r="C950" s="4"/>
@@ -19154,7 +19174,7 @@
       <c r="P950" s="4"/>
       <c r="Q950" s="4"/>
     </row>
-    <row r="951" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="951" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A951" s="6"/>
       <c r="B951" s="4"/>
       <c r="C951" s="4"/>
@@ -19173,7 +19193,7 @@
       <c r="P951" s="4"/>
       <c r="Q951" s="4"/>
     </row>
-    <row r="952" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="952" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A952" s="6"/>
       <c r="B952" s="4"/>
       <c r="C952" s="4"/>
@@ -19192,7 +19212,7 @@
       <c r="P952" s="4"/>
       <c r="Q952" s="4"/>
     </row>
-    <row r="953" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="953" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A953" s="6"/>
       <c r="B953" s="4"/>
       <c r="C953" s="4"/>
@@ -19211,7 +19231,7 @@
       <c r="P953" s="4"/>
       <c r="Q953" s="4"/>
     </row>
-    <row r="954" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="954" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A954" s="6"/>
       <c r="B954" s="4"/>
       <c r="C954" s="4"/>
@@ -19230,7 +19250,7 @@
       <c r="P954" s="4"/>
       <c r="Q954" s="4"/>
     </row>
-    <row r="955" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="955" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A955" s="6"/>
       <c r="B955" s="4"/>
       <c r="C955" s="4"/>
@@ -19249,7 +19269,7 @@
       <c r="P955" s="4"/>
       <c r="Q955" s="4"/>
     </row>
-    <row r="956" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="956" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A956" s="6"/>
       <c r="B956" s="4"/>
       <c r="C956" s="4"/>
@@ -19268,7 +19288,7 @@
       <c r="P956" s="4"/>
       <c r="Q956" s="4"/>
     </row>
-    <row r="957" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="957" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A957" s="6"/>
       <c r="B957" s="4"/>
       <c r="C957" s="4"/>
@@ -19287,7 +19307,7 @@
       <c r="P957" s="4"/>
       <c r="Q957" s="4"/>
     </row>
-    <row r="958" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="958" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A958" s="6"/>
       <c r="B958" s="4"/>
       <c r="C958" s="4"/>
@@ -19306,7 +19326,7 @@
       <c r="P958" s="4"/>
       <c r="Q958" s="4"/>
     </row>
-    <row r="959" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="959" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="6"/>
       <c r="B959" s="4"/>
       <c r="C959" s="4"/>
@@ -19325,7 +19345,7 @@
       <c r="P959" s="4"/>
       <c r="Q959" s="4"/>
     </row>
-    <row r="960" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="960" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="6"/>
       <c r="B960" s="4"/>
       <c r="C960" s="4"/>
@@ -19344,7 +19364,7 @@
       <c r="P960" s="4"/>
       <c r="Q960" s="4"/>
     </row>
-    <row r="961" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="961" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A961" s="6"/>
       <c r="B961" s="4"/>
       <c r="C961" s="4"/>
@@ -19363,7 +19383,7 @@
       <c r="P961" s="4"/>
       <c r="Q961" s="4"/>
     </row>
-    <row r="962" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="962" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A962" s="6"/>
       <c r="B962" s="4"/>
       <c r="C962" s="4"/>
@@ -19382,7 +19402,7 @@
       <c r="P962" s="4"/>
       <c r="Q962" s="4"/>
     </row>
-    <row r="963" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="963" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A963" s="6"/>
       <c r="B963" s="4"/>
       <c r="C963" s="4"/>
@@ -19401,7 +19421,7 @@
       <c r="P963" s="4"/>
       <c r="Q963" s="4"/>
     </row>
-    <row r="964" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="964" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A964" s="6"/>
       <c r="B964" s="4"/>
       <c r="C964" s="4"/>
@@ -19420,7 +19440,7 @@
       <c r="P964" s="4"/>
       <c r="Q964" s="4"/>
     </row>
-    <row r="965" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="965" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A965" s="6"/>
       <c r="B965" s="4"/>
       <c r="C965" s="4"/>
@@ -19439,7 +19459,7 @@
       <c r="P965" s="4"/>
       <c r="Q965" s="4"/>
     </row>
-    <row r="966" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="966" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A966" s="6"/>
       <c r="B966" s="4"/>
       <c r="C966" s="4"/>
@@ -19458,7 +19478,7 @@
       <c r="P966" s="4"/>
       <c r="Q966" s="4"/>
     </row>
-    <row r="967" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="967" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A967" s="6"/>
       <c r="B967" s="4"/>
       <c r="C967" s="4"/>
@@ -19477,7 +19497,7 @@
       <c r="P967" s="4"/>
       <c r="Q967" s="4"/>
     </row>
-    <row r="968" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="968" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A968" s="6"/>
       <c r="B968" s="4"/>
       <c r="C968" s="4"/>
@@ -19496,7 +19516,7 @@
       <c r="P968" s="4"/>
       <c r="Q968" s="4"/>
     </row>
-    <row r="969" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="969" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A969" s="6"/>
       <c r="B969" s="4"/>
       <c r="C969" s="4"/>
@@ -19515,7 +19535,7 @@
       <c r="P969" s="4"/>
       <c r="Q969" s="4"/>
     </row>
-    <row r="970" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="970" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A970" s="6"/>
       <c r="B970" s="4"/>
       <c r="C970" s="4"/>
@@ -19534,7 +19554,7 @@
       <c r="P970" s="4"/>
       <c r="Q970" s="4"/>
     </row>
-    <row r="971" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="971" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A971" s="6"/>
       <c r="B971" s="4"/>
       <c r="C971" s="4"/>
@@ -19553,7 +19573,7 @@
       <c r="P971" s="4"/>
       <c r="Q971" s="4"/>
     </row>
-    <row r="972" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="972" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A972" s="6"/>
       <c r="B972" s="4"/>
       <c r="C972" s="4"/>
@@ -19572,7 +19592,7 @@
       <c r="P972" s="4"/>
       <c r="Q972" s="4"/>
     </row>
-    <row r="973" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="973" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A973" s="6"/>
       <c r="B973" s="4"/>
       <c r="C973" s="4"/>
@@ -19591,7 +19611,7 @@
       <c r="P973" s="4"/>
       <c r="Q973" s="4"/>
     </row>
-    <row r="974" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="974" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A974" s="6"/>
       <c r="B974" s="4"/>
       <c r="C974" s="4"/>
@@ -19610,7 +19630,7 @@
       <c r="P974" s="4"/>
       <c r="Q974" s="4"/>
     </row>
-    <row r="975" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="975" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A975" s="6"/>
       <c r="B975" s="4"/>
       <c r="C975" s="4"/>
@@ -19629,7 +19649,7 @@
       <c r="P975" s="4"/>
       <c r="Q975" s="4"/>
     </row>
-    <row r="976" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="976" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A976" s="6"/>
       <c r="B976" s="4"/>
       <c r="C976" s="4"/>
@@ -19648,7 +19668,7 @@
       <c r="P976" s="4"/>
       <c r="Q976" s="4"/>
     </row>
-    <row r="977" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="977" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A977" s="6"/>
       <c r="B977" s="4"/>
       <c r="C977" s="4"/>
@@ -19667,7 +19687,7 @@
       <c r="P977" s="4"/>
       <c r="Q977" s="4"/>
     </row>
-    <row r="978" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="978" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A978" s="6"/>
       <c r="B978" s="4"/>
       <c r="C978" s="4"/>
@@ -19686,7 +19706,7 @@
       <c r="P978" s="4"/>
       <c r="Q978" s="4"/>
     </row>
-    <row r="979" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="979" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A979" s="6"/>
       <c r="B979" s="4"/>
       <c r="C979" s="4"/>
@@ -19705,7 +19725,7 @@
       <c r="P979" s="4"/>
       <c r="Q979" s="4"/>
     </row>
-    <row r="980" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="980" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A980" s="6"/>
       <c r="B980" s="4"/>
       <c r="C980" s="4"/>
@@ -19724,7 +19744,7 @@
       <c r="P980" s="4"/>
       <c r="Q980" s="4"/>
     </row>
-    <row r="981" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="981" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A981" s="6"/>
       <c r="B981" s="4"/>
       <c r="C981" s="4"/>
@@ -19743,7 +19763,7 @@
       <c r="P981" s="4"/>
       <c r="Q981" s="4"/>
     </row>
-    <row r="982" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="982" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A982" s="6"/>
       <c r="B982" s="4"/>
       <c r="C982" s="4"/>
@@ -19762,7 +19782,7 @@
       <c r="P982" s="4"/>
       <c r="Q982" s="4"/>
     </row>
-    <row r="983" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="983" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A983" s="6"/>
       <c r="B983" s="4"/>
       <c r="C983" s="4"/>
@@ -19781,7 +19801,7 @@
       <c r="P983" s="4"/>
       <c r="Q983" s="4"/>
     </row>
-    <row r="984" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="984" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A984" s="6"/>
       <c r="B984" s="4"/>
       <c r="C984" s="4"/>
@@ -19800,7 +19820,7 @@
       <c r="P984" s="4"/>
       <c r="Q984" s="4"/>
     </row>
-    <row r="985" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="985" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A985" s="6"/>
       <c r="B985" s="4"/>
       <c r="C985" s="4"/>
@@ -19819,7 +19839,7 @@
       <c r="P985" s="4"/>
       <c r="Q985" s="4"/>
     </row>
-    <row r="986" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="986" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A986" s="6"/>
       <c r="B986" s="4"/>
       <c r="C986" s="4"/>
@@ -19838,7 +19858,7 @@
       <c r="P986" s="4"/>
       <c r="Q986" s="4"/>
     </row>
-    <row r="987" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="987" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A987" s="6"/>
       <c r="B987" s="4"/>
       <c r="C987" s="4"/>
@@ -19857,7 +19877,7 @@
       <c r="P987" s="4"/>
       <c r="Q987" s="4"/>
     </row>
-    <row r="988" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="988" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A988" s="6"/>
       <c r="B988" s="4"/>
       <c r="C988" s="4"/>
@@ -19876,7 +19896,7 @@
       <c r="P988" s="4"/>
       <c r="Q988" s="4"/>
     </row>
-    <row r="989" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="989" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A989" s="6"/>
       <c r="B989" s="4"/>
       <c r="C989" s="4"/>
@@ -19895,7 +19915,7 @@
       <c r="P989" s="4"/>
       <c r="Q989" s="4"/>
     </row>
-    <row r="990" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="990" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A990" s="6"/>
       <c r="B990" s="4"/>
       <c r="C990" s="4"/>
@@ -19914,7 +19934,7 @@
       <c r="P990" s="4"/>
       <c r="Q990" s="4"/>
     </row>
-    <row r="991" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="991" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A991" s="6"/>
       <c r="B991" s="4"/>
       <c r="C991" s="4"/>
@@ -19933,7 +19953,7 @@
       <c r="P991" s="4"/>
       <c r="Q991" s="4"/>
     </row>
-    <row r="992" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="992" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A992" s="6"/>
       <c r="B992" s="4"/>
       <c r="C992" s="4"/>
@@ -19952,7 +19972,7 @@
       <c r="P992" s="4"/>
       <c r="Q992" s="4"/>
     </row>
-    <row r="993" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="993" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A993" s="6"/>
       <c r="B993" s="4"/>
       <c r="C993" s="4"/>
@@ -19971,7 +19991,7 @@
       <c r="P993" s="4"/>
       <c r="Q993" s="4"/>
     </row>
-    <row r="994" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="994" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A994" s="6"/>
       <c r="B994" s="4"/>
       <c r="C994" s="4"/>
@@ -19990,7 +20010,7 @@
       <c r="P994" s="4"/>
       <c r="Q994" s="4"/>
     </row>
-    <row r="995" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="995" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A995" s="6"/>
       <c r="B995" s="4"/>
       <c r="C995" s="4"/>
@@ -20009,7 +20029,7 @@
       <c r="P995" s="4"/>
       <c r="Q995" s="4"/>
     </row>
-    <row r="996" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="996" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A996" s="6"/>
       <c r="B996" s="4"/>
       <c r="C996" s="4"/>
@@ -20028,7 +20048,7 @@
       <c r="P996" s="4"/>
       <c r="Q996" s="4"/>
     </row>
-    <row r="997" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="997" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A997" s="6"/>
       <c r="B997" s="4"/>
       <c r="C997" s="4"/>
@@ -20047,7 +20067,7 @@
       <c r="P997" s="4"/>
       <c r="Q997" s="4"/>
     </row>
-    <row r="998" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="998" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A998" s="6"/>
       <c r="B998" s="4"/>
       <c r="C998" s="4"/>
@@ -20066,7 +20086,7 @@
       <c r="P998" s="4"/>
       <c r="Q998" s="4"/>
     </row>
-    <row r="999" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="999" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A999" s="6"/>
       <c r="B999" s="4"/>
       <c r="C999" s="4"/>
@@ -20085,7 +20105,7 @@
       <c r="P999" s="4"/>
       <c r="Q999" s="4"/>
     </row>
-    <row r="1000" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1000" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1000" s="6"/>
       <c r="B1000" s="4"/>
       <c r="C1000" s="4"/>

--- a/source/INVOICE.xlsx
+++ b/source/INVOICE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\ADMISSION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C7CF95A7-79BB-4346-9015-0ECA4F51626E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBB50F5-D031-4E6B-9A8F-F15437FABC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="8">
-        <v>12360</v>
+        <v>12240</v>
       </c>
       <c r="I4" s="10">
         <v>7550</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" s="17">
         <f t="shared" si="0"/>
-        <v>89910</v>
+        <v>89790</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="8">
-        <v>12840</v>
+        <v>13080</v>
       </c>
       <c r="I5" s="10">
         <v>7550</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="Q5" s="17">
         <f t="shared" si="0"/>
-        <v>90390</v>
+        <v>90630</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="8">
-        <v>28080</v>
+        <v>24870</v>
       </c>
       <c r="I6" s="10">
         <v>10730</v>
@@ -850,7 +850,7 @@
       </c>
       <c r="Q6" s="17">
         <f t="shared" si="0"/>
-        <v>108810</v>
+        <v>105600</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>5000</v>
       </c>
       <c r="H7" s="8">
-        <v>24900</v>
+        <v>25890</v>
       </c>
       <c r="I7" s="10">
         <v>11330</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q7" s="17">
         <f t="shared" si="0"/>
-        <v>114730</v>
+        <v>115720</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -930,7 +930,7 @@
         <v>5000</v>
       </c>
       <c r="H8" s="8">
-        <v>24900</v>
+        <v>25890</v>
       </c>
       <c r="I8" s="10">
         <v>11330</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="0"/>
-        <v>114730</v>
+        <v>115720</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -984,7 +984,7 @@
         <v>5000</v>
       </c>
       <c r="H9" s="8">
-        <v>26040</v>
+        <v>27030</v>
       </c>
       <c r="I9" s="10">
         <v>13230</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="0"/>
-        <v>117770</v>
+        <v>118760</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>5000</v>
       </c>
       <c r="H10" s="8">
-        <v>26040</v>
+        <v>27030</v>
       </c>
       <c r="I10" s="10">
         <v>13230</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="0"/>
-        <v>117770</v>
+        <v>118760</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
         <v>5000</v>
       </c>
       <c r="H11" s="8">
-        <v>27660</v>
+        <v>28890</v>
       </c>
       <c r="I11" s="10">
         <v>13230</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Q11" s="17">
         <f t="shared" si="0"/>
-        <v>119390</v>
+        <v>120620</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1146,7 +1146,7 @@
         <v>6000</v>
       </c>
       <c r="H12" s="8">
-        <v>17940</v>
+        <v>19560</v>
       </c>
       <c r="I12" s="10">
         <v>16190</v>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="Q12" s="17">
         <f t="shared" si="0"/>
-        <v>119130</v>
+        <v>120750</v>
       </c>
     </row>
     <row r="13" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1200,7 +1200,7 @@
         <v>6000</v>
       </c>
       <c r="H13" s="8">
-        <v>17940</v>
+        <v>19560</v>
       </c>
       <c r="I13" s="10">
         <v>14330</v>
@@ -1228,7 +1228,7 @@
       </c>
       <c r="Q13" s="17">
         <f t="shared" si="0"/>
-        <v>117270</v>
+        <v>118890</v>
       </c>
     </row>
     <row r="14" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1254,7 +1254,7 @@
         <v>6000</v>
       </c>
       <c r="H14" s="8">
-        <v>24180</v>
+        <v>22580</v>
       </c>
       <c r="I14" s="10">
         <v>14330</v>
@@ -1282,7 +1282,7 @@
       </c>
       <c r="Q14" s="17">
         <f t="shared" si="0"/>
-        <v>123510</v>
+        <v>121910</v>
       </c>
     </row>
     <row r="15" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1308,7 +1308,7 @@
         <v>8000</v>
       </c>
       <c r="H15" s="8">
-        <v>12480</v>
+        <v>14280</v>
       </c>
       <c r="I15" s="10">
         <v>14330</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Q15" s="17">
         <f t="shared" si="0"/>
-        <v>128810</v>
+        <v>130610</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1362,7 +1362,7 @@
         <v>8000</v>
       </c>
       <c r="H16" s="8">
-        <v>12480</v>
+        <v>14280</v>
       </c>
       <c r="I16" s="10">
         <v>14330</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="Q16" s="17">
         <f t="shared" si="0"/>
-        <v>128810</v>
+        <v>130610</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>8000</v>
       </c>
       <c r="H17" s="8">
-        <v>12480</v>
+        <v>14280</v>
       </c>
       <c r="I17" s="10">
         <v>14330</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Q17" s="17">
         <f t="shared" si="0"/>
-        <v>128810</v>
+        <v>130610</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">

--- a/source/INVOICE.xlsx
+++ b/source/INVOICE.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\KBI\ACCOUNTS\ADMISSION\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DBBB50F5-D031-4E6B-9A8F-F15437FABC71}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{62F1B7E6-8B59-418F-9DCC-CB423CA67BBB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -660,7 +660,7 @@
         <v>0</v>
       </c>
       <c r="H3" s="8">
-        <v>8040</v>
+        <v>6840</v>
       </c>
       <c r="I3" s="10">
         <v>5300</v>
@@ -688,7 +688,7 @@
       </c>
       <c r="Q3" s="17">
         <f t="shared" si="0"/>
-        <v>83340</v>
+        <v>82140</v>
       </c>
     </row>
     <row r="4" spans="1:27" x14ac:dyDescent="0.25">
@@ -714,7 +714,7 @@
         <v>0</v>
       </c>
       <c r="H4" s="8">
-        <v>12240</v>
+        <v>12480</v>
       </c>
       <c r="I4" s="10">
         <v>7550</v>
@@ -742,7 +742,7 @@
       </c>
       <c r="Q4" s="17">
         <f t="shared" si="0"/>
-        <v>89790</v>
+        <v>90030</v>
       </c>
     </row>
     <row r="5" spans="1:27" x14ac:dyDescent="0.25">
@@ -768,7 +768,7 @@
         <v>0</v>
       </c>
       <c r="H5" s="8">
-        <v>13080</v>
+        <v>13380</v>
       </c>
       <c r="I5" s="10">
         <v>7550</v>
@@ -796,7 +796,7 @@
       </c>
       <c r="Q5" s="17">
         <f t="shared" si="0"/>
-        <v>90630</v>
+        <v>90930</v>
       </c>
     </row>
     <row r="6" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -822,7 +822,7 @@
         <v>0</v>
       </c>
       <c r="H6" s="8">
-        <v>24870</v>
+        <v>24450</v>
       </c>
       <c r="I6" s="10">
         <v>10730</v>
@@ -850,7 +850,7 @@
       </c>
       <c r="Q6" s="17">
         <f t="shared" si="0"/>
-        <v>105600</v>
+        <v>105180</v>
       </c>
     </row>
     <row r="7" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -876,7 +876,7 @@
         <v>5000</v>
       </c>
       <c r="H7" s="8">
-        <v>25890</v>
+        <v>25550</v>
       </c>
       <c r="I7" s="10">
         <v>11330</v>
@@ -904,7 +904,7 @@
       </c>
       <c r="Q7" s="17">
         <f t="shared" si="0"/>
-        <v>115720</v>
+        <v>115380</v>
       </c>
     </row>
     <row r="8" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -930,7 +930,7 @@
         <v>5000</v>
       </c>
       <c r="H8" s="8">
-        <v>25890</v>
+        <v>25730</v>
       </c>
       <c r="I8" s="10">
         <v>11330</v>
@@ -958,7 +958,7 @@
       </c>
       <c r="Q8" s="17">
         <f t="shared" si="0"/>
-        <v>115720</v>
+        <v>115560</v>
       </c>
     </row>
     <row r="9" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -984,7 +984,7 @@
         <v>5000</v>
       </c>
       <c r="H9" s="8">
-        <v>27030</v>
+        <v>26890</v>
       </c>
       <c r="I9" s="10">
         <v>13230</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="Q9" s="17">
         <f t="shared" si="0"/>
-        <v>118760</v>
+        <v>118620</v>
       </c>
     </row>
     <row r="10" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1038,7 +1038,7 @@
         <v>5000</v>
       </c>
       <c r="H10" s="8">
-        <v>27030</v>
+        <v>26910</v>
       </c>
       <c r="I10" s="10">
         <v>13230</v>
@@ -1066,7 +1066,7 @@
       </c>
       <c r="Q10" s="17">
         <f t="shared" si="0"/>
-        <v>118760</v>
+        <v>118640</v>
       </c>
     </row>
     <row r="11" spans="1:27" x14ac:dyDescent="0.25">
@@ -1092,7 +1092,7 @@
         <v>5000</v>
       </c>
       <c r="H11" s="8">
-        <v>28890</v>
+        <v>28850</v>
       </c>
       <c r="I11" s="10">
         <v>13230</v>
@@ -1120,7 +1120,7 @@
       </c>
       <c r="Q11" s="17">
         <f t="shared" si="0"/>
-        <v>120620</v>
+        <v>120580</v>
       </c>
     </row>
     <row r="12" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1308,7 +1308,7 @@
         <v>8000</v>
       </c>
       <c r="H15" s="8">
-        <v>14280</v>
+        <v>11880</v>
       </c>
       <c r="I15" s="10">
         <v>14330</v>
@@ -1336,7 +1336,7 @@
       </c>
       <c r="Q15" s="17">
         <f t="shared" si="0"/>
-        <v>130610</v>
+        <v>128210</v>
       </c>
     </row>
     <row r="16" spans="1:27" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1362,7 +1362,7 @@
         <v>8000</v>
       </c>
       <c r="H16" s="8">
-        <v>14280</v>
+        <v>11880</v>
       </c>
       <c r="I16" s="10">
         <v>14330</v>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="Q16" s="17">
         <f t="shared" si="0"/>
-        <v>130610</v>
+        <v>128210</v>
       </c>
     </row>
     <row r="17" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -1416,7 +1416,7 @@
         <v>8000</v>
       </c>
       <c r="H17" s="8">
-        <v>14280</v>
+        <v>11880</v>
       </c>
       <c r="I17" s="10">
         <v>14330</v>
@@ -1444,7 +1444,7 @@
       </c>
       <c r="Q17" s="17">
         <f t="shared" si="0"/>
-        <v>130610</v>
+        <v>128210</v>
       </c>
     </row>
     <row r="18" spans="1:17" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
